--- a/Visualization/results/bla6250EM0626goodtrace/all_neurons_transients.xlsx
+++ b/Visualization/results/bla6250EM0626goodtrace/all_neurons_transients.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:X604"/>
+  <dimension ref="A1:X603"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -589,15 +589,15 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 1363, 'value': -0.5987378405669224, 'amplitude': 0.1608788240613831, 'start_idx': 1344, 'end_idx': 1382, 'duration': 7.916666666666667, 'fwhm': 3.6958208488873843, 'rise_time': 3.9583333333333335, 'decay_time': 3.9583333333333335, 'auc': 0.8954883354531543}, {'index': 1428, 'value': -0.5610918883461864, 'amplitude': 0.19852477628211906, 'start_idx': 1410, 'end_idx': 1445, 'duration': 7.291666666666667, 'fwhm': 5.709845128027004, 'rise_time': 3.75, 'decay_time': 3.541666666666667, 'auc': 1.179370677022826}]</t>
         </is>
       </c>
       <c r="P2" t="n">
@@ -675,15 +675,15 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 1651, 'value': -0.47534273565491264, 'amplitude': 0.2842739289733928, 'start_idx': 1632, 'end_idx': 1658, 'duration': 5.416666666666667, 'fwhm': 11.434668181763405, 'rise_time': 3.9583333333333335, 'decay_time': 1.4583333333333335, 'auc': 1.3684603922315102}, {'index': 1757, 'value': -0.5078789795308973, 'amplitude': 0.2517376850974081, 'start_idx': 1742, 'end_idx': 1771, 'duration': 6.041666666666667, 'fwhm': 3.134029524073204, 'rise_time': 3.125, 'decay_time': 2.916666666666667, 'auc': 1.29656886687008}]</t>
         </is>
       </c>
       <c r="P3" t="n">
@@ -2739,15 +2739,15 @@
       </c>
       <c r="M27" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N27" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O27" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 1715, 'value': -0.29295093351197965, 'amplitude': 0.346100179674256, 'start_idx': 1711, 'end_idx': 1725, 'duration': 2.916666666666667, 'fwhm': 7.052678483016072, 'rise_time': 0.8333333333333334, 'decay_time': 2.0833333333333335, 'auc': 0.9088468471817059}]</t>
         </is>
       </c>
       <c r="P27" t="n">
@@ -3169,15 +3169,15 @@
       </c>
       <c r="M32" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N32" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O32" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 18, 'value': -0.48764418128201714, 'amplitude': 0.21633321257475768, 'start_idx': 1, 'end_idx': 43, 'duration': 8.75, 'fwhm': 4.434691408280843, 'rise_time': 3.541666666666667, 'decay_time': 5.208333333333334, 'auc': 1.1447226018052263}]</t>
         </is>
       </c>
       <c r="P32" t="n">
@@ -3427,15 +3427,15 @@
       </c>
       <c r="M35" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N35" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O35" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 2118, 'value': -0.15126321953490077, 'amplitude': 0.5527141743218741, 'start_idx': 2114, 'end_idx': 2144, 'duration': 6.25, 'fwhm': 7.716550633484379, 'rise_time': 0.8333333333333334, 'decay_time': 5.416666666666667, 'auc': 3.091308458544141}]</t>
         </is>
       </c>
       <c r="P35" t="n">
@@ -3513,15 +3513,15 @@
       </c>
       <c r="M36" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N36" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O36" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 2237, 'value': -0.22014891990814311, 'amplitude': 0.4838284739486317, 'start_idx': 2199, 'end_idx': 2248, 'duration': 10.208333333333334, 'fwhm': 4.718546405665242, 'rise_time': 7.916666666666667, 'decay_time': 2.291666666666667, 'auc': 4.214935900432025}, {'index': 2362, 'value': -0.15688849600104393, 'amplitude': 0.5470888978557309, 'start_idx': 2346, 'end_idx': 2397, 'duration': 10.625, 'fwhm': 3.0626085585042047, 'rise_time': 3.3333333333333335, 'decay_time': 7.291666666666667, 'auc': 4.239946795547456}]</t>
         </is>
       </c>
       <c r="P36" t="n">
@@ -3599,15 +3599,15 @@
       </c>
       <c r="M37" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N37" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O37" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 2508, 'value': -0.24944637128685881, 'amplitude': 0.454531022569916, 'start_idx': 2504, 'end_idx': 2531, 'duration': 5.625, 'fwhm': 5.147488915680185, 'rise_time': 0.8333333333333334, 'decay_time': 4.791666666666667, 'auc': 2.0911815831607594}]</t>
         </is>
       </c>
       <c r="P37" t="n">
@@ -3685,15 +3685,15 @@
       </c>
       <c r="M38" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N38" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O38" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 2650, 'value': -0.2687913480137937, 'amplitude': 0.43518604584298115, 'start_idx': 2624, 'end_idx': 2658, 'duration': 7.083333333333334, 'fwhm': 5.965728220747337, 'rise_time': 5.416666666666667, 'decay_time': 1.6666666666666667, 'auc': 2.570111318916952}]</t>
         </is>
       </c>
       <c r="P38" t="n">
@@ -4631,15 +4631,15 @@
       </c>
       <c r="M49" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N49" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O49" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 2318, 'value': 0.0437633659323583, 'amplitude': 0.7349554231915093, 'start_idx': 2311, 'end_idx': 2323, 'duration': 2.5, 'fwhm': 4.829075199310941, 'rise_time': 1.4583333333333335, 'decay_time': 1.0416666666666667, 'auc': 1.7963761401120188}]</t>
         </is>
       </c>
       <c r="P49" t="n">
@@ -4717,15 +4717,15 @@
       </c>
       <c r="M50" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N50" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O50" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 2649, 'value': -0.30143522094179703, 'amplitude': 0.38975683631735397, 'start_idx': 2646, 'end_idx': 2655, 'duration': 1.875, 'fwhm': 7.716597656311896, 'rise_time': 0.625, 'decay_time': 1.25, 'auc': 0.7019382682493448}, {'index': 2730, 'value': -0.3369769734301522, 'amplitude': 0.3542150838289988, 'start_idx': 2697, 'end_idx': 2748, 'duration': 10.625, 'fwhm': 5.296909345678671, 'rise_time': 6.875, 'decay_time': 3.75, 'auc': 2.806092034368316}, {'index': 2823, 'value': -0.2838539940621664, 'amplitude': 0.4073380631969846, 'start_idx': 2820, 'end_idx': 2846, 'duration': 5.416666666666667, 'fwhm': 11.976643847669191, 'rise_time': 0.625, 'decay_time': 4.791666666666667, 'auc': 1.7566759217553776}, {'index': 2894, 'value': -0.25960874146133334, 'amplitude': 0.43158331579781767, 'start_idx': 2868, 'end_idx': 2913, 'duration': 9.375, 'fwhm': 3.1473619631456513, 'rise_time': 5.416666666666667, 'decay_time': 3.9583333333333335, 'auc': 3.3267930917786015}, {'index': 2960, 'value': -0.20613552181133502, 'amplitude': 0.485056535447816, 'start_idx': 2955, 'end_idx': 2965, 'duration': 2.0833333333333335, 'fwhm': 7.963771243068247, 'rise_time': 1.0416666666666667, 'decay_time': 1.0416666666666667, 'auc': 0.9898600253498803}]</t>
         </is>
       </c>
       <c r="P50" t="n">
@@ -4803,15 +4803,15 @@
       </c>
       <c r="M51" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N51" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O51" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 281, 'value': 0.3042433004713792, 'amplitude': 0.3328944495908585, 'start_idx': 268, 'end_idx': 302, 'duration': 7.083333333333334, 'fwhm': 3.194164041882945, 'rise_time': 2.7083333333333335, 'decay_time': 4.375, 'auc': 1.5292757699487574}]</t>
         </is>
       </c>
       <c r="P51" t="n">
@@ -4889,15 +4889,15 @@
       </c>
       <c r="M52" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N52" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O52" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 394, 'value': 0.3931384084687306, 'amplitude': 0.4217895575882099, 'start_idx': 382, 'end_idx': 430, 'duration': 10.0, 'fwhm': 2.7118767574276488, 'rise_time': 2.5, 'decay_time': 7.5, 'auc': 2.3482019485987564}]</t>
         </is>
       </c>
       <c r="P52" t="n">
@@ -5577,15 +5577,15 @@
       </c>
       <c r="M60" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N60" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O60" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 2117, 'value': 0.3225313914526815, 'amplitude': 0.3511825405721608, 'start_idx': 2099, 'end_idx': 2138, 'duration': 8.125, 'fwhm': 3.391827100907676, 'rise_time': 3.75, 'decay_time': 4.375, 'auc': 1.8904160093829132}]</t>
         </is>
       </c>
       <c r="P60" t="n">
@@ -6093,15 +6093,15 @@
       </c>
       <c r="M66" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N66" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O66" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 2787, 'value': 0.3998976070133916, 'amplitude': 0.4285487561328709, 'start_idx': 2776, 'end_idx': 2807, 'duration': 6.458333333333334, 'fwhm': 5.489150835564374, 'rise_time': 2.291666666666667, 'decay_time': 4.166666666666667, 'auc': 2.15937714457926}]</t>
         </is>
       </c>
       <c r="P66" t="n">
@@ -7555,15 +7555,15 @@
       </c>
       <c r="M83" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N83" t="n">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c r="O83" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 2598, 'value': -0.031285788201038014, 'amplitude': 0.4461573055222113, 'start_idx': 2595, 'end_idx': 2623, 'duration': 5.833333333333334, 'fwhm': 10.58542812195403, 'rise_time': 0.625, 'decay_time': 5.208333333333334, 'auc': 1.9761100420046183}, {'index': 2648, 'value': -0.04309515921416403, 'amplitude': 0.43434793450908527, 'start_idx': 2623, 'end_idx': 2657, 'duration': 7.083333333333334, 'fwhm': 7.627798846389643, 'rise_time': 5.208333333333334, 'decay_time': 1.875, 'auc': 2.544968682092698}, {'index': 2730, 'value': -0.004358687281732028, 'amplitude': 0.4730844064415172, 'start_idx': 2724, 'end_idx': 2751, 'duration': 5.625, 'fwhm': 8.145687840944902, 'rise_time': 1.25, 'decay_time': 4.375, 'auc': 1.9104213573519024}, {'index': 2815, 'value': -0.05804715953990716, 'amplitude': 0.4193959341833421, 'start_idx': 2797, 'end_idx': 2842, 'duration': 9.375, 'fwhm': 4.877867971186258, 'rise_time': 3.75, 'decay_time': 5.625, 'auc': 2.78208813328052}, {'index': 2898, 'value': -0.07698493596367487, 'amplitude': 0.4004581577595744, 'start_idx': 2862, 'end_idx': 2914, 'duration': 10.833333333333334, 'fwhm': 3.6094646300706286, 'rise_time': 7.5, 'decay_time': 3.3333333333333335, 'auc': 3.0053997510141137}]</t>
         </is>
       </c>
       <c r="P83" t="n">
@@ -7985,15 +7985,15 @@
       </c>
       <c r="M88" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N88" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O88" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 1199, 'value': 0.10250556580018323, 'amplitude': 0.20414851453790553, 'start_idx': 1186, 'end_idx': 1216, 'duration': 6.25, 'fwhm': 3.8934311908348227, 'rise_time': 2.7083333333333335, 'decay_time': 3.541666666666667, 'auc': 0.9899413707813498}, {'index': 1399, 'value': 0.10676592977107252, 'amplitude': 0.2084088785087948, 'start_idx': 1370, 'end_idx': 1422, 'duration': 10.833333333333334, 'fwhm': 5.9197876560852105, 'rise_time': 6.041666666666667, 'decay_time': 4.791666666666667, 'auc': 1.4304246616801184}]</t>
         </is>
       </c>
       <c r="P88" t="n">
@@ -8759,15 +8759,15 @@
       </c>
       <c r="M97" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N97" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O97" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 249, 'value': -0.49688835427236827, 'amplitude': 0.168835054595104, 'start_idx': 236, 'end_idx': 265, 'duration': 6.041666666666667, 'fwhm': 2.775605318508839, 'rise_time': 2.7083333333333335, 'decay_time': 3.3333333333333335, 'auc': 0.6884047345604402}]</t>
         </is>
       </c>
       <c r="P97" t="n">
@@ -8845,15 +8845,15 @@
       </c>
       <c r="M98" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N98" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O98" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 560, 'value': -0.34068172023041715, 'amplitude': 0.3250416886370551, 'start_idx': 557, 'end_idx': 585, 'duration': 5.833333333333334, 'fwhm': 3.728825913325551, 'rise_time': 0.625, 'decay_time': 5.208333333333334, 'auc': 1.2394913990540966}]</t>
         </is>
       </c>
       <c r="P98" t="n">
@@ -9619,15 +9619,15 @@
       </c>
       <c r="M107" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N107" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O107" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 1802, 'value': -0.5552703160043573, 'amplitude': 0.110453092863115, 'start_idx': 1785, 'end_idx': 1826, 'duration': 8.541666666666668, 'fwhm': 5.534999528632862, 'rise_time': 3.541666666666667, 'decay_time': 5.0, 'auc': 0.6002865180868391}]</t>
         </is>
       </c>
       <c r="P107" t="n">
@@ -10135,15 +10135,15 @@
       </c>
       <c r="M113" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N113" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O113" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 458, 'value': 0.14405011273562487, 'amplitude': 0.8705719449310537, 'start_idx': 435, 'end_idx': 472, 'duration': 7.708333333333334, 'fwhm': 2.5615247440369515, 'rise_time': 4.791666666666667, 'decay_time': 2.916666666666667, 'auc': 4.477961306042948}]</t>
         </is>
       </c>
       <c r="P113" t="n">
@@ -10221,15 +10221,15 @@
       </c>
       <c r="M114" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N114" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O114" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 854, 'value': -0.2611057158253243, 'amplitude': 0.46541611637010455, 'start_idx': 828, 'end_idx': 876, 'duration': 10.0, 'fwhm': 4.677383129923906, 'rise_time': 5.416666666666667, 'decay_time': 4.583333333333334, 'auc': 3.454741595966176}, {'index': 902, 'value': -0.16204341817520934, 'amplitude': 0.5644784140202195, 'start_idx': 876, 'end_idx': 920, 'duration': 9.166666666666668, 'fwhm': 5.10457480028407, 'rise_time': 5.416666666666667, 'decay_time': 3.75, 'auc': 3.866460671101742}]</t>
         </is>
       </c>
       <c r="P114" t="n">
@@ -10307,15 +10307,15 @@
       </c>
       <c r="M115" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N115" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O115" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 1186, 'value': -0.24301740678539538, 'amplitude': 0.48350442541003347, 'start_idx': 1162, 'end_idx': 1206, 'duration': 9.166666666666668, 'fwhm': 4.04898294916175, 'rise_time': 5.0, 'decay_time': 4.166666666666667, 'auc': 3.1844897337187787}, {'index': 1311, 'value': -0.3190734172497333, 'amplitude': 0.40744841494569556, 'start_idx': 1309, 'end_idx': 1337, 'duration': 5.833333333333334, 'fwhm': 5.4844298528139275, 'rise_time': 0.4166666666666667, 'decay_time': 5.416666666666667, 'auc': 1.6899758350962262}]</t>
         </is>
       </c>
       <c r="P115" t="n">
@@ -11425,15 +11425,15 @@
       </c>
       <c r="M128" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N128" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O128" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 1815, 'value': -0.569306825916734, 'amplitude': 0.2343999206787306, 'start_idx': 1799, 'end_idx': 1828, 'duration': 6.041666666666667, 'fwhm': 12.76832348776343, 'rise_time': 3.3333333333333335, 'decay_time': 2.7083333333333335, 'auc': 1.276718298000329}, {'index': 1898, 'value': -0.5713274261430819, 'amplitude': 0.23237932045238274, 'start_idx': 1895, 'end_idx': 1918, 'duration': 4.791666666666667, 'fwhm': 4.496648877215487, 'rise_time': 0.625, 'decay_time': 4.166666666666667, 'auc': 0.9516711421335213}]</t>
         </is>
       </c>
       <c r="P128" t="n">
@@ -11597,15 +11597,15 @@
       </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N130" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O130" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 2315, 'value': -0.32205066377845876, 'amplitude': 0.48165608281700584, 'start_idx': 2310, 'end_idx': 2323, 'duration': 2.7083333333333335, 'fwhm': 6.787679089833887, 'rise_time': 1.0416666666666667, 'decay_time': 1.6666666666666667, 'auc': 1.2625701124806548}]</t>
         </is>
       </c>
       <c r="P130" t="n">
@@ -12371,15 +12371,15 @@
       </c>
       <c r="M139" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N139" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O139" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 165, 'value': 0.3438339569894853, 'amplitude': 0.8366028009895046, 'start_idx': 155, 'end_idx': 170, 'duration': 3.125, 'fwhm': 1.460697720613613, 'rise_time': 2.0833333333333335, 'decay_time': 1.0416666666666667, 'auc': 2.1939294811013808}]</t>
         </is>
       </c>
       <c r="P139" t="n">
@@ -12543,15 +12543,15 @@
       </c>
       <c r="M141" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N141" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O141" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 1158, 'value': 0.025216082777989687, 'amplitude': 0.5179849267780089, 'start_idx': 1151, 'end_idx': 1162, 'duration': 2.291666666666667, 'fwhm': 3.001971209163088, 'rise_time': 1.4583333333333335, 'decay_time': 0.8333333333333334, 'auc': 1.0868722884787572}]</t>
         </is>
       </c>
       <c r="P141" t="n">
@@ -14177,15 +14177,15 @@
       </c>
       <c r="M160" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N160" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O160" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 2961, 'value': 0.04554147503931878, 'amplitude': 0.538310319039338, 'start_idx': 2954, 'end_idx': 2964, 'duration': 2.0833333333333335, 'fwhm': 2.2406967133023654, 'rise_time': 1.4583333333333335, 'decay_time': 0.625, 'auc': 1.0020856477544569}, {'index': 2990, 'value': -0.09963617014068937, 'amplitude': 0.3931326738593298, 'start_idx': 2983, 'end_idx': 2995, 'duration': 2.5, 'fwhm': 1.8799923877140639, 'rise_time': 1.4583333333333335, 'decay_time': 1.0416666666666667, 'auc': 0.759375696721512}]</t>
         </is>
       </c>
       <c r="P160" t="n">
@@ -14521,15 +14521,15 @@
       </c>
       <c r="M164" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N164" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O164" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 1595, 'value': 0.34618051739230377, 'amplitude': 0.9115255587308655, 'start_idx': 1575, 'end_idx': 1622, 'duration': 9.791666666666668, 'fwhm': 5.259567448981197, 'rise_time': 4.166666666666667, 'decay_time': 5.625, 'auc': 7.085154704936565}]</t>
         </is>
       </c>
       <c r="P164" t="n">
@@ -16327,15 +16327,15 @@
       </c>
       <c r="M185" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N185" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O185" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 151, 'value': -0.43089787799794627, 'amplitude': 0.3422501551881167, 'start_idx': 136, 'end_idx': 167, 'duration': 6.458333333333334, 'fwhm': 4.082708658098794, 'rise_time': 3.125, 'decay_time': 3.3333333333333335, 'auc': 1.9022132391870445}]</t>
         </is>
       </c>
       <c r="P185" t="n">
@@ -16671,15 +16671,15 @@
       </c>
       <c r="M189" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N189" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O189" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 1061, 'value': -0.5900249959750014, 'amplitude': 0.15824223622466793, 'start_idx': 1047, 'end_idx': 1077, 'duration': 6.25, 'fwhm': 2.99720863072082, 'rise_time': 2.916666666666667, 'decay_time': 3.3333333333333335, 'auc': 0.6939300877051854}]</t>
         </is>
       </c>
       <c r="P189" t="n">
@@ -16757,15 +16757,15 @@
       </c>
       <c r="M190" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N190" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O190" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 1707, 'value': -0.5423092963548899, 'amplitude': 0.2059579358447794, 'start_idx': 1700, 'end_idx': 1729, 'duration': 6.041666666666667, 'fwhm': 5.306983452806691, 'rise_time': 1.4583333333333335, 'decay_time': 4.583333333333334, 'auc': 1.074654596587702}]</t>
         </is>
       </c>
       <c r="P190" t="n">
@@ -17187,15 +17187,15 @@
       </c>
       <c r="M195" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N195" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O195" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 2848, 'value': -0.45188794203426996, 'amplitude': 0.2963792901653993, 'start_idx': 2837, 'end_idx': 2867, 'duration': 6.25, 'fwhm': 2.6718785176181354, 'rise_time': 2.291666666666667, 'decay_time': 3.9583333333333335, 'auc': 1.4909328452430035}, {'index': 2891, 'value': -0.5486548153647014, 'amplitude': 0.1996124168349679, 'start_idx': 2888, 'end_idx': 2895, 'duration': 1.4583333333333335, 'fwhm': 5.100093449893279, 'rise_time': 0.625, 'decay_time': 0.8333333333333334, 'auc': 0.2883281508867555}]</t>
         </is>
       </c>
       <c r="P195" t="n">
@@ -17359,15 +17359,15 @@
       </c>
       <c r="M197" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N197" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O197" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 1644, 'value': -0.5949877275049171, 'amplitude': 0.2447380819618269, 'start_idx': 1631, 'end_idx': 1657, 'duration': 5.416666666666667, 'fwhm': 2.3122804892419424, 'rise_time': 2.7083333333333335, 'decay_time': 2.7083333333333335, 'auc': 1.1577342840371379}, {'index': 1670, 'value': -0.6204628079981351, 'amplitude': 0.2192630014686089, 'start_idx': 1657, 'end_idx': 1683, 'duration': 5.416666666666667, 'fwhm': 2.3914221052308924, 'rise_time': 2.7083333333333335, 'decay_time': 2.7083333333333335, 'auc': 1.0500509694913274}]</t>
         </is>
       </c>
       <c r="P197" t="n">
@@ -17445,15 +17445,15 @@
       </c>
       <c r="M198" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N198" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O198" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 1755, 'value': -0.6500519742997574, 'amplitude': 0.18967383516698666, 'start_idx': 1747, 'end_idx': 1770, 'duration': 4.791666666666667, 'fwhm': 3.128773168850264, 'rise_time': 1.6666666666666667, 'decay_time': 3.125, 'auc': 0.8108621879364395}]</t>
         </is>
       </c>
       <c r="P198" t="n">
@@ -18133,15 +18133,15 @@
       </c>
       <c r="M206" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N206" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O206" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 1453, 'value': -0.5423756007290665, 'amplitude': 0.1820210514591264, 'start_idx': 1434, 'end_idx': 1474, 'duration': 8.333333333333334, 'fwhm': 3.2710095064150364, 'rise_time': 3.9583333333333335, 'decay_time': 4.375, 'auc': 1.2753329352738554}]</t>
         </is>
       </c>
       <c r="P206" t="n">
@@ -19251,15 +19251,15 @@
       </c>
       <c r="M219" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N219" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O219" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 1313, 'value': -0.4315577478091278, 'amplitude': 0.27589378676252574, 'start_idx': 1308, 'end_idx': 1335, 'duration': 5.625, 'fwhm': 8.686579040756234, 'rise_time': 1.0416666666666667, 'decay_time': 4.583333333333334, 'auc': 1.0603278131029072}, {'index': 1454, 'value': -0.5156045541447716, 'amplitude': 0.19184698042688197, 'start_idx': 1443, 'end_idx': 1474, 'duration': 6.458333333333334, 'fwhm': 2.5895524224370567, 'rise_time': 2.291666666666667, 'decay_time': 4.166666666666667, 'auc': 0.8797743980874229}]</t>
         </is>
       </c>
       <c r="P219" t="n">
@@ -19337,15 +19337,15 @@
       </c>
       <c r="M220" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N220" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O220" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 1653, 'value': -0.374940484231477, 'amplitude': 0.33251105034017653, 'start_idx': 1645, 'end_idx': 1665, 'duration': 4.166666666666667, 'fwhm': 4.013392447380919, 'rise_time': 1.6666666666666667, 'decay_time': 2.5, 'auc': 1.2601048133627648}]</t>
         </is>
       </c>
       <c r="P220" t="n">
@@ -19509,15 +19509,15 @@
       </c>
       <c r="M222" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N222" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O222" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 1826, 'value': -0.3750526526301894, 'amplitude': 0.33239888194146416, 'start_idx': 1811, 'end_idx': 1837, 'duration': 5.416666666666667, 'fwhm': 3.378618549502856, 'rise_time': 3.125, 'decay_time': 2.291666666666667, 'auc': 1.5894387617285368}]</t>
         </is>
       </c>
       <c r="P222" t="n">
@@ -19595,15 +19595,15 @@
       </c>
       <c r="M223" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N223" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O223" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 1993, 'value': -0.15812864372714727, 'amplitude': 0.5493228908445063, 'start_idx': 1983, 'end_idx': 1997, 'duration': 2.916666666666667, 'fwhm': 4.267079704000167, 'rise_time': 2.0833333333333335, 'decay_time': 0.8333333333333334, 'auc': 1.515587372261213}, {'index': 2039, 'value': -0.35933319514738854, 'amplitude': 0.348118339424265, 'start_idx': 2032, 'end_idx': 2054, 'duration': 4.583333333333334, 'fwhm': 4.101306713623671, 'rise_time': 1.4583333333333335, 'decay_time': 3.125, 'auc': 1.425956341783551}]</t>
         </is>
       </c>
       <c r="P223" t="n">
@@ -20197,15 +20197,15 @@
       </c>
       <c r="M230" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N230" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O230" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 2878, 'value': -0.38014128230880806, 'amplitude': 0.3273102522628455, 'start_idx': 2873, 'end_idx': 2882, 'duration': 1.875, 'fwhm': 4.21355699650358, 'rise_time': 1.0416666666666667, 'decay_time': 0.8333333333333334, 'auc': 0.588841446184735}]</t>
         </is>
       </c>
       <c r="P230" t="n">
@@ -20283,15 +20283,15 @@
       </c>
       <c r="M231" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N231" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O231" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 81, 'value': -0.09096771484098332, 'amplitude': 0.38732410555084285, 'start_idx': 67, 'end_idx': 95, 'duration': 5.833333333333334, 'fwhm': 3.2743252721218052, 'rise_time': 2.916666666666667, 'decay_time': 2.916666666666667, 'auc': 1.8599449165805553}]</t>
         </is>
       </c>
       <c r="P231" t="n">
@@ -20455,15 +20455,15 @@
       </c>
       <c r="M233" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N233" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O233" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 1408, 'value': 0.09641003299636813, 'amplitude': 0.5747018533881942, 'start_idx': 1403, 'end_idx': 1417, 'duration': 2.916666666666667, 'fwhm': 7.888720711305885, 'rise_time': 1.0416666666666667, 'decay_time': 1.875, 'auc': 1.6395554721730115}]</t>
         </is>
       </c>
       <c r="P233" t="n">
@@ -20885,15 +20885,15 @@
       </c>
       <c r="M238" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N238" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O238" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 2812, 'value': 0.14072980395407217, 'amplitude': 0.6190216243458984, 'start_idx': 2804, 'end_idx': 2828, 'duration': 5.0, 'fwhm': 8.097775306502609, 'rise_time': 1.6666666666666667, 'decay_time': 3.3333333333333335, 'auc': 2.735737197689444}, {'index': 2896, 'value': 0.47184853574597874, 'amplitude': 0.9501403561378049, 'start_idx': 2887, 'end_idx': 2912, 'duration': 5.208333333333334, 'fwhm': 3.037354407417183, 'rise_time': 1.875, 'decay_time': 3.3333333333333335, 'auc': 4.413741483890831}]</t>
         </is>
       </c>
       <c r="P238" t="n">
@@ -21057,15 +21057,15 @@
       </c>
       <c r="M240" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N240" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O240" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 327, 'value': -0.4256771137095525, 'amplitude': 0.31089510356443195, 'start_idx': 309, 'end_idx': 355, 'duration': 9.583333333333334, 'fwhm': 2.6930796834564794, 'rise_time': 3.75, 'decay_time': 5.833333333333334, 'auc': 2.0805819902029437}]</t>
         </is>
       </c>
       <c r="P240" t="n">
@@ -21143,15 +21143,15 @@
       </c>
       <c r="M241" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N241" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O241" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 1707, 'value': -0.4725913726512942, 'amplitude': 0.2639808446226903, 'start_idx': 1701, 'end_idx': 1721, 'duration': 4.166666666666667, 'fwhm': 7.571984749219449, 'rise_time': 1.25, 'decay_time': 2.916666666666667, 'auc': 1.0391089313524777}, {'index': 1755, 'value': -0.4954365097453481, 'amplitude': 0.2411357075286364, 'start_idx': 1742, 'end_idx': 1776, 'duration': 7.083333333333334, 'fwhm': 2.9944640511561715, 'rise_time': 2.7083333333333335, 'decay_time': 4.375, 'auc': 1.3312052848302163}]</t>
         </is>
       </c>
       <c r="P241" t="n">
@@ -21659,15 +21659,15 @@
       </c>
       <c r="M247" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N247" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O247" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 2949, 'value': -0.414119879573807, 'amplitude': 0.32245233770017745, 'start_idx': 2928, 'end_idx': 2958, 'duration': 6.25, 'fwhm': 3.0420926975214497, 'rise_time': 4.375, 'decay_time': 1.875, 'auc': 1.7147731662532593}]</t>
         </is>
       </c>
       <c r="P247" t="n">
@@ -22347,15 +22347,15 @@
       </c>
       <c r="M255" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N255" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O255" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 1991, 'value': -0.31655375781436546, 'amplitude': 0.4013895173878327, 'start_idx': 1979, 'end_idx': 2012, 'duration': 6.875, 'fwhm': 2.243799742534189, 'rise_time': 2.5, 'decay_time': 4.375, 'auc': 2.416719827399588}]</t>
         </is>
       </c>
       <c r="P255" t="n">
@@ -23981,15 +23981,15 @@
       </c>
       <c r="M274" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N274" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O274" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 2382, 'value': -0.7029714313106121, 'amplitude': 0.04839478175884626, 'start_idx': 2377, 'end_idx': 2387, 'duration': 2.0833333333333335, 'fwhm': 1.449854807396965, 'rise_time': 1.0416666666666667, 'decay_time': 1.0416666666666667, 'auc': 0.07382245763430192}]</t>
         </is>
       </c>
       <c r="P274" t="n">
@@ -24497,15 +24497,15 @@
       </c>
       <c r="M280" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N280" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O280" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 2002, 'value': -0.06621848441476291, 'amplitude': 0.5282605956121293, 'start_idx': 1986, 'end_idx': 2016, 'duration': 6.25, 'fwhm': 3.051332269861244, 'rise_time': 3.3333333333333335, 'decay_time': 2.916666666666667, 'auc': 2.8244057885561498}, {'index': 2034, 'value': -0.14753199675295903, 'amplitude': 0.4469470832739332, 'start_idx': 2021, 'end_idx': 2057, 'duration': 7.5, 'fwhm': 2.34507438980998, 'rise_time': 2.7083333333333335, 'decay_time': 4.791666666666667, 'auc': 2.392016630675059}]</t>
         </is>
       </c>
       <c r="P280" t="n">
@@ -25529,15 +25529,15 @@
       </c>
       <c r="M292" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N292" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O292" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 1030, 'value': -0.40606107488828386, 'amplitude': 0.2373126187529448, 'start_idx': 996, 'end_idx': 1047, 'duration': 10.625, 'fwhm': 6.302790540133667, 'rise_time': 7.083333333333334, 'decay_time': 3.541666666666667, 'auc': 1.7352443709431256}]</t>
         </is>
       </c>
       <c r="P292" t="n">
@@ -25615,15 +25615,15 @@
       </c>
       <c r="M293" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N293" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O293" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 1716, 'value': -0.26248271042922605, 'amplitude': 0.3808909832120026, 'start_idx': 1711, 'end_idx': 1727, 'duration': 3.3333333333333335, 'fwhm': 6.866763524859607, 'rise_time': 1.0416666666666667, 'decay_time': 2.291666666666667, 'auc': 1.1465820303774112}]</t>
         </is>
       </c>
       <c r="P293" t="n">
@@ -25959,15 +25959,15 @@
       </c>
       <c r="M297" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N297" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O297" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 184, 'value': -0.18476418787273063, 'amplitude': 0.47962045387428964, 'start_idx': 159, 'end_idx': 204, 'duration': 9.375, 'fwhm': 4.598110651236513, 'rise_time': 5.208333333333334, 'decay_time': 4.166666666666667, 'auc': 3.075396199430388}]</t>
         </is>
       </c>
       <c r="P297" t="n">
@@ -26131,15 +26131,15 @@
       </c>
       <c r="M299" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N299" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O299" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 853, 'value': -0.2843315865592302, 'amplitude': 0.3800530551877901, 'start_idx': 837, 'end_idx': 880, 'duration': 8.958333333333334, 'fwhm': 2.8934252177694715, 'rise_time': 3.3333333333333335, 'decay_time': 5.625, 'auc': 2.58332458412499}]</t>
         </is>
       </c>
       <c r="P299" t="n">
@@ -27765,15 +27765,15 @@
       </c>
       <c r="M318" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N318" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O318" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 1896, 'value': -0.18750160395085488, 'amplitude': 0.39223479796362026, 'start_idx': 1880, 'end_idx': 1906, 'duration': 5.416666666666667, 'fwhm': 3.4775778003952005, 'rise_time': 3.3333333333333335, 'decay_time': 2.0833333333333335, 'auc': 1.9236000187572335}]</t>
         </is>
       </c>
       <c r="P318" t="n">
@@ -27851,15 +27851,15 @@
       </c>
       <c r="M319" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N319" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O319" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 2038, 'value': -0.16251074893051112, 'amplitude': 0.4172256529839641, 'start_idx': 2026, 'end_idx': 2053, 'duration': 5.625, 'fwhm': 2.269652565304957, 'rise_time': 2.5, 'decay_time': 3.125, 'auc': 1.9185408097972256}]</t>
         </is>
       </c>
       <c r="P319" t="n">
@@ -28195,15 +28195,15 @@
       </c>
       <c r="M323" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N323" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O323" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 609, 'value': -0.27098263596556826, 'amplitude': 0.2654675606280551, 'start_idx': 590, 'end_idx': 612, 'duration': 4.583333333333334, 'fwhm': 4.674178657353731, 'rise_time': 3.9583333333333335, 'decay_time': 0.625, 'auc': 0.9315134251999071}, {'index': 709, 'value': -0.376977312405943, 'amplitude': 0.15947288418768035, 'start_idx': 693, 'end_idx': 725, 'duration': 6.666666666666667, 'fwhm': 4.069061164523499, 'rise_time': 3.3333333333333335, 'decay_time': 3.3333333333333335, 'auc': 0.7163770896203259}]</t>
         </is>
       </c>
       <c r="P323" t="n">
@@ -29227,15 +29227,15 @@
       </c>
       <c r="M335" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N335" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O335" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 144, 'value': 0.09670597431643904, 'amplitude': 0.45996161019045634, 'start_idx': 128, 'end_idx': 147, 'duration': 3.9583333333333335, 'fwhm': 5.55912974695266, 'rise_time': 3.3333333333333335, 'decay_time': 0.625, 'auc': 1.4068151805147981}, {'index': 186, 'value': -0.024644658942815277, 'amplitude': 0.338610976931202, 'start_idx': 176, 'end_idx': 201, 'duration': 5.208333333333334, 'fwhm': 1.85951881288099, 'rise_time': 2.0833333333333335, 'decay_time': 3.125, 'auc': 1.1808267072100367}]</t>
         </is>
       </c>
       <c r="P335" t="n">
@@ -29313,15 +29313,15 @@
       </c>
       <c r="M336" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N336" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O336" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 766, 'value': 0.17316920200658412, 'amplitude': 0.5364248378806014, 'start_idx': 750, 'end_idx': 782, 'duration': 6.666666666666667, 'fwhm': 3.160274975895566, 'rise_time': 3.3333333333333335, 'decay_time': 3.3333333333333335, 'auc': 2.4519492669093834}, {'index': 856, 'value': 0.22299284658259272, 'amplitude': 0.58624848245661, 'start_idx': 838, 'end_idx': 891, 'duration': 11.041666666666668, 'fwhm': 4.082288150168078, 'rise_time': 3.75, 'decay_time': 7.291666666666667, 'auc': 4.6614558868929326}]</t>
         </is>
       </c>
       <c r="P336" t="n">
@@ -30431,15 +30431,15 @@
       </c>
       <c r="M349" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N349" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O349" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 558, 'value': -0.46733094130993386, 'amplitude': 0.26338458705584483, 'start_idx': 544, 'end_idx': 590, 'duration': 9.583333333333334, 'fwhm': 11.285710645769433, 'rise_time': 2.916666666666667, 'decay_time': 6.666666666666667, 'auc': 1.7674696728749029}, {'index': 609, 'value': -0.5743896164620446, 'amplitude': 0.15632591190373413, 'start_idx': 590, 'end_idx': 643, 'duration': 11.041666666666668, 'fwhm': 4.471545418932834, 'rise_time': 3.9583333333333335, 'decay_time': 7.083333333333334, 'auc': 0.9118025891089225}]</t>
         </is>
       </c>
       <c r="P349" t="n">
@@ -31033,15 +31033,15 @@
       </c>
       <c r="M356" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N356" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O356" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 2809, 'value': -0.30473066947731126, 'amplitude': 0.42598485888846743, 'start_idx': 2800, 'end_idx': 2815, 'duration': 3.125, 'fwhm': 3.4964979444090245, 'rise_time': 1.875, 'decay_time': 1.25, 'auc': 1.2345429921589204}]</t>
         </is>
       </c>
       <c r="P356" t="n">
@@ -31635,15 +31635,15 @@
       </c>
       <c r="M363" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N363" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O363" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 2476, 'value': -0.42854513928544835, 'amplitude': 0.3188649196942881, 'start_idx': 2468, 'end_idx': 2499, 'duration': 6.458333333333334, 'fwhm': 4.939065573491727, 'rise_time': 1.6666666666666667, 'decay_time': 4.791666666666667, 'auc': 1.8751755465162978}, {'index': 2559, 'value': -0.44423633254861755, 'amplitude': 0.3031737264311189, 'start_idx': 2556, 'end_idx': 2568, 'duration': 2.5, 'fwhm': 7.130289193400756, 'rise_time': 0.625, 'decay_time': 1.875, 'auc': 0.7326387105292579}]</t>
         </is>
       </c>
       <c r="P363" t="n">
@@ -31893,15 +31893,15 @@
       </c>
       <c r="M366" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N366" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O366" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 2977, 'value': -0.361281322174933, 'amplitude': 0.3861287368048035, 'start_idx': 2965, 'end_idx': 2991, 'duration': 5.416666666666667, 'fwhm': 3.567583843690822, 'rise_time': 2.5, 'decay_time': 2.916666666666667, 'auc': 1.8971857256616225}]</t>
         </is>
       </c>
       <c r="P366" t="n">
@@ -32151,15 +32151,15 @@
       </c>
       <c r="M369" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N369" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O369" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 1185, 'value': -0.5743247281693868, 'amplitude': 0.16626583435956221, 'start_idx': 1176, 'end_idx': 1202, 'duration': 5.416666666666667, 'fwhm': 10.75787362419888, 'rise_time': 1.875, 'decay_time': 3.541666666666667, 'auc': 0.7323133134526766}]</t>
         </is>
       </c>
       <c r="P369" t="n">
@@ -32237,15 +32237,15 @@
       </c>
       <c r="M370" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N370" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O370" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 1659, 'value': -0.4008340329634608, 'amplitude': 0.33975652956548824, 'start_idx': 1638, 'end_idx': 1666, 'duration': 5.833333333333334, 'fwhm': 4.400125658548623, 'rise_time': 4.375, 'decay_time': 1.4583333333333335, 'auc': 1.7426573018959726}]</t>
         </is>
       </c>
       <c r="P370" t="n">
@@ -32323,15 +32323,15 @@
       </c>
       <c r="M371" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N371" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O371" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 2011, 'value': -0.26180901173282395, 'amplitude': 0.4787815507961251, 'start_idx': 2010, 'end_idx': 2027, 'duration': 3.541666666666667, 'fwhm': 3.5797914204995136, 'rise_time': 0.20833333333333334, 'decay_time': 3.3333333333333335, 'auc': 1.4472546566272633}]</t>
         </is>
       </c>
       <c r="P371" t="n">
@@ -32581,15 +32581,15 @@
       </c>
       <c r="M374" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N374" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O374" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 2562, 'value': -0.38071447511484297, 'amplitude': 0.3598760874141061, 'start_idx': 2556, 'end_idx': 2568, 'duration': 2.5, 'fwhm': 6.8448496669194965, 'rise_time': 1.25, 'decay_time': 1.25, 'auc': 0.8803364824747666}]</t>
         </is>
       </c>
       <c r="P374" t="n">
@@ -33269,15 +33269,15 @@
       </c>
       <c r="M382" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N382" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O382" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 1270, 'value': 0.17654262932350198, 'amplitude': 0.7354274395225199, 'start_idx': 1247, 'end_idx': 1291, 'duration': 9.166666666666668, 'fwhm': 4.946138341812325, 'rise_time': 4.791666666666667, 'decay_time': 4.375, 'auc': 5.677314369242819}, {'index': 1425, 'value': -0.28766383608432144, 'amplitude': 0.2712209741146965, 'start_idx': 1404, 'end_idx': 1434, 'duration': 6.25, 'fwhm': 4.784704717277417, 'rise_time': 4.375, 'decay_time': 1.875, 'auc': 1.0760804834996414}]</t>
         </is>
       </c>
       <c r="P382" t="n">
@@ -34989,15 +34989,15 @@
       </c>
       <c r="M402" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N402" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O402" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 51, 'value': -0.337733382773299, 'amplitude': 0.4329506453102637, 'start_idx': 38, 'end_idx': 62, 'duration': 5.0, 'fwhm': 2.2750085967683287, 'rise_time': 2.7083333333333335, 'decay_time': 2.291666666666667, 'auc': 1.8691176841530381}]</t>
         </is>
       </c>
       <c r="P402" t="n">
@@ -35247,15 +35247,15 @@
       </c>
       <c r="M405" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N405" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O405" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 2034, 'value': -0.48102855771205016, 'amplitude': 0.28965547037151257, 'start_idx': 2026, 'end_idx': 2054, 'duration': 5.833333333333334, 'fwhm': 1.7388488744994866, 'rise_time': 1.6666666666666667, 'decay_time': 4.166666666666667, 'auc': 1.2866294048036058}]</t>
         </is>
       </c>
       <c r="P405" t="n">
@@ -35333,15 +35333,15 @@
       </c>
       <c r="M406" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N406" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O406" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 2243, 'value': -0.4199179763318547, 'amplitude': 0.35076605175170805, 'start_idx': 2228, 'end_idx': 2257, 'duration': 6.041666666666667, 'fwhm': 2.934638711631313, 'rise_time': 3.125, 'decay_time': 2.916666666666667, 'auc': 1.8835986087388816}]</t>
         </is>
       </c>
       <c r="P406" t="n">
@@ -35763,15 +35763,15 @@
       </c>
       <c r="M411" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N411" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O411" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 1756, 'value': -0.439119361470023, 'amplitude': 0.29697605420123324, 'start_idx': 1741, 'end_idx': 1771, 'duration': 6.25, 'fwhm': 3.4781213790490995, 'rise_time': 3.125, 'decay_time': 3.125, 'auc': 1.5972467412686429}]</t>
         </is>
       </c>
       <c r="P411" t="n">
@@ -35935,15 +35935,15 @@
       </c>
       <c r="M413" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N413" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O413" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 2076, 'value': -0.5199736660171677, 'amplitude': 0.2161217496540886, 'start_idx': 2056, 'end_idx': 2085, 'duration': 6.041666666666667, 'fwhm': 2.2426515815645116, 'rise_time': 4.166666666666667, 'decay_time': 1.875, 'auc': 0.9623849087386463}]</t>
         </is>
       </c>
       <c r="P413" t="n">
@@ -36193,15 +36193,15 @@
       </c>
       <c r="M416" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N416" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O416" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 51, 'value': -0.3942468191444945, 'amplitude': 0.3639351654068768, 'start_idx': 43, 'end_idx': 66, 'duration': 4.791666666666667, 'fwhm': 2.5092952498553034, 'rise_time': 1.6666666666666667, 'decay_time': 3.125, 'auc': 1.5589751853423792}, {'index': 150, 'value': -0.4686994209735495, 'amplitude': 0.2894825635778218, 'start_idx': 135, 'end_idx': 168, 'duration': 6.875, 'fwhm': 3.7488370983930963, 'rise_time': 3.125, 'decay_time': 3.75, 'auc': 1.6745618965334383}, {'index': 186, 'value': -0.4687860786254596, 'amplitude': 0.2893959059259117, 'start_idx': 168, 'end_idx': 219, 'duration': 10.625, 'fwhm': 2.710682511272739, 'rise_time': 3.75, 'decay_time': 6.875, 'auc': 1.7914499527163381}]</t>
         </is>
       </c>
       <c r="P416" t="n">
@@ -36279,15 +36279,15 @@
       </c>
       <c r="M417" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N417" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O417" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 530, 'value': -0.4909710645306804, 'amplitude': 0.2672109200206909, 'start_idx': 506, 'end_idx': 536, 'duration': 6.25, 'fwhm': 7.822523740453894, 'rise_time': 5.0, 'decay_time': 1.25, 'auc': 1.4488422914627093}, {'index': 614, 'value': -0.6371833322418664, 'amplitude': 0.1209986523095049, 'start_idx': 589, 'end_idx': 623, 'duration': 7.083333333333334, 'fwhm': 6.425581059444573, 'rise_time': 5.208333333333334, 'decay_time': 1.875, 'auc': 0.6190820752852784}, {'index': 678, 'value': -0.6666183570529224, 'amplitude': 0.09156362749844893, 'start_idx': 659, 'end_idx': 693, 'duration': 7.083333333333334, 'fwhm': 3.9929300864211115, 'rise_time': 3.9583333333333335, 'decay_time': 3.125, 'auc': 0.4408321533381159}, {'index': 711, 'value': -0.6668557790394356, 'amplitude': 0.09132620551193571, 'start_idx': 693, 'end_idx': 728, 'duration': 7.291666666666667, 'fwhm': 2.563284404328054, 'rise_time': 3.75, 'decay_time': 3.541666666666667, 'auc': 0.3937589459272537}]</t>
         </is>
       </c>
       <c r="P417" t="n">
@@ -36537,15 +36537,15 @@
       </c>
       <c r="M420" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N420" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O420" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 1658, 'value': -0.4255634823441361, 'amplitude': 0.3326185022072352, 'start_idx': 1650, 'end_idx': 1666, 'duration': 3.3333333333333335, 'fwhm': 6.8967588391767745, 'rise_time': 1.6666666666666667, 'decay_time': 1.6666666666666667, 'auc': 1.0827085930161726}, {'index': 1703, 'value': -0.5310735279412117, 'amplitude': 0.22710845661015966, 'start_idx': 1683, 'end_idx': 1721, 'duration': 7.916666666666667, 'fwhm': 3.4211611882381496, 'rise_time': 4.166666666666667, 'decay_time': 3.75, 'auc': 1.5512092697260997}, {'index': 1756, 'value': -0.5604347266478241, 'amplitude': 0.1977472579035472, 'start_idx': 1747, 'end_idx': 1771, 'duration': 5.0, 'fwhm': 2.1934955556090094, 'rise_time': 1.875, 'decay_time': 3.125, 'auc': 0.8113112001964344}]</t>
         </is>
       </c>
       <c r="P420" t="n">
@@ -36795,15 +36795,15 @@
       </c>
       <c r="M423" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N423" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O423" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 2508, 'value': -0.40716441492291666, 'amplitude': 0.35101756962845465, 'start_idx': 2493, 'end_idx': 2540, 'duration': 9.791666666666668, 'fwhm': 3.362599548518972, 'rise_time': 3.125, 'decay_time': 6.666666666666667, 'auc': 2.664277842511717}]</t>
         </is>
       </c>
       <c r="P423" t="n">
@@ -38257,15 +38257,15 @@
       </c>
       <c r="M440" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N440" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O440" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 611, 'value': -0.6126258750369615, 'amplitude': 0.15370153178760682, 'start_idx': 590, 'end_idx': 628, 'duration': 7.916666666666667, 'fwhm': 4.336356925494561, 'rise_time': 4.375, 'decay_time': 3.541666666666667, 'auc': 0.8979191380521822}, {'index': 641, 'value': -0.6426364702095272, 'amplitude': 0.12369093661504116, 'start_idx': 628, 'end_idx': 658, 'duration': 6.25, 'fwhm': 3.074230063146217, 'rise_time': 2.7083333333333335, 'decay_time': 3.541666666666667, 'auc': 0.5961178035361033}, {'index': 713, 'value': -0.6801018360570376, 'amplitude': 0.08622557076753079, 'start_idx': 702, 'end_idx': 731, 'duration': 6.041666666666667, 'fwhm': 3.151796662926216, 'rise_time': 2.291666666666667, 'decay_time': 3.75, 'auc': 0.3446856470583507}, {'index': 751, 'value': -0.6726013580378383, 'amplitude': 0.09372604878673008, 'start_idx': 731, 'end_idx': 770, 'duration': 8.125, 'fwhm': 5.258760406962514, 'rise_time': 4.166666666666667, 'decay_time': 3.9583333333333335, 'auc': 0.5142638586809462}]</t>
         </is>
       </c>
       <c r="P440" t="n">
@@ -38343,15 +38343,15 @@
       </c>
       <c r="M441" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N441" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O441" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 1757, 'value': -0.4895144306418946, 'amplitude': 0.27681297618267375, 'start_idx': 1746, 'end_idx': 1774, 'duration': 5.833333333333334, 'fwhm': 2.6830326084520095, 'rise_time': 2.291666666666667, 'decay_time': 3.541666666666667, 'auc': 1.4060023770001058}]</t>
         </is>
       </c>
       <c r="P441" t="n">
@@ -39117,15 +39117,15 @@
       </c>
       <c r="M450" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N450" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O450" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 85, 'value': -0.4660436222229871, 'amplitude': 0.2795645225749731, 'start_idx': 81, 'end_idx': 90, 'duration': 1.875, 'fwhm': 8.497249613960667, 'rise_time': 0.8333333333333334, 'decay_time': 1.0416666666666667, 'auc': 0.5179003245174449}, {'index': 186, 'value': -0.46099241292303594, 'amplitude': 0.2846157318749243, 'start_idx': 176, 'end_idx': 215, 'duration': 8.125, 'fwhm': 3.4908853451906436, 'rise_time': 2.0833333333333335, 'decay_time': 6.041666666666667, 'auc': 1.3215022693842562}]</t>
         </is>
       </c>
       <c r="P450" t="n">
@@ -39289,15 +39289,15 @@
       </c>
       <c r="M452" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N452" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O452" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 1306, 'value': 0.025791660917414132, 'amplitude': 0.7713998057153744, 'start_idx': 1291, 'end_idx': 1334, 'duration': 8.958333333333334, 'fwhm': 3.1045334246468315, 'rise_time': 3.125, 'decay_time': 5.833333333333334, 'auc': 5.434926009742784}]</t>
         </is>
       </c>
       <c r="P452" t="n">
@@ -39547,15 +39547,15 @@
       </c>
       <c r="M455" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N455" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O455" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 1661, 'value': -0.29160436230818915, 'amplitude': 0.4540037824897711, 'start_idx': 1634, 'end_idx': 1683, 'duration': 10.208333333333334, 'fwhm': 5.8688914605387295, 'rise_time': 5.625, 'decay_time': 4.583333333333334, 'auc': 4.058274213216409}]</t>
         </is>
       </c>
       <c r="P455" t="n">
@@ -40665,15 +40665,15 @@
       </c>
       <c r="M468" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N468" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O468" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 1278, 'value': -0.2099357931259688, 'amplitude': 0.45355955952846827, 'start_idx': 1258, 'end_idx': 1292, 'duration': 7.083333333333334, 'fwhm': 2.076414312965369, 'rise_time': 4.166666666666667, 'decay_time': 2.916666666666667, 'auc': 2.6145579658272657}, {'index': 1371, 'value': -0.32373316837205635, 'amplitude': 0.3397621842823807, 'start_idx': 1351, 'end_idx': 1386, 'duration': 7.291666666666667, 'fwhm': 14.03532338034637, 'rise_time': 4.166666666666667, 'decay_time': 3.125, 'auc': 1.8293262070074203}]</t>
         </is>
       </c>
       <c r="P468" t="n">
@@ -41181,15 +41181,15 @@
       </c>
       <c r="M474" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N474" t="n">
-        <v>0</v>
+        <v>8</v>
       </c>
       <c r="O474" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 2318, 'value': -0.30608414391036903, 'amplitude': 0.357411208744068, 'start_idx': 2311, 'end_idx': 2324, 'duration': 2.7083333333333335, 'fwhm': 2.9950962586541627, 'rise_time': 1.4583333333333335, 'decay_time': 1.25, 'auc': 0.9116076988435611}, {'index': 2369, 'value': -0.3697344009437952, 'amplitude': 0.2937609517106418, 'start_idx': 2347, 'end_idx': 2394, 'duration': 9.791666666666668, 'fwhm': 3.1778866455403927, 'rise_time': 4.583333333333334, 'decay_time': 5.208333333333334, 'auc': 2.1207245446674214}, {'index': 2430, 'value': -0.4521178678163185, 'amplitude': 0.21137748483811852, 'start_idx': 2406, 'end_idx': 2434, 'duration': 5.833333333333334, 'fwhm': 10.728392301035115, 'rise_time': 5.0, 'decay_time': 0.8333333333333334, 'auc': 0.9101144770211633}, {'index': 2508, 'value': -0.4252116382627908, 'amplitude': 0.23828371439164625, 'start_idx': 2491, 'end_idx': 2532, 'duration': 8.541666666666668, 'fwhm': 4.816854618601951, 'rise_time': 3.541666666666667, 'decay_time': 5.0, 'auc': 1.5037797945337759}, {'index': 2590, 'value': -0.44616598939768004, 'amplitude': 0.217329363256757, 'start_idx': 2582, 'end_idx': 2595, 'duration': 2.7083333333333335, 'fwhm': 10.184531773839467, 'rise_time': 1.6666666666666667, 'decay_time': 1.0416666666666667, 'auc': 0.5651973243130002}, {'index': 2650, 'value': -0.43166040476542256, 'amplitude': 0.2318349478890145, 'start_idx': 2634, 'end_idx': 2682, 'duration': 10.0, 'fwhm': 7.227838201786767, 'rise_time': 3.3333333333333335, 'decay_time': 6.666666666666667, 'auc': 1.6027347172473623}, {'index': 2729, 'value': -0.48059883852733953, 'amplitude': 0.1828965141270975, 'start_idx': 2717, 'end_idx': 2748, 'duration': 6.458333333333334, 'fwhm': 6.363755821427901, 'rise_time': 2.5, 'decay_time': 3.9583333333333335, 'auc': 0.9248535262261653}, {'index': 2812, 'value': -0.44768335433477224, 'amplitude': 0.2158119983196648, 'start_idx': 2804, 'end_idx': 2829, 'duration': 5.208333333333334, 'fwhm': 8.95809126775788, 'rise_time': 1.6666666666666667, 'decay_time': 3.541666666666667, 'auc': 0.9421421815981754}]</t>
         </is>
       </c>
       <c r="P474" t="n">
@@ -41869,15 +41869,15 @@
       </c>
       <c r="M482" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N482" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O482" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 2369, 'value': -0.2568721944212775, 'amplitude': 0.47638132128313393, 'start_idx': 2359, 'end_idx': 2391, 'duration': 6.666666666666667, 'fwhm': 4.172403878375803, 'rise_time': 2.0833333333333335, 'decay_time': 4.583333333333334, 'auc': 2.454521079002591}, {'index': 2430, 'value': -0.45112075632339915, 'amplitude': 0.2821327593810123, 'start_idx': 2423, 'end_idx': 2434, 'duration': 2.291666666666667, 'fwhm': 6.30601136506139, 'rise_time': 1.4583333333333335, 'decay_time': 0.8333333333333334, 'auc': 0.6227993296443736}]</t>
         </is>
       </c>
       <c r="P482" t="n">
@@ -42127,15 +42127,15 @@
       </c>
       <c r="M485" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N485" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O485" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 1370, 'value': -0.6997155321428957, 'amplitude': 0.15907531599132652, 'start_idx': 1352, 'end_idx': 1386, 'duration': 7.083333333333334, 'fwhm': 3.363074446643187, 'rise_time': 3.75, 'decay_time': 3.3333333333333335, 'auc': 0.7732502763728167}]</t>
         </is>
       </c>
       <c r="P485" t="n">
@@ -43331,15 +43331,15 @@
       </c>
       <c r="M499" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N499" t="n">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c r="O499" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 539, 'value': -0.5615058741054267, 'amplitude': 0.17331603737380108, 'start_idx': 508, 'end_idx': 556, 'duration': 10.0, 'fwhm': 11.206936876747164, 'rise_time': 6.458333333333334, 'decay_time': 3.541666666666667, 'auc': 1.1324911325165203}, {'index': 675, 'value': -0.5581372885091197, 'amplitude': 0.17668462297010812, 'start_idx': 656, 'end_idx': 693, 'duration': 7.708333333333334, 'fwhm': 2.9833333399379334, 'rise_time': 3.9583333333333335, 'decay_time': 3.75, 'auc': 0.9617457948075652}, {'index': 751, 'value': -0.6591888515664139, 'amplitude': 0.07563305991281388, 'start_idx': 732, 'end_idx': 766, 'duration': 7.083333333333334, 'fwhm': 4.285789483555789, 'rise_time': 3.9583333333333335, 'decay_time': 3.125, 'auc': 0.3352816968856398}]</t>
         </is>
       </c>
       <c r="P499" t="n">
@@ -43761,15 +43761,15 @@
       </c>
       <c r="M504" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N504" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O504" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 1710, 'value': -0.4872362665855152, 'amplitude': 0.2475856448937126, 'start_idx': 1693, 'end_idx': 1721, 'duration': 5.833333333333334, 'fwhm': 4.724898031838431, 'rise_time': 3.541666666666667, 'decay_time': 2.291666666666667, 'auc': 1.3368431585691396}, {'index': 1757, 'value': -0.5148643065152666, 'amplitude': 0.21995760496396122, 'start_idx': 1744, 'end_idx': 1772, 'duration': 5.833333333333334, 'fwhm': 2.424713989252562, 'rise_time': 2.7083333333333335, 'decay_time': 3.125, 'auc': 0.9547049566238527}]</t>
         </is>
       </c>
       <c r="P504" t="n">
@@ -43810,40 +43810,40 @@
     </row>
     <row r="505">
       <c r="A505" t="n">
-        <v>1930</v>
+        <v>2027</v>
       </c>
       <c r="B505" t="n">
-        <v>1940</v>
+        <v>2034</v>
       </c>
       <c r="C505" t="n">
-        <v>1987</v>
+        <v>2056</v>
       </c>
       <c r="D505" t="n">
-        <v>0.6158221331716038</v>
+        <v>0.3870289150068482</v>
       </c>
       <c r="E505" t="n">
-        <v>-0.1189997783076239</v>
+        <v>-0.3477929964723796</v>
       </c>
       <c r="F505" t="n">
         <v>-0.7348219114792278</v>
       </c>
       <c r="G505" t="n">
-        <v>11.875</v>
+        <v>6.041666666666667</v>
       </c>
       <c r="H505" t="n">
-        <v>3.403378587670716</v>
+        <v>2.177950238118503</v>
       </c>
       <c r="I505" t="n">
-        <v>2.083333333333333</v>
+        <v>1.458333333333333</v>
       </c>
       <c r="J505" t="n">
-        <v>9.791666666666668</v>
+        <v>4.583333333333334</v>
       </c>
       <c r="K505" t="n">
-        <v>5.980749003653108</v>
+        <v>1.687081641414703</v>
       </c>
       <c r="L505" t="n">
-        <v>8.36899740535836</v>
+        <v>5.259707001450675</v>
       </c>
       <c r="M505" t="inlineStr">
         <is>
@@ -43859,16 +43859,16 @@
         </is>
       </c>
       <c r="P505" t="n">
-        <v>0.9187049232712777</v>
+        <v>0.9615250132601991</v>
       </c>
       <c r="Q505" t="n">
-        <v>0.2127659574468085</v>
+        <v>0.3181818181818182</v>
       </c>
       <c r="R505" t="n">
-        <v>0.1521487773522775</v>
+        <v>0.2550783953772598</v>
       </c>
       <c r="S505" t="n">
-        <v>0.9479176693607895</v>
+        <v>0.9231638916089872</v>
       </c>
       <c r="T505" t="inlineStr">
         <is>
@@ -43896,40 +43896,40 @@
     </row>
     <row r="506">
       <c r="A506" t="n">
-        <v>2027</v>
+        <v>2263</v>
       </c>
       <c r="B506" t="n">
-        <v>2034</v>
+        <v>2280</v>
       </c>
       <c r="C506" t="n">
-        <v>2056</v>
+        <v>2333</v>
       </c>
       <c r="D506" t="n">
-        <v>0.3870289150068482</v>
+        <v>0.5656291536540867</v>
       </c>
       <c r="E506" t="n">
-        <v>-0.3477929964723796</v>
+        <v>-0.1691927578251411</v>
       </c>
       <c r="F506" t="n">
         <v>-0.7348219114792278</v>
       </c>
       <c r="G506" t="n">
-        <v>6.041666666666667</v>
+        <v>14.58333333333333</v>
       </c>
       <c r="H506" t="n">
-        <v>2.177950238118503</v>
+        <v>9.56642533936872</v>
       </c>
       <c r="I506" t="n">
-        <v>1.458333333333333</v>
+        <v>3.541666666666667</v>
       </c>
       <c r="J506" t="n">
-        <v>4.583333333333334</v>
+        <v>11.04166666666667</v>
       </c>
       <c r="K506" t="n">
-        <v>1.687081641414703</v>
+        <v>7.264075347877292</v>
       </c>
       <c r="L506" t="n">
-        <v>5.259707001450675</v>
+        <v>7.686876882690736</v>
       </c>
       <c r="M506" t="inlineStr">
         <is>
@@ -43945,16 +43945,16 @@
         </is>
       </c>
       <c r="P506" t="n">
-        <v>0.9615250132601991</v>
+        <v>0.7508594756858853</v>
       </c>
       <c r="Q506" t="n">
-        <v>0.3181818181818182</v>
+        <v>0.3207547169811321</v>
       </c>
       <c r="R506" t="n">
-        <v>0.2550783953772598</v>
+        <v>0.03810310573702116</v>
       </c>
       <c r="S506" t="n">
-        <v>0.9231638916089872</v>
+        <v>0.8116884693677495</v>
       </c>
       <c r="T506" t="inlineStr">
         <is>
@@ -43982,40 +43982,40 @@
     </row>
     <row r="507">
       <c r="A507" t="n">
-        <v>2263</v>
+        <v>2333</v>
       </c>
       <c r="B507" t="n">
-        <v>2280</v>
+        <v>2349</v>
       </c>
       <c r="C507" t="n">
-        <v>2333</v>
+        <v>2416</v>
       </c>
       <c r="D507" t="n">
-        <v>0.5656291536540867</v>
+        <v>0.4819218655705347</v>
       </c>
       <c r="E507" t="n">
-        <v>-0.1691927578251411</v>
+        <v>-0.2529000459086931</v>
       </c>
       <c r="F507" t="n">
         <v>-0.7348219114792278</v>
       </c>
       <c r="G507" t="n">
-        <v>14.58333333333333</v>
+        <v>17.29166666666667</v>
       </c>
       <c r="H507" t="n">
-        <v>9.56642533936872</v>
+        <v>3.0273085687629</v>
       </c>
       <c r="I507" t="n">
-        <v>3.541666666666667</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="J507" t="n">
-        <v>11.04166666666667</v>
+        <v>13.95833333333333</v>
       </c>
       <c r="K507" t="n">
-        <v>7.264075347877292</v>
+        <v>5.6617047211955</v>
       </c>
       <c r="L507" t="n">
-        <v>7.686876882690736</v>
+        <v>6.549298288084396</v>
       </c>
       <c r="M507" t="inlineStr">
         <is>
@@ -44031,16 +44031,16 @@
         </is>
       </c>
       <c r="P507" t="n">
-        <v>0.7508594756858853</v>
+        <v>0.8706713200193651</v>
       </c>
       <c r="Q507" t="n">
-        <v>0.3207547169811321</v>
+        <v>0.2388059701492537</v>
       </c>
       <c r="R507" t="n">
-        <v>0.03810310573702116</v>
+        <v>0.2729183087247113</v>
       </c>
       <c r="S507" t="n">
-        <v>0.8116884693677495</v>
+        <v>0.9366379940379137</v>
       </c>
       <c r="T507" t="inlineStr">
         <is>
@@ -44068,40 +44068,40 @@
     </row>
     <row r="508">
       <c r="A508" t="n">
-        <v>2333</v>
+        <v>2416</v>
       </c>
       <c r="B508" t="n">
-        <v>2349</v>
+        <v>2436</v>
       </c>
       <c r="C508" t="n">
-        <v>2416</v>
+        <v>2483</v>
       </c>
       <c r="D508" t="n">
-        <v>0.4819218655705347</v>
+        <v>0.3137152584879427</v>
       </c>
       <c r="E508" t="n">
-        <v>-0.2529000459086931</v>
+        <v>-0.4211066529912851</v>
       </c>
       <c r="F508" t="n">
         <v>-0.7348219114792278</v>
       </c>
       <c r="G508" t="n">
-        <v>17.29166666666667</v>
+        <v>13.95833333333333</v>
       </c>
       <c r="H508" t="n">
-        <v>3.0273085687629</v>
+        <v>3.981408734308427</v>
       </c>
       <c r="I508" t="n">
-        <v>3.333333333333333</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="J508" t="n">
-        <v>13.95833333333333</v>
+        <v>9.791666666666668</v>
       </c>
       <c r="K508" t="n">
-        <v>5.6617047211955</v>
+        <v>3.234301606011378</v>
       </c>
       <c r="L508" t="n">
-        <v>6.549298288084396</v>
+        <v>4.263377431378076</v>
       </c>
       <c r="M508" t="inlineStr">
         <is>
@@ -44117,16 +44117,16 @@
         </is>
       </c>
       <c r="P508" t="n">
-        <v>0.8706713200193651</v>
+        <v>0.8854647794043773</v>
       </c>
       <c r="Q508" t="n">
-        <v>0.2388059701492537</v>
+        <v>0.425531914893617</v>
       </c>
       <c r="R508" t="n">
-        <v>0.2729183087247113</v>
+        <v>0.1405855425121888</v>
       </c>
       <c r="S508" t="n">
-        <v>0.9366379940379137</v>
+        <v>0.7559763000162718</v>
       </c>
       <c r="T508" t="inlineStr">
         <is>
@@ -44154,40 +44154,40 @@
     </row>
     <row r="509">
       <c r="A509" t="n">
-        <v>2416</v>
+        <v>2483</v>
       </c>
       <c r="B509" t="n">
-        <v>2436</v>
+        <v>2513</v>
       </c>
       <c r="C509" t="n">
-        <v>2483</v>
+        <v>2539</v>
       </c>
       <c r="D509" t="n">
-        <v>0.3137152584879427</v>
+        <v>0.3219361568183916</v>
       </c>
       <c r="E509" t="n">
-        <v>-0.4211066529912851</v>
+        <v>-0.4128857546608363</v>
       </c>
       <c r="F509" t="n">
         <v>-0.7348219114792278</v>
       </c>
       <c r="G509" t="n">
-        <v>13.95833333333333</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="H509" t="n">
-        <v>3.981408734308427</v>
+        <v>5.732021528550699</v>
       </c>
       <c r="I509" t="n">
-        <v>4.166666666666667</v>
+        <v>6.25</v>
       </c>
       <c r="J509" t="n">
-        <v>9.791666666666668</v>
+        <v>5.416666666666667</v>
       </c>
       <c r="K509" t="n">
-        <v>3.234301606011378</v>
+        <v>2.650258358544703</v>
       </c>
       <c r="L509" t="n">
-        <v>4.263377431378076</v>
+        <v>4.375099100820037</v>
       </c>
       <c r="M509" t="inlineStr">
         <is>
@@ -44203,16 +44203,16 @@
         </is>
       </c>
       <c r="P509" t="n">
-        <v>0.8854647794043773</v>
+        <v>0.735068637186056</v>
       </c>
       <c r="Q509" t="n">
-        <v>0.425531914893617</v>
+        <v>1.153846153846154</v>
       </c>
       <c r="R509" t="n">
-        <v>0.1405855425121888</v>
+        <v>0.127958147693328</v>
       </c>
       <c r="S509" t="n">
-        <v>0.7559763000162718</v>
+        <v>0.9694337386785415</v>
       </c>
       <c r="T509" t="inlineStr">
         <is>
@@ -44240,40 +44240,40 @@
     </row>
     <row r="510">
       <c r="A510" t="n">
-        <v>2483</v>
+        <v>2539</v>
       </c>
       <c r="B510" t="n">
-        <v>2513</v>
+        <v>2579</v>
       </c>
       <c r="C510" t="n">
-        <v>2539</v>
+        <v>2620</v>
       </c>
       <c r="D510" t="n">
-        <v>0.3219361568183916</v>
+        <v>0.2758803123698879</v>
       </c>
       <c r="E510" t="n">
-        <v>-0.4128857546608363</v>
+        <v>-0.4589415991093399</v>
       </c>
       <c r="F510" t="n">
         <v>-0.7348219114792278</v>
       </c>
       <c r="G510" t="n">
-        <v>11.66666666666667</v>
+        <v>16.875</v>
       </c>
       <c r="H510" t="n">
-        <v>5.732021528550699</v>
+        <v>11.48176006832216</v>
       </c>
       <c r="I510" t="n">
-        <v>6.25</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="J510" t="n">
-        <v>5.416666666666667</v>
+        <v>8.541666666666668</v>
       </c>
       <c r="K510" t="n">
-        <v>2.650258358544703</v>
+        <v>3.810693517272791</v>
       </c>
       <c r="L510" t="n">
-        <v>4.375099100820037</v>
+        <v>3.749202073205883</v>
       </c>
       <c r="M510" t="inlineStr">
         <is>
@@ -44289,16 +44289,16 @@
         </is>
       </c>
       <c r="P510" t="n">
-        <v>0.735068637186056</v>
+        <v>0.6348393411205194</v>
       </c>
       <c r="Q510" t="n">
-        <v>1.153846153846154</v>
+        <v>0.975609756097561</v>
       </c>
       <c r="R510" t="n">
-        <v>0.127958147693328</v>
+        <v>0.09854628572308495</v>
       </c>
       <c r="S510" t="n">
-        <v>0.9694337386785415</v>
+        <v>0.8099154182384274</v>
       </c>
       <c r="T510" t="inlineStr">
         <is>
@@ -44326,40 +44326,40 @@
     </row>
     <row r="511">
       <c r="A511" t="n">
-        <v>2539</v>
+        <v>2620</v>
       </c>
       <c r="B511" t="n">
-        <v>2579</v>
+        <v>2650</v>
       </c>
       <c r="C511" t="n">
-        <v>2620</v>
+        <v>2682</v>
       </c>
       <c r="D511" t="n">
-        <v>0.2758803123698879</v>
+        <v>0.2946005346859912</v>
       </c>
       <c r="E511" t="n">
-        <v>-0.4589415991093399</v>
+        <v>-0.4402213767932366</v>
       </c>
       <c r="F511" t="n">
         <v>-0.7348219114792278</v>
       </c>
       <c r="G511" t="n">
-        <v>16.875</v>
+        <v>12.91666666666667</v>
       </c>
       <c r="H511" t="n">
-        <v>11.48176006832216</v>
+        <v>7.255122528715958</v>
       </c>
       <c r="I511" t="n">
-        <v>8.333333333333334</v>
+        <v>6.25</v>
       </c>
       <c r="J511" t="n">
-        <v>8.541666666666668</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="K511" t="n">
-        <v>3.810693517272791</v>
+        <v>2.931529708083943</v>
       </c>
       <c r="L511" t="n">
-        <v>3.749202073205883</v>
+        <v>4.003609122826398</v>
       </c>
       <c r="M511" t="inlineStr">
         <is>
@@ -44375,16 +44375,16 @@
         </is>
       </c>
       <c r="P511" t="n">
-        <v>0.6348393411205194</v>
+        <v>0.6775219198820241</v>
       </c>
       <c r="Q511" t="n">
-        <v>0.975609756097561</v>
+        <v>0.9375</v>
       </c>
       <c r="R511" t="n">
-        <v>0.09854628572308495</v>
+        <v>0.07937934035283768</v>
       </c>
       <c r="S511" t="n">
-        <v>0.8099154182384274</v>
+        <v>0.8887445542037794</v>
       </c>
       <c r="T511" t="inlineStr">
         <is>
@@ -44412,40 +44412,40 @@
     </row>
     <row r="512">
       <c r="A512" t="n">
-        <v>2620</v>
+        <v>2749</v>
       </c>
       <c r="B512" t="n">
-        <v>2650</v>
+        <v>2852</v>
       </c>
       <c r="C512" t="n">
-        <v>2682</v>
+        <v>2998</v>
       </c>
       <c r="D512" t="n">
-        <v>0.2946005346859912</v>
+        <v>0.6731513692509432</v>
       </c>
       <c r="E512" t="n">
-        <v>-0.4402213767932366</v>
+        <v>-0.06167054222828462</v>
       </c>
       <c r="F512" t="n">
         <v>-0.7348219114792278</v>
       </c>
       <c r="G512" t="n">
-        <v>12.91666666666667</v>
+        <v>51.875</v>
       </c>
       <c r="H512" t="n">
-        <v>7.255122528715958</v>
+        <v>7.612617281896898</v>
       </c>
       <c r="I512" t="n">
-        <v>6.25</v>
+        <v>21.45833333333334</v>
       </c>
       <c r="J512" t="n">
-        <v>6.666666666666667</v>
+        <v>30.41666666666667</v>
       </c>
       <c r="K512" t="n">
-        <v>2.931529708083943</v>
+        <v>17.99207398740641</v>
       </c>
       <c r="L512" t="n">
-        <v>4.003609122826398</v>
+        <v>9.148099360541694</v>
       </c>
       <c r="M512" t="inlineStr">
         <is>
@@ -44461,16 +44461,16 @@
         </is>
       </c>
       <c r="P512" t="n">
-        <v>0.6775219198820241</v>
+        <v>0.59703417797283</v>
       </c>
       <c r="Q512" t="n">
-        <v>0.9375</v>
+        <v>0.7054794520547946</v>
       </c>
       <c r="R512" t="n">
-        <v>0.07937934035283768</v>
+        <v>0.3184002967241105</v>
       </c>
       <c r="S512" t="n">
-        <v>0.8887445542037794</v>
+        <v>0.8044261307149897</v>
       </c>
       <c r="T512" t="inlineStr">
         <is>
@@ -44498,40 +44498,40 @@
     </row>
     <row r="513">
       <c r="A513" t="n">
-        <v>2749</v>
+        <v>0</v>
       </c>
       <c r="B513" t="n">
-        <v>2852</v>
+        <v>13</v>
       </c>
       <c r="C513" t="n">
-        <v>2998</v>
+        <v>42</v>
       </c>
       <c r="D513" t="n">
-        <v>0.6731513692509432</v>
+        <v>0.3322844651929279</v>
       </c>
       <c r="E513" t="n">
-        <v>-0.06167054222828462</v>
+        <v>-0.3484916571179822</v>
       </c>
       <c r="F513" t="n">
-        <v>-0.7348219114792278</v>
+        <v>-0.6807761223109101</v>
       </c>
       <c r="G513" t="n">
-        <v>51.875</v>
+        <v>8.75</v>
       </c>
       <c r="H513" t="n">
-        <v>7.612617281896898</v>
+        <v>4.094860964539929</v>
       </c>
       <c r="I513" t="n">
-        <v>21.45833333333334</v>
+        <v>2.708333333333333</v>
       </c>
       <c r="J513" t="n">
-        <v>30.41666666666667</v>
+        <v>6.041666666666667</v>
       </c>
       <c r="K513" t="n">
-        <v>17.99207398740641</v>
+        <v>1.856486007026849</v>
       </c>
       <c r="L513" t="n">
-        <v>9.148099360541694</v>
+        <v>4.595317663803903</v>
       </c>
       <c r="M513" t="inlineStr">
         <is>
@@ -44547,20 +44547,20 @@
         </is>
       </c>
       <c r="P513" t="n">
-        <v>0.59703417797283</v>
+        <v>0.9161673308340348</v>
       </c>
       <c r="Q513" t="n">
-        <v>0.7054794520547946</v>
+        <v>0.4482758620689655</v>
       </c>
       <c r="R513" t="n">
-        <v>0.3184002967241105</v>
+        <v>0.3437136621078778</v>
       </c>
       <c r="S513" t="n">
-        <v>0.8044261307149897</v>
+        <v>0.9281966808633068</v>
       </c>
       <c r="T513" t="inlineStr">
         <is>
-          <t>n50</t>
+          <t>n51</t>
         </is>
       </c>
       <c r="U513" t="n">
@@ -44584,65 +44584,65 @@
     </row>
     <row r="514">
       <c r="A514" t="n">
-        <v>0</v>
+        <v>497</v>
       </c>
       <c r="B514" t="n">
-        <v>13</v>
+        <v>564</v>
       </c>
       <c r="C514" t="n">
-        <v>42</v>
+        <v>719</v>
       </c>
       <c r="D514" t="n">
-        <v>0.3322844651929279</v>
+        <v>0.3123644990464653</v>
       </c>
       <c r="E514" t="n">
-        <v>-0.3484916571179822</v>
+        <v>-0.3684116232644448</v>
       </c>
       <c r="F514" t="n">
         <v>-0.6807761223109101</v>
       </c>
       <c r="G514" t="n">
-        <v>8.75</v>
+        <v>46.25</v>
       </c>
       <c r="H514" t="n">
-        <v>4.094860964539929</v>
+        <v>14.86792022496605</v>
       </c>
       <c r="I514" t="n">
-        <v>2.708333333333333</v>
+        <v>13.95833333333333</v>
       </c>
       <c r="J514" t="n">
-        <v>6.041666666666667</v>
+        <v>32.29166666666667</v>
       </c>
       <c r="K514" t="n">
-        <v>1.856486007026849</v>
+        <v>6.394832817241106</v>
       </c>
       <c r="L514" t="n">
-        <v>4.595317663803903</v>
+        <v>4.31983511230374</v>
       </c>
       <c r="M514" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N514" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O514" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 608, 'value': -0.546764624572802, 'amplitude': 0.13401149773810817, 'start_idx': 589, 'end_idx': 611, 'duration': 4.583333333333334, 'fwhm': 5.90986890191933, 'rise_time': 3.9583333333333335, 'decay_time': 0.625, 'auc': 0.46723301555794583}]</t>
         </is>
       </c>
       <c r="P514" t="n">
-        <v>0.9161673308340348</v>
+        <v>0.7456504101368738</v>
       </c>
       <c r="Q514" t="n">
-        <v>0.4482758620689655</v>
+        <v>0.432258064516129</v>
       </c>
       <c r="R514" t="n">
-        <v>0.3437136621078778</v>
+        <v>0.6336979629598031</v>
       </c>
       <c r="S514" t="n">
-        <v>0.9281966808633068</v>
+        <v>0.6040460323663979</v>
       </c>
       <c r="T514" t="inlineStr">
         <is>
@@ -44670,40 +44670,40 @@
     </row>
     <row r="515">
       <c r="A515" t="n">
-        <v>497</v>
+        <v>2091</v>
       </c>
       <c r="B515" t="n">
-        <v>564</v>
+        <v>2115</v>
       </c>
       <c r="C515" t="n">
-        <v>719</v>
+        <v>2147</v>
       </c>
       <c r="D515" t="n">
-        <v>0.3123644990464653</v>
+        <v>0.4535878787706751</v>
       </c>
       <c r="E515" t="n">
-        <v>-0.3684116232644448</v>
+        <v>-0.227188243540235</v>
       </c>
       <c r="F515" t="n">
         <v>-0.6807761223109101</v>
       </c>
       <c r="G515" t="n">
-        <v>46.25</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="H515" t="n">
-        <v>14.86792022496605</v>
+        <v>7.582410598774819</v>
       </c>
       <c r="I515" t="n">
-        <v>13.95833333333333</v>
+        <v>5</v>
       </c>
       <c r="J515" t="n">
-        <v>32.29166666666667</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="K515" t="n">
-        <v>6.394832817241106</v>
+        <v>4.167318937033249</v>
       </c>
       <c r="L515" t="n">
-        <v>4.31983511230374</v>
+        <v>6.272879444400187</v>
       </c>
       <c r="M515" t="inlineStr">
         <is>
@@ -44719,16 +44719,16 @@
         </is>
       </c>
       <c r="P515" t="n">
-        <v>0.7456504101368738</v>
+        <v>0.8194373538043671</v>
       </c>
       <c r="Q515" t="n">
-        <v>0.432258064516129</v>
+        <v>0.75</v>
       </c>
       <c r="R515" t="n">
-        <v>0.6336979629598031</v>
+        <v>0.2618590038571329</v>
       </c>
       <c r="S515" t="n">
-        <v>0.6040460323663979</v>
+        <v>0.9632352029163253</v>
       </c>
       <c r="T515" t="inlineStr">
         <is>
@@ -44756,40 +44756,40 @@
     </row>
     <row r="516">
       <c r="A516" t="n">
-        <v>2091</v>
+        <v>2147</v>
       </c>
       <c r="B516" t="n">
-        <v>2115</v>
+        <v>2181</v>
       </c>
       <c r="C516" t="n">
-        <v>2147</v>
+        <v>2230</v>
       </c>
       <c r="D516" t="n">
-        <v>0.4535878787706751</v>
+        <v>0.4253759800985039</v>
       </c>
       <c r="E516" t="n">
-        <v>-0.227188243540235</v>
+        <v>-0.2554001422124063</v>
       </c>
       <c r="F516" t="n">
         <v>-0.6807761223109101</v>
       </c>
       <c r="G516" t="n">
-        <v>11.66666666666667</v>
+        <v>17.29166666666667</v>
       </c>
       <c r="H516" t="n">
-        <v>7.582410598774819</v>
+        <v>7.867136343039553</v>
       </c>
       <c r="I516" t="n">
-        <v>5</v>
+        <v>7.083333333333334</v>
       </c>
       <c r="J516" t="n">
-        <v>6.666666666666667</v>
+        <v>10.20833333333333</v>
       </c>
       <c r="K516" t="n">
-        <v>4.167318937033249</v>
+        <v>6.090981725032139</v>
       </c>
       <c r="L516" t="n">
-        <v>6.272879444400187</v>
+        <v>5.882723870252589</v>
       </c>
       <c r="M516" t="inlineStr">
         <is>
@@ -44805,16 +44805,16 @@
         </is>
       </c>
       <c r="P516" t="n">
-        <v>0.8194373538043671</v>
+        <v>0.603088902403297</v>
       </c>
       <c r="Q516" t="n">
-        <v>0.75</v>
+        <v>0.6938775510204082</v>
       </c>
       <c r="R516" t="n">
-        <v>0.2618590038571329</v>
+        <v>0.1301489791847439</v>
       </c>
       <c r="S516" t="n">
-        <v>0.9632352029163253</v>
+        <v>0.7281552793533004</v>
       </c>
       <c r="T516" t="inlineStr">
         <is>
@@ -44842,65 +44842,65 @@
     </row>
     <row r="517">
       <c r="A517" t="n">
-        <v>2147</v>
+        <v>2261</v>
       </c>
       <c r="B517" t="n">
-        <v>2181</v>
+        <v>2310</v>
       </c>
       <c r="C517" t="n">
-        <v>2230</v>
+        <v>2392</v>
       </c>
       <c r="D517" t="n">
-        <v>0.4253759800985039</v>
+        <v>0.4558304429134559</v>
       </c>
       <c r="E517" t="n">
-        <v>-0.2554001422124063</v>
+        <v>-0.2249456793974542</v>
       </c>
       <c r="F517" t="n">
         <v>-0.6807761223109101</v>
       </c>
       <c r="G517" t="n">
-        <v>17.29166666666667</v>
+        <v>27.29166666666667</v>
       </c>
       <c r="H517" t="n">
-        <v>7.867136343039553</v>
+        <v>28.26675268033929</v>
       </c>
       <c r="I517" t="n">
-        <v>7.083333333333334</v>
+        <v>10.20833333333333</v>
       </c>
       <c r="J517" t="n">
-        <v>10.20833333333333</v>
+        <v>17.08333333333334</v>
       </c>
       <c r="K517" t="n">
-        <v>6.090981725032139</v>
+        <v>9.829566123393146</v>
       </c>
       <c r="L517" t="n">
-        <v>5.882723870252589</v>
+        <v>6.303892915377684</v>
       </c>
       <c r="M517" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N517" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O517" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 2359, 'value': -0.2646550714570267, 'amplitude': 0.4161210508538834, 'start_idx': 2341, 'end_idx': 2363, 'duration': 4.583333333333334, 'fwhm': 4.516107295712857, 'rise_time': 3.75, 'decay_time': 0.8333333333333334, 'auc': 1.78522145719765}]</t>
         </is>
       </c>
       <c r="P517" t="n">
-        <v>0.603088902403297</v>
+        <v>0.5649239261542869</v>
       </c>
       <c r="Q517" t="n">
-        <v>0.6938775510204082</v>
+        <v>0.5975609756097561</v>
       </c>
       <c r="R517" t="n">
-        <v>0.1301489791847439</v>
+        <v>0.1450124502981192</v>
       </c>
       <c r="S517" t="n">
-        <v>0.7281552793533004</v>
+        <v>0.490075772591999</v>
       </c>
       <c r="T517" t="inlineStr">
         <is>
@@ -44928,65 +44928,65 @@
     </row>
     <row r="518">
       <c r="A518" t="n">
-        <v>2261</v>
+        <v>2535</v>
       </c>
       <c r="B518" t="n">
-        <v>2310</v>
+        <v>2596</v>
       </c>
       <c r="C518" t="n">
-        <v>2392</v>
+        <v>2687</v>
       </c>
       <c r="D518" t="n">
-        <v>0.4558304429134559</v>
+        <v>0.3223618044415694</v>
       </c>
       <c r="E518" t="n">
-        <v>-0.2249456793974542</v>
+        <v>-0.3584143178693407</v>
       </c>
       <c r="F518" t="n">
         <v>-0.6807761223109101</v>
       </c>
       <c r="G518" t="n">
-        <v>27.29166666666667</v>
+        <v>31.66666666666667</v>
       </c>
       <c r="H518" t="n">
-        <v>28.26675268033929</v>
+        <v>8.273160572113341</v>
       </c>
       <c r="I518" t="n">
-        <v>10.20833333333333</v>
+        <v>12.70833333333333</v>
       </c>
       <c r="J518" t="n">
-        <v>17.08333333333334</v>
+        <v>18.95833333333334</v>
       </c>
       <c r="K518" t="n">
-        <v>9.829566123393146</v>
+        <v>7.326786053732386</v>
       </c>
       <c r="L518" t="n">
-        <v>6.303892915377684</v>
+        <v>4.458092535941917</v>
       </c>
       <c r="M518" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N518" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O518" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 2552, 'value': -0.4265578676434473, 'amplitude': 0.25421825466746284, 'start_idx': 2536, 'end_idx': 2564, 'duration': 5.833333333333334, 'fwhm': 2.4346796946413938, 'rise_time': 3.3333333333333335, 'decay_time': 2.5, 'auc': 1.1888070791572798}, {'index': 2665, 'value': -0.4120514137560603, 'amplitude': 0.2687247085548498, 'start_idx': 2655, 'end_idx': 2686, 'duration': 6.458333333333334, 'fwhm': 4.500702659432629, 'rise_time': 2.0833333333333335, 'decay_time': 4.375, 'auc': 1.3705478253536434}]</t>
         </is>
       </c>
       <c r="P518" t="n">
-        <v>0.5649239261542869</v>
+        <v>0.5693448633881686</v>
       </c>
       <c r="Q518" t="n">
-        <v>0.5975609756097561</v>
+        <v>0.6703296703296703</v>
       </c>
       <c r="R518" t="n">
-        <v>0.1450124502981192</v>
+        <v>0.1243576804956857</v>
       </c>
       <c r="S518" t="n">
-        <v>0.490075772591999</v>
+        <v>0.3924735144642315</v>
       </c>
       <c r="T518" t="inlineStr">
         <is>
@@ -45014,40 +45014,40 @@
     </row>
     <row r="519">
       <c r="A519" t="n">
-        <v>2535</v>
+        <v>2687</v>
       </c>
       <c r="B519" t="n">
-        <v>2596</v>
+        <v>2724</v>
       </c>
       <c r="C519" t="n">
-        <v>2687</v>
+        <v>2755</v>
       </c>
       <c r="D519" t="n">
-        <v>0.3223618044415694</v>
+        <v>0.2977517288225186</v>
       </c>
       <c r="E519" t="n">
-        <v>-0.3584143178693407</v>
+        <v>-0.3830243934883915</v>
       </c>
       <c r="F519" t="n">
         <v>-0.6807761223109101</v>
       </c>
       <c r="G519" t="n">
-        <v>31.66666666666667</v>
+        <v>14.16666666666667</v>
       </c>
       <c r="H519" t="n">
-        <v>8.273160572113341</v>
+        <v>7.131677908963638</v>
       </c>
       <c r="I519" t="n">
-        <v>12.70833333333333</v>
+        <v>7.708333333333334</v>
       </c>
       <c r="J519" t="n">
-        <v>18.95833333333334</v>
+        <v>6.458333333333334</v>
       </c>
       <c r="K519" t="n">
-        <v>7.326786053732386</v>
+        <v>2.867049819978827</v>
       </c>
       <c r="L519" t="n">
-        <v>4.458092535941917</v>
+        <v>4.11774826154404</v>
       </c>
       <c r="M519" t="inlineStr">
         <is>
@@ -45063,16 +45063,16 @@
         </is>
       </c>
       <c r="P519" t="n">
-        <v>0.5693448633881686</v>
+        <v>0.6289021049296659</v>
       </c>
       <c r="Q519" t="n">
-        <v>0.6703296703296703</v>
+        <v>1.193548387096774</v>
       </c>
       <c r="R519" t="n">
-        <v>0.1243576804956857</v>
+        <v>0.09205112360817541</v>
       </c>
       <c r="S519" t="n">
-        <v>0.3924735144642315</v>
+        <v>0.9716361598525282</v>
       </c>
       <c r="T519" t="inlineStr">
         <is>
@@ -45100,40 +45100,40 @@
     </row>
     <row r="520">
       <c r="A520" t="n">
-        <v>2687</v>
+        <v>118</v>
       </c>
       <c r="B520" t="n">
-        <v>2724</v>
+        <v>186</v>
       </c>
       <c r="C520" t="n">
-        <v>2755</v>
+        <v>267</v>
       </c>
       <c r="D520" t="n">
-        <v>0.2977517288225186</v>
+        <v>0.6649598535912619</v>
       </c>
       <c r="E520" t="n">
-        <v>-0.3830243934883915</v>
+        <v>-0.1356609093912762</v>
       </c>
       <c r="F520" t="n">
-        <v>-0.6807761223109101</v>
+        <v>-0.800620762982538</v>
       </c>
       <c r="G520" t="n">
+        <v>31.04166666666667</v>
+      </c>
+      <c r="H520" t="n">
+        <v>13.86467834425793</v>
+      </c>
+      <c r="I520" t="n">
         <v>14.16666666666667</v>
       </c>
-      <c r="H520" t="n">
-        <v>7.131677908963638</v>
-      </c>
-      <c r="I520" t="n">
-        <v>7.708333333333334</v>
-      </c>
       <c r="J520" t="n">
-        <v>6.458333333333334</v>
+        <v>16.875</v>
       </c>
       <c r="K520" t="n">
-        <v>2.867049819978827</v>
+        <v>9.37505078269659</v>
       </c>
       <c r="L520" t="n">
-        <v>4.11774826154404</v>
+        <v>14.61915084002156</v>
       </c>
       <c r="M520" t="inlineStr">
         <is>
@@ -45149,20 +45149,20 @@
         </is>
       </c>
       <c r="P520" t="n">
-        <v>0.6289021049296659</v>
+        <v>0.7385004119647055</v>
       </c>
       <c r="Q520" t="n">
-        <v>1.193548387096774</v>
+        <v>0.8395061728395062</v>
       </c>
       <c r="R520" t="n">
-        <v>0.09205112360817541</v>
+        <v>0.5378262814675107</v>
       </c>
       <c r="S520" t="n">
-        <v>0.9716361598525282</v>
+        <v>0.9186630617269947</v>
       </c>
       <c r="T520" t="inlineStr">
         <is>
-          <t>n51</t>
+          <t>n52</t>
         </is>
       </c>
       <c r="U520" t="n">
@@ -45186,65 +45186,65 @@
     </row>
     <row r="521">
       <c r="A521" t="n">
-        <v>118</v>
+        <v>303</v>
       </c>
       <c r="B521" t="n">
-        <v>186</v>
+        <v>327</v>
       </c>
       <c r="C521" t="n">
-        <v>267</v>
+        <v>483</v>
       </c>
       <c r="D521" t="n">
-        <v>0.6649598535912619</v>
+        <v>0.2593106894368999</v>
       </c>
       <c r="E521" t="n">
-        <v>-0.1356609093912762</v>
+        <v>-0.5413100735456381</v>
       </c>
       <c r="F521" t="n">
         <v>-0.800620762982538</v>
       </c>
       <c r="G521" t="n">
-        <v>31.04166666666667</v>
+        <v>37.5</v>
       </c>
       <c r="H521" t="n">
-        <v>13.86467834425793</v>
+        <v>12.36829609761969</v>
       </c>
       <c r="I521" t="n">
-        <v>14.16666666666667</v>
+        <v>5</v>
       </c>
       <c r="J521" t="n">
-        <v>16.875</v>
+        <v>32.5</v>
       </c>
       <c r="K521" t="n">
-        <v>9.37505078269659</v>
+        <v>3.178336326318259</v>
       </c>
       <c r="L521" t="n">
-        <v>14.61915084002156</v>
+        <v>5.700948805908246</v>
       </c>
       <c r="M521" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N521" t="n">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c r="O521" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 364, 'value': -0.7018202643592326, 'amplitude': 0.09880049862330542, 'start_idx': 351, 'end_idx': 379, 'duration': 5.833333333333334, 'fwhm': 3.4325239152173146, 'rise_time': 2.7083333333333335, 'decay_time': 3.125, 'auc': 0.4402781947251167}, {'index': 395, 'value': -0.7021348513551141, 'amplitude': 0.09848591162742393, 'start_idx': 379, 'end_idx': 417, 'duration': 7.916666666666667, 'fwhm': 2.764102701943365, 'rise_time': 3.3333333333333335, 'decay_time': 4.583333333333334, 'auc': 0.5048208129157064}, {'index': 441, 'value': -0.7381455200407842, 'amplitude': 0.062475242941753883, 'start_idx': 429, 'end_idx': 457, 'duration': 5.833333333333334, 'fwhm': 2.7357660990984676, 'rise_time': 2.5, 'decay_time': 3.3333333333333335, 'auc': 0.22340187620200777}, {'index': 469, 'value': -0.7361283832692516, 'amplitude': 0.06449237971328647, 'start_idx': 457, 'end_idx': 482, 'duration': 5.208333333333334, 'fwhm': 2.7313652323401647, 'rise_time': 2.5, 'decay_time': 2.7083333333333335, 'auc': 0.20877158560554}]</t>
         </is>
       </c>
       <c r="P521" t="n">
-        <v>0.7385004119647055</v>
+        <v>0.8176962043260707</v>
       </c>
       <c r="Q521" t="n">
-        <v>0.8395061728395062</v>
+        <v>0.1538461538461539</v>
       </c>
       <c r="R521" t="n">
-        <v>0.5378262814675107</v>
+        <v>0.6723230537094391</v>
       </c>
       <c r="S521" t="n">
-        <v>0.9186630617269947</v>
+        <v>0.5013948270739006</v>
       </c>
       <c r="T521" t="inlineStr">
         <is>
@@ -45272,40 +45272,40 @@
     </row>
     <row r="522">
       <c r="A522" t="n">
-        <v>303</v>
+        <v>953</v>
       </c>
       <c r="B522" t="n">
-        <v>327</v>
+        <v>971</v>
       </c>
       <c r="C522" t="n">
-        <v>483</v>
+        <v>1002</v>
       </c>
       <c r="D522" t="n">
-        <v>0.2593106894368999</v>
+        <v>0.1636642750020362</v>
       </c>
       <c r="E522" t="n">
-        <v>-0.5413100735456381</v>
+        <v>-0.6369564879805019</v>
       </c>
       <c r="F522" t="n">
         <v>-0.800620762982538</v>
       </c>
       <c r="G522" t="n">
-        <v>37.5</v>
+        <v>10.20833333333333</v>
       </c>
       <c r="H522" t="n">
-        <v>12.36829609761969</v>
+        <v>4.278192538212646</v>
       </c>
       <c r="I522" t="n">
-        <v>5</v>
+        <v>3.75</v>
       </c>
       <c r="J522" t="n">
-        <v>32.5</v>
+        <v>6.458333333333334</v>
       </c>
       <c r="K522" t="n">
-        <v>3.178336326318259</v>
+        <v>1.087005057622171</v>
       </c>
       <c r="L522" t="n">
-        <v>5.700948805908246</v>
+        <v>3.598161167859381</v>
       </c>
       <c r="M522" t="inlineStr">
         <is>
@@ -45321,16 +45321,16 @@
         </is>
       </c>
       <c r="P522" t="n">
-        <v>0.8176962043260707</v>
+        <v>0.8825113058800111</v>
       </c>
       <c r="Q522" t="n">
-        <v>0.1538461538461539</v>
+        <v>0.5806451612903225</v>
       </c>
       <c r="R522" t="n">
-        <v>0.6723230537094391</v>
+        <v>0.2759676273912925</v>
       </c>
       <c r="S522" t="n">
-        <v>0.5013948270739006</v>
+        <v>0.9375777334992784</v>
       </c>
       <c r="T522" t="inlineStr">
         <is>
@@ -45358,40 +45358,40 @@
     </row>
     <row r="523">
       <c r="A523" t="n">
-        <v>953</v>
+        <v>1002</v>
       </c>
       <c r="B523" t="n">
-        <v>971</v>
+        <v>1026</v>
       </c>
       <c r="C523" t="n">
-        <v>1002</v>
+        <v>1046</v>
       </c>
       <c r="D523" t="n">
-        <v>0.1636642750020362</v>
+        <v>0.177180639925914</v>
       </c>
       <c r="E523" t="n">
-        <v>-0.6369564879805019</v>
+        <v>-0.623440123056624</v>
       </c>
       <c r="F523" t="n">
         <v>-0.800620762982538</v>
       </c>
       <c r="G523" t="n">
-        <v>10.20833333333333</v>
+        <v>9.166666666666668</v>
       </c>
       <c r="H523" t="n">
-        <v>4.278192538212646</v>
+        <v>13.32949982049151</v>
       </c>
       <c r="I523" t="n">
-        <v>3.75</v>
+        <v>5</v>
       </c>
       <c r="J523" t="n">
-        <v>6.458333333333334</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K523" t="n">
-        <v>1.087005057622171</v>
+        <v>1.136854964265016</v>
       </c>
       <c r="L523" t="n">
-        <v>3.598161167859381</v>
+        <v>3.895318622649737</v>
       </c>
       <c r="M523" t="inlineStr">
         <is>
@@ -45407,16 +45407,16 @@
         </is>
       </c>
       <c r="P523" t="n">
-        <v>0.8825113058800111</v>
+        <v>0.6405415253106141</v>
       </c>
       <c r="Q523" t="n">
-        <v>0.5806451612903225</v>
+        <v>1.2</v>
       </c>
       <c r="R523" t="n">
-        <v>0.2759676273912925</v>
+        <v>0.08792453583859813</v>
       </c>
       <c r="S523" t="n">
-        <v>0.9375777334992784</v>
+        <v>0.9550157174375256</v>
       </c>
       <c r="T523" t="inlineStr">
         <is>
@@ -45444,40 +45444,40 @@
     </row>
     <row r="524">
       <c r="A524" t="n">
-        <v>1002</v>
+        <v>1046</v>
       </c>
       <c r="B524" t="n">
-        <v>1026</v>
+        <v>1061</v>
       </c>
       <c r="C524" t="n">
-        <v>1046</v>
+        <v>1076</v>
       </c>
       <c r="D524" t="n">
-        <v>0.177180639925914</v>
+        <v>0.1613035856758894</v>
       </c>
       <c r="E524" t="n">
-        <v>-0.623440123056624</v>
+        <v>-0.6393171773066486</v>
       </c>
       <c r="F524" t="n">
         <v>-0.800620762982538</v>
       </c>
       <c r="G524" t="n">
-        <v>9.166666666666668</v>
+        <v>6.25</v>
       </c>
       <c r="H524" t="n">
-        <v>13.32949982049151</v>
+        <v>2.744420627399506</v>
       </c>
       <c r="I524" t="n">
-        <v>5</v>
+        <v>3.125</v>
       </c>
       <c r="J524" t="n">
-        <v>4.166666666666667</v>
+        <v>3.125</v>
       </c>
       <c r="K524" t="n">
-        <v>1.136854964265016</v>
+        <v>0.6264366157045251</v>
       </c>
       <c r="L524" t="n">
-        <v>3.895318622649737</v>
+        <v>3.5462613829942</v>
       </c>
       <c r="M524" t="inlineStr">
         <is>
@@ -45493,16 +45493,16 @@
         </is>
       </c>
       <c r="P524" t="n">
-        <v>0.6405415253106141</v>
+        <v>0.7127225466410267</v>
       </c>
       <c r="Q524" t="n">
-        <v>1.2</v>
+        <v>1</v>
       </c>
       <c r="R524" t="n">
-        <v>0.08792453583859813</v>
+        <v>0.2584983779470356</v>
       </c>
       <c r="S524" t="n">
-        <v>0.9550157174375256</v>
+        <v>0.6020291377715647</v>
       </c>
       <c r="T524" t="inlineStr">
         <is>
@@ -45530,40 +45530,40 @@
     </row>
     <row r="525">
       <c r="A525" t="n">
-        <v>1046</v>
+        <v>1580</v>
       </c>
       <c r="B525" t="n">
-        <v>1061</v>
+        <v>1600</v>
       </c>
       <c r="C525" t="n">
-        <v>1076</v>
+        <v>1622</v>
       </c>
       <c r="D525" t="n">
-        <v>0.1613035856758894</v>
+        <v>0.3621552466942733</v>
       </c>
       <c r="E525" t="n">
-        <v>-0.6393171773066486</v>
+        <v>-0.4384655162882647</v>
       </c>
       <c r="F525" t="n">
         <v>-0.800620762982538</v>
       </c>
       <c r="G525" t="n">
-        <v>6.25</v>
+        <v>8.75</v>
       </c>
       <c r="H525" t="n">
-        <v>2.744420627399506</v>
+        <v>3.348078418597188</v>
       </c>
       <c r="I525" t="n">
-        <v>3.125</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="J525" t="n">
-        <v>3.125</v>
+        <v>4.583333333333334</v>
       </c>
       <c r="K525" t="n">
-        <v>0.6264366157045251</v>
+        <v>2.33052976825565</v>
       </c>
       <c r="L525" t="n">
-        <v>3.5462613829942</v>
+        <v>7.961987705476082</v>
       </c>
       <c r="M525" t="inlineStr">
         <is>
@@ -45579,16 +45579,16 @@
         </is>
       </c>
       <c r="P525" t="n">
-        <v>0.7127225466410267</v>
+        <v>0.7155268823571905</v>
       </c>
       <c r="Q525" t="n">
-        <v>1</v>
+        <v>0.9090909090909091</v>
       </c>
       <c r="R525" t="n">
-        <v>0.2584983779470356</v>
+        <v>0.1162619160481142</v>
       </c>
       <c r="S525" t="n">
-        <v>0.6020291377715647</v>
+        <v>0.9194230312091447</v>
       </c>
       <c r="T525" t="inlineStr">
         <is>
@@ -45616,40 +45616,40 @@
     </row>
     <row r="526">
       <c r="A526" t="n">
-        <v>1580</v>
+        <v>1683</v>
       </c>
       <c r="B526" t="n">
-        <v>1600</v>
+        <v>1693</v>
       </c>
       <c r="C526" t="n">
-        <v>1622</v>
+        <v>1744</v>
       </c>
       <c r="D526" t="n">
-        <v>0.3621552466942733</v>
+        <v>0.3110327564473681</v>
       </c>
       <c r="E526" t="n">
-        <v>-0.4384655162882647</v>
+        <v>-0.48958800653517</v>
       </c>
       <c r="F526" t="n">
         <v>-0.800620762982538</v>
       </c>
       <c r="G526" t="n">
-        <v>8.75</v>
+        <v>12.70833333333333</v>
       </c>
       <c r="H526" t="n">
-        <v>3.348078418597188</v>
+        <v>3.401078167724449</v>
       </c>
       <c r="I526" t="n">
-        <v>4.166666666666667</v>
+        <v>2.083333333333333</v>
       </c>
       <c r="J526" t="n">
-        <v>4.583333333333334</v>
+        <v>10.625</v>
       </c>
       <c r="K526" t="n">
-        <v>2.33052976825565</v>
+        <v>2.572601318148309</v>
       </c>
       <c r="L526" t="n">
-        <v>7.961987705476082</v>
+        <v>6.838059107079175</v>
       </c>
       <c r="M526" t="inlineStr">
         <is>
@@ -45665,16 +45665,16 @@
         </is>
       </c>
       <c r="P526" t="n">
-        <v>0.7155268823571905</v>
+        <v>0.9059469821354478</v>
       </c>
       <c r="Q526" t="n">
-        <v>0.9090909090909091</v>
+        <v>0.196078431372549</v>
       </c>
       <c r="R526" t="n">
-        <v>0.1162619160481142</v>
+        <v>0.3227582470796194</v>
       </c>
       <c r="S526" t="n">
-        <v>0.9194230312091447</v>
+        <v>0.9520331188733822</v>
       </c>
       <c r="T526" t="inlineStr">
         <is>
@@ -45702,40 +45702,40 @@
     </row>
     <row r="527">
       <c r="A527" t="n">
-        <v>1683</v>
+        <v>1963</v>
       </c>
       <c r="B527" t="n">
-        <v>1693</v>
+        <v>2004</v>
       </c>
       <c r="C527" t="n">
-        <v>1744</v>
+        <v>2060</v>
       </c>
       <c r="D527" t="n">
-        <v>0.3110327564473681</v>
+        <v>0.7316857539468444</v>
       </c>
       <c r="E527" t="n">
-        <v>-0.48958800653517</v>
+        <v>-0.06893500903569358</v>
       </c>
       <c r="F527" t="n">
         <v>-0.800620762982538</v>
       </c>
       <c r="G527" t="n">
-        <v>12.70833333333333</v>
+        <v>20.20833333333334</v>
       </c>
       <c r="H527" t="n">
-        <v>3.401078167724449</v>
+        <v>7.418982291528144</v>
       </c>
       <c r="I527" t="n">
-        <v>2.083333333333333</v>
+        <v>8.541666666666668</v>
       </c>
       <c r="J527" t="n">
-        <v>10.625</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="K527" t="n">
-        <v>2.572601318148309</v>
+        <v>7.751819297125465</v>
       </c>
       <c r="L527" t="n">
-        <v>6.838059107079175</v>
+        <v>16.08612060814552</v>
       </c>
       <c r="M527" t="inlineStr">
         <is>
@@ -45751,16 +45751,16 @@
         </is>
       </c>
       <c r="P527" t="n">
-        <v>0.9059469821354478</v>
+        <v>0.7848781267161653</v>
       </c>
       <c r="Q527" t="n">
-        <v>0.196078431372549</v>
+        <v>0.7321428571428572</v>
       </c>
       <c r="R527" t="n">
-        <v>0.3227582470796194</v>
+        <v>0.1316704294485689</v>
       </c>
       <c r="S527" t="n">
-        <v>0.9520331188733822</v>
+        <v>0.8970626877660174</v>
       </c>
       <c r="T527" t="inlineStr">
         <is>
@@ -45788,65 +45788,65 @@
     </row>
     <row r="528">
       <c r="A528" t="n">
-        <v>1963</v>
+        <v>2060</v>
       </c>
       <c r="B528" t="n">
-        <v>2004</v>
+        <v>2106</v>
       </c>
       <c r="C528" t="n">
-        <v>2060</v>
+        <v>2153</v>
       </c>
       <c r="D528" t="n">
-        <v>0.7316857539468444</v>
+        <v>0.2657320585098296</v>
       </c>
       <c r="E528" t="n">
-        <v>-0.06893500903569358</v>
+        <v>-0.5348887044727084</v>
       </c>
       <c r="F528" t="n">
         <v>-0.800620762982538</v>
       </c>
       <c r="G528" t="n">
-        <v>20.20833333333334</v>
+        <v>19.375</v>
       </c>
       <c r="H528" t="n">
-        <v>7.418982291528144</v>
+        <v>8.432223461501186</v>
       </c>
       <c r="I528" t="n">
-        <v>8.541666666666668</v>
+        <v>9.583333333333334</v>
       </c>
       <c r="J528" t="n">
-        <v>11.66666666666667</v>
+        <v>9.791666666666668</v>
       </c>
       <c r="K528" t="n">
-        <v>7.751819297125465</v>
+        <v>3.364226539504758</v>
       </c>
       <c r="L528" t="n">
-        <v>16.08612060814552</v>
+        <v>5.842122686661522</v>
       </c>
       <c r="M528" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N528" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O528" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 2079, 'value': -0.6615506709299103, 'amplitude': 0.13907009205262777, 'start_idx': 2076, 'end_idx': 2088, 'duration': 2.5, 'fwhm': 2.6601981020464414, 'rise_time': 0.625, 'decay_time': 1.875, 'auc': 0.3061837016370837}, {'index': 2129, 'value': -0.5540132098388821, 'amplitude': 0.2466075531436559, 'start_idx': 2122, 'end_idx': 2152, 'duration': 6.25, 'fwhm': 3.142574921558416, 'rise_time': 1.4583333333333335, 'decay_time': 4.791666666666667, 'auc': 1.1809285012252606}]</t>
         </is>
       </c>
       <c r="P528" t="n">
-        <v>0.7848781267161653</v>
+        <v>0.6102390725713464</v>
       </c>
       <c r="Q528" t="n">
-        <v>0.7321428571428572</v>
+        <v>0.9787234042553191</v>
       </c>
       <c r="R528" t="n">
-        <v>0.1316704294485689</v>
+        <v>0.4069156817144862</v>
       </c>
       <c r="S528" t="n">
-        <v>0.8970626877660174</v>
+        <v>0.6936543270617908</v>
       </c>
       <c r="T528" t="inlineStr">
         <is>
@@ -45874,40 +45874,40 @@
     </row>
     <row r="529">
       <c r="A529" t="n">
-        <v>2060</v>
+        <v>2264</v>
       </c>
       <c r="B529" t="n">
-        <v>2106</v>
+        <v>2282</v>
       </c>
       <c r="C529" t="n">
-        <v>2153</v>
+        <v>2407</v>
       </c>
       <c r="D529" t="n">
-        <v>0.2657320585098296</v>
+        <v>0.6300088322957815</v>
       </c>
       <c r="E529" t="n">
-        <v>-0.5348887044727084</v>
+        <v>-0.1706119306867565</v>
       </c>
       <c r="F529" t="n">
         <v>-0.800620762982538</v>
       </c>
       <c r="G529" t="n">
-        <v>19.375</v>
+        <v>29.79166666666667</v>
       </c>
       <c r="H529" t="n">
-        <v>8.432223461501186</v>
+        <v>12.06459104884724</v>
       </c>
       <c r="I529" t="n">
-        <v>9.583333333333334</v>
+        <v>3.75</v>
       </c>
       <c r="J529" t="n">
-        <v>9.791666666666668</v>
+        <v>26.04166666666667</v>
       </c>
       <c r="K529" t="n">
-        <v>3.364226539504758</v>
+        <v>9.65932543469634</v>
       </c>
       <c r="L529" t="n">
-        <v>5.842122686661522</v>
+        <v>13.85075219223567</v>
       </c>
       <c r="M529" t="inlineStr">
         <is>
@@ -45923,16 +45923,16 @@
         </is>
       </c>
       <c r="P529" t="n">
-        <v>0.6102390725713464</v>
+        <v>0.8692003347648061</v>
       </c>
       <c r="Q529" t="n">
-        <v>0.9787234042553191</v>
+        <v>0.144</v>
       </c>
       <c r="R529" t="n">
-        <v>0.4069156817144862</v>
+        <v>0.3638267855769474</v>
       </c>
       <c r="S529" t="n">
-        <v>0.6936543270617908</v>
+        <v>0.8307359089304753</v>
       </c>
       <c r="T529" t="inlineStr">
         <is>
@@ -45960,40 +45960,40 @@
     </row>
     <row r="530">
       <c r="A530" t="n">
-        <v>2264</v>
+        <v>2407</v>
       </c>
       <c r="B530" t="n">
-        <v>2282</v>
+        <v>2449</v>
       </c>
       <c r="C530" t="n">
-        <v>2407</v>
+        <v>2488</v>
       </c>
       <c r="D530" t="n">
-        <v>0.6300088322957815</v>
+        <v>0.2593009833862764</v>
       </c>
       <c r="E530" t="n">
-        <v>-0.1706119306867565</v>
+        <v>-0.5413197795962617</v>
       </c>
       <c r="F530" t="n">
         <v>-0.800620762982538</v>
       </c>
       <c r="G530" t="n">
-        <v>29.79166666666667</v>
+        <v>16.875</v>
       </c>
       <c r="H530" t="n">
-        <v>12.06459104884724</v>
+        <v>7.370211997803912</v>
       </c>
       <c r="I530" t="n">
-        <v>3.75</v>
+        <v>8.75</v>
       </c>
       <c r="J530" t="n">
-        <v>26.04166666666667</v>
+        <v>8.125</v>
       </c>
       <c r="K530" t="n">
-        <v>9.65932543469634</v>
+        <v>3.15347136054027</v>
       </c>
       <c r="L530" t="n">
-        <v>13.85075219223567</v>
+        <v>5.700735418261819</v>
       </c>
       <c r="M530" t="inlineStr">
         <is>
@@ -46009,16 +46009,16 @@
         </is>
       </c>
       <c r="P530" t="n">
-        <v>0.8692003347648061</v>
+        <v>0.6662344625735682</v>
       </c>
       <c r="Q530" t="n">
-        <v>0.144</v>
+        <v>1.076923076923077</v>
       </c>
       <c r="R530" t="n">
-        <v>0.3638267855769474</v>
+        <v>0.2085615834939871</v>
       </c>
       <c r="S530" t="n">
-        <v>0.8307359089304753</v>
+        <v>0.9669450779188059</v>
       </c>
       <c r="T530" t="inlineStr">
         <is>
@@ -46046,40 +46046,40 @@
     </row>
     <row r="531">
       <c r="A531" t="n">
-        <v>2407</v>
+        <v>2488</v>
       </c>
       <c r="B531" t="n">
-        <v>2449</v>
+        <v>2512</v>
       </c>
       <c r="C531" t="n">
-        <v>2488</v>
+        <v>2539</v>
       </c>
       <c r="D531" t="n">
-        <v>0.2593009833862764</v>
+        <v>0.2381847849282218</v>
       </c>
       <c r="E531" t="n">
-        <v>-0.5413197795962617</v>
+        <v>-0.5624359780543162</v>
       </c>
       <c r="F531" t="n">
         <v>-0.800620762982538</v>
       </c>
       <c r="G531" t="n">
-        <v>16.875</v>
+        <v>10.625</v>
       </c>
       <c r="H531" t="n">
-        <v>7.370211997803912</v>
+        <v>4.450352264075548</v>
       </c>
       <c r="I531" t="n">
-        <v>8.75</v>
+        <v>5</v>
       </c>
       <c r="J531" t="n">
-        <v>8.125</v>
+        <v>5.625</v>
       </c>
       <c r="K531" t="n">
-        <v>3.15347136054027</v>
+        <v>1.707292415393781</v>
       </c>
       <c r="L531" t="n">
-        <v>5.700735418261819</v>
+        <v>5.236495526546667</v>
       </c>
       <c r="M531" t="inlineStr">
         <is>
@@ -46095,16 +46095,16 @@
         </is>
       </c>
       <c r="P531" t="n">
-        <v>0.6662344625735682</v>
+        <v>0.6732303715885801</v>
       </c>
       <c r="Q531" t="n">
-        <v>1.076923076923077</v>
+        <v>0.8888888888888888</v>
       </c>
       <c r="R531" t="n">
-        <v>0.2085615834939871</v>
+        <v>0.0706460290120737</v>
       </c>
       <c r="S531" t="n">
-        <v>0.9669450779188059</v>
+        <v>0.9843941100763237</v>
       </c>
       <c r="T531" t="inlineStr">
         <is>
@@ -46132,40 +46132,40 @@
     </row>
     <row r="532">
       <c r="A532" t="n">
-        <v>2488</v>
+        <v>2617</v>
       </c>
       <c r="B532" t="n">
-        <v>2512</v>
+        <v>2649</v>
       </c>
       <c r="C532" t="n">
-        <v>2539</v>
+        <v>2682</v>
       </c>
       <c r="D532" t="n">
-        <v>0.2381847849282218</v>
+        <v>0.181659841391084</v>
       </c>
       <c r="E532" t="n">
-        <v>-0.5624359780543162</v>
+        <v>-0.618960921591454</v>
       </c>
       <c r="F532" t="n">
         <v>-0.800620762982538</v>
       </c>
       <c r="G532" t="n">
-        <v>10.625</v>
+        <v>13.54166666666667</v>
       </c>
       <c r="H532" t="n">
-        <v>4.450352264075548</v>
+        <v>5.164131359415762</v>
       </c>
       <c r="I532" t="n">
-        <v>5</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="J532" t="n">
-        <v>5.625</v>
+        <v>6.875</v>
       </c>
       <c r="K532" t="n">
-        <v>1.707292415393781</v>
+        <v>1.649577542357405</v>
       </c>
       <c r="L532" t="n">
-        <v>5.236495526546667</v>
+        <v>3.993793923840501</v>
       </c>
       <c r="M532" t="inlineStr">
         <is>
@@ -46181,16 +46181,16 @@
         </is>
       </c>
       <c r="P532" t="n">
-        <v>0.6732303715885801</v>
+        <v>0.6609180710445235</v>
       </c>
       <c r="Q532" t="n">
-        <v>0.8888888888888888</v>
+        <v>0.9696969696969697</v>
       </c>
       <c r="R532" t="n">
-        <v>0.0706460290120737</v>
+        <v>0.1492293976077732</v>
       </c>
       <c r="S532" t="n">
-        <v>0.9843941100763237</v>
+        <v>0.917979112186831</v>
       </c>
       <c r="T532" t="inlineStr">
         <is>
@@ -46218,40 +46218,40 @@
     </row>
     <row r="533">
       <c r="A533" t="n">
-        <v>2617</v>
+        <v>2821</v>
       </c>
       <c r="B533" t="n">
-        <v>2649</v>
+        <v>2838</v>
       </c>
       <c r="C533" t="n">
-        <v>2682</v>
+        <v>2863</v>
       </c>
       <c r="D533" t="n">
-        <v>0.181659841391084</v>
+        <v>0.1944743867771306</v>
       </c>
       <c r="E533" t="n">
-        <v>-0.618960921591454</v>
+        <v>-0.6061463762054075</v>
       </c>
       <c r="F533" t="n">
         <v>-0.800620762982538</v>
       </c>
       <c r="G533" t="n">
-        <v>13.54166666666667</v>
+        <v>8.75</v>
       </c>
       <c r="H533" t="n">
-        <v>5.164131359415762</v>
+        <v>3.474840881241524</v>
       </c>
       <c r="I533" t="n">
-        <v>6.666666666666667</v>
+        <v>3.541666666666667</v>
       </c>
       <c r="J533" t="n">
-        <v>6.875</v>
+        <v>5.208333333333334</v>
       </c>
       <c r="K533" t="n">
-        <v>1.649577542357405</v>
+        <v>1.218932939568461</v>
       </c>
       <c r="L533" t="n">
-        <v>3.993793923840501</v>
+        <v>4.275521867163933</v>
       </c>
       <c r="M533" t="inlineStr">
         <is>
@@ -46267,16 +46267,16 @@
         </is>
       </c>
       <c r="P533" t="n">
-        <v>0.6609180710445235</v>
+        <v>0.7054156557365724</v>
       </c>
       <c r="Q533" t="n">
-        <v>0.9696969696969697</v>
+        <v>0.6799999999999999</v>
       </c>
       <c r="R533" t="n">
-        <v>0.1492293976077732</v>
+        <v>0.03534621764358201</v>
       </c>
       <c r="S533" t="n">
-        <v>0.917979112186831</v>
+        <v>0.9323009881674055</v>
       </c>
       <c r="T533" t="inlineStr">
         <is>
@@ -46304,40 +46304,40 @@
     </row>
     <row r="534">
       <c r="A534" t="n">
-        <v>2821</v>
+        <v>2912</v>
       </c>
       <c r="B534" t="n">
-        <v>2838</v>
+        <v>2952</v>
       </c>
       <c r="C534" t="n">
-        <v>2863</v>
+        <v>2998</v>
       </c>
       <c r="D534" t="n">
-        <v>0.1944743867771306</v>
+        <v>0.170855564308264</v>
       </c>
       <c r="E534" t="n">
-        <v>-0.6061463762054075</v>
+        <v>-0.6297651986742741</v>
       </c>
       <c r="F534" t="n">
         <v>-0.800620762982538</v>
       </c>
       <c r="G534" t="n">
-        <v>8.75</v>
+        <v>17.91666666666667</v>
       </c>
       <c r="H534" t="n">
-        <v>3.474840881241524</v>
+        <v>11.36012133208842</v>
       </c>
       <c r="I534" t="n">
-        <v>3.541666666666667</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="J534" t="n">
-        <v>5.208333333333334</v>
+        <v>9.583333333333334</v>
       </c>
       <c r="K534" t="n">
-        <v>1.218932939568461</v>
+        <v>2.51129202922227</v>
       </c>
       <c r="L534" t="n">
-        <v>4.275521867163933</v>
+        <v>3.756261754735713</v>
       </c>
       <c r="M534" t="inlineStr">
         <is>
@@ -46353,16 +46353,16 @@
         </is>
       </c>
       <c r="P534" t="n">
-        <v>0.7054156557365724</v>
+        <v>0.5186297522996035</v>
       </c>
       <c r="Q534" t="n">
-        <v>0.6799999999999999</v>
+        <v>0.8695652173913043</v>
       </c>
       <c r="R534" t="n">
-        <v>0.03534621764358201</v>
+        <v>0.1333707783504333</v>
       </c>
       <c r="S534" t="n">
-        <v>0.9323009881674055</v>
+        <v>0.3589114695753839</v>
       </c>
       <c r="T534" t="inlineStr">
         <is>
@@ -46390,40 +46390,40 @@
     </row>
     <row r="535">
       <c r="A535" t="n">
-        <v>2912</v>
+        <v>0</v>
       </c>
       <c r="B535" t="n">
-        <v>2952</v>
+        <v>21</v>
       </c>
       <c r="C535" t="n">
-        <v>2998</v>
+        <v>45</v>
       </c>
       <c r="D535" t="n">
-        <v>0.170855564308264</v>
+        <v>0.5357104075727093</v>
       </c>
       <c r="E535" t="n">
-        <v>-0.6297651986742741</v>
+        <v>-0.06371001736919116</v>
       </c>
       <c r="F535" t="n">
-        <v>-0.800620762982538</v>
+        <v>-0.5994204249419004</v>
       </c>
       <c r="G535" t="n">
-        <v>17.91666666666667</v>
+        <v>9.375</v>
       </c>
       <c r="H535" t="n">
-        <v>11.36012133208842</v>
+        <v>4.926050686610083</v>
       </c>
       <c r="I535" t="n">
-        <v>8.333333333333334</v>
+        <v>4.375</v>
       </c>
       <c r="J535" t="n">
-        <v>9.583333333333334</v>
+        <v>5</v>
       </c>
       <c r="K535" t="n">
-        <v>2.51129202922227</v>
+        <v>3.788742913213162</v>
       </c>
       <c r="L535" t="n">
-        <v>3.756261754735713</v>
+        <v>5.562740137012204</v>
       </c>
       <c r="M535" t="inlineStr">
         <is>
@@ -46439,20 +46439,20 @@
         </is>
       </c>
       <c r="P535" t="n">
-        <v>0.5186297522996035</v>
+        <v>0.7602701426850659</v>
       </c>
       <c r="Q535" t="n">
-        <v>0.8695652173913043</v>
+        <v>0.875</v>
       </c>
       <c r="R535" t="n">
-        <v>0.1333707783504333</v>
+        <v>0.2569885563721011</v>
       </c>
       <c r="S535" t="n">
-        <v>0.3589114695753839</v>
+        <v>0.9799347448748446</v>
       </c>
       <c r="T535" t="inlineStr">
         <is>
-          <t>n52</t>
+          <t>n53</t>
         </is>
       </c>
       <c r="U535" t="n">
@@ -46476,40 +46476,40 @@
     </row>
     <row r="536">
       <c r="A536" t="n">
-        <v>0</v>
+        <v>45</v>
       </c>
       <c r="B536" t="n">
-        <v>21</v>
+        <v>104</v>
       </c>
       <c r="C536" t="n">
-        <v>45</v>
+        <v>264</v>
       </c>
       <c r="D536" t="n">
-        <v>0.5357104075727093</v>
+        <v>1.022225267681624</v>
       </c>
       <c r="E536" t="n">
-        <v>-0.06371001736919116</v>
+        <v>0.4228048427397233</v>
       </c>
       <c r="F536" t="n">
         <v>-0.5994204249419004</v>
       </c>
       <c r="G536" t="n">
-        <v>9.375</v>
+        <v>45.625</v>
       </c>
       <c r="H536" t="n">
-        <v>4.926050686610083</v>
+        <v>29.03723455650205</v>
       </c>
       <c r="I536" t="n">
-        <v>4.375</v>
+        <v>12.29166666666667</v>
       </c>
       <c r="J536" t="n">
-        <v>5</v>
+        <v>33.33333333333334</v>
       </c>
       <c r="K536" t="n">
-        <v>3.788742913213162</v>
+        <v>28.10067532045264</v>
       </c>
       <c r="L536" t="n">
-        <v>5.562740137012204</v>
+        <v>10.61464075593646</v>
       </c>
       <c r="M536" t="inlineStr">
         <is>
@@ -46525,16 +46525,16 @@
         </is>
       </c>
       <c r="P536" t="n">
-        <v>0.7602701426850659</v>
+        <v>0.7698387322343438</v>
       </c>
       <c r="Q536" t="n">
-        <v>0.875</v>
+        <v>0.36875</v>
       </c>
       <c r="R536" t="n">
-        <v>0.2569885563721011</v>
+        <v>0.2798282113864605</v>
       </c>
       <c r="S536" t="n">
-        <v>0.9799347448748446</v>
+        <v>0.6441391450944365</v>
       </c>
       <c r="T536" t="inlineStr">
         <is>
@@ -46562,40 +46562,40 @@
     </row>
     <row r="537">
       <c r="A537" t="n">
-        <v>45</v>
+        <v>1840</v>
       </c>
       <c r="B537" t="n">
-        <v>104</v>
+        <v>1862</v>
       </c>
       <c r="C537" t="n">
-        <v>264</v>
+        <v>1923</v>
       </c>
       <c r="D537" t="n">
-        <v>1.022225267681624</v>
+        <v>0.5505351708000178</v>
       </c>
       <c r="E537" t="n">
-        <v>0.4228048427397233</v>
+        <v>-0.0488852541418826</v>
       </c>
       <c r="F537" t="n">
         <v>-0.5994204249419004</v>
       </c>
       <c r="G537" t="n">
-        <v>45.625</v>
+        <v>17.29166666666667</v>
       </c>
       <c r="H537" t="n">
-        <v>29.03723455650205</v>
+        <v>6.303726377270825</v>
       </c>
       <c r="I537" t="n">
-        <v>12.29166666666667</v>
+        <v>4.583333333333334</v>
       </c>
       <c r="J537" t="n">
-        <v>33.33333333333334</v>
+        <v>12.70833333333333</v>
       </c>
       <c r="K537" t="n">
-        <v>28.10067532045264</v>
+        <v>7.379002292736995</v>
       </c>
       <c r="L537" t="n">
-        <v>10.61464075593646</v>
+        <v>5.716678354863719</v>
       </c>
       <c r="M537" t="inlineStr">
         <is>
@@ -46611,16 +46611,16 @@
         </is>
       </c>
       <c r="P537" t="n">
-        <v>0.7698387322343438</v>
+        <v>0.8342296560626881</v>
       </c>
       <c r="Q537" t="n">
-        <v>0.36875</v>
+        <v>0.360655737704918</v>
       </c>
       <c r="R537" t="n">
-        <v>0.2798282113864605</v>
+        <v>0.1604673633732243</v>
       </c>
       <c r="S537" t="n">
-        <v>0.6441391450944365</v>
+        <v>0.5112207517059801</v>
       </c>
       <c r="T537" t="inlineStr">
         <is>
@@ -46648,65 +46648,65 @@
     </row>
     <row r="538">
       <c r="A538" t="n">
-        <v>1840</v>
+        <v>2148</v>
       </c>
       <c r="B538" t="n">
-        <v>1862</v>
+        <v>2165</v>
       </c>
       <c r="C538" t="n">
-        <v>1923</v>
+        <v>2234</v>
       </c>
       <c r="D538" t="n">
-        <v>0.5505351708000178</v>
+        <v>0.4739939766353016</v>
       </c>
       <c r="E538" t="n">
-        <v>-0.0488852541418826</v>
+        <v>-0.1254264483065988</v>
       </c>
       <c r="F538" t="n">
         <v>-0.5994204249419004</v>
       </c>
       <c r="G538" t="n">
-        <v>17.29166666666667</v>
+        <v>17.91666666666667</v>
       </c>
       <c r="H538" t="n">
-        <v>6.303726377270825</v>
+        <v>6.808355405118315</v>
       </c>
       <c r="I538" t="n">
-        <v>4.583333333333334</v>
+        <v>3.541666666666667</v>
       </c>
       <c r="J538" t="n">
-        <v>12.70833333333333</v>
+        <v>14.375</v>
       </c>
       <c r="K538" t="n">
-        <v>7.379002292736995</v>
+        <v>7.223649664251652</v>
       </c>
       <c r="L538" t="n">
-        <v>5.716678354863719</v>
+        <v>4.921885558427106</v>
       </c>
       <c r="M538" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N538" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O538" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 2218, 'value': -0.15189075866294327, 'amplitude': 0.44752966627895713, 'start_idx': 2203, 'end_idx': 2233, 'duration': 6.25, 'fwhm': 3.294911655598109, 'rise_time': 3.125, 'decay_time': 3.125, 'auc': 2.4655937132859873}]</t>
         </is>
       </c>
       <c r="P538" t="n">
-        <v>0.8342296560626881</v>
+        <v>0.7048544284868192</v>
       </c>
       <c r="Q538" t="n">
-        <v>0.360655737704918</v>
+        <v>0.2463768115942029</v>
       </c>
       <c r="R538" t="n">
-        <v>0.1604673633732243</v>
+        <v>0.09445474767318951</v>
       </c>
       <c r="S538" t="n">
-        <v>0.5112207517059801</v>
+        <v>0.2401176813913811</v>
       </c>
       <c r="T538" t="inlineStr">
         <is>
@@ -46734,40 +46734,40 @@
     </row>
     <row r="539">
       <c r="A539" t="n">
-        <v>2148</v>
+        <v>2234</v>
       </c>
       <c r="B539" t="n">
-        <v>2165</v>
+        <v>2280</v>
       </c>
       <c r="C539" t="n">
-        <v>2234</v>
+        <v>2340</v>
       </c>
       <c r="D539" t="n">
-        <v>0.4739939766353016</v>
+        <v>0.7870357896900138</v>
       </c>
       <c r="E539" t="n">
-        <v>-0.1254264483065988</v>
+        <v>0.1876153647481134</v>
       </c>
       <c r="F539" t="n">
         <v>-0.5994204249419004</v>
       </c>
       <c r="G539" t="n">
-        <v>17.91666666666667</v>
+        <v>22.08333333333334</v>
       </c>
       <c r="H539" t="n">
-        <v>6.808355405118315</v>
+        <v>20.02411805889419</v>
       </c>
       <c r="I539" t="n">
-        <v>3.541666666666667</v>
+        <v>9.583333333333334</v>
       </c>
       <c r="J539" t="n">
-        <v>14.375</v>
+        <v>12.5</v>
       </c>
       <c r="K539" t="n">
-        <v>7.223649664251652</v>
+        <v>13.90089160210619</v>
       </c>
       <c r="L539" t="n">
-        <v>4.921885558427106</v>
+        <v>8.172466905040521</v>
       </c>
       <c r="M539" t="inlineStr">
         <is>
@@ -46783,16 +46783,16 @@
         </is>
       </c>
       <c r="P539" t="n">
-        <v>0.7048544284868192</v>
+        <v>0.6079830902972041</v>
       </c>
       <c r="Q539" t="n">
-        <v>0.2463768115942029</v>
+        <v>0.7666666666666667</v>
       </c>
       <c r="R539" t="n">
-        <v>0.09445474767318951</v>
+        <v>0.134608582167421</v>
       </c>
       <c r="S539" t="n">
-        <v>0.2401176813913811</v>
+        <v>0.6392770146903566</v>
       </c>
       <c r="T539" t="inlineStr">
         <is>
@@ -46820,40 +46820,40 @@
     </row>
     <row r="540">
       <c r="A540" t="n">
-        <v>2234</v>
+        <v>2340</v>
       </c>
       <c r="B540" t="n">
-        <v>2280</v>
+        <v>2351</v>
       </c>
       <c r="C540" t="n">
-        <v>2340</v>
+        <v>2405</v>
       </c>
       <c r="D540" t="n">
-        <v>0.7870357896900138</v>
+        <v>0.6266114054726263</v>
       </c>
       <c r="E540" t="n">
-        <v>0.1876153647481134</v>
+        <v>0.02719098053072591</v>
       </c>
       <c r="F540" t="n">
         <v>-0.5994204249419004</v>
       </c>
       <c r="G540" t="n">
-        <v>22.08333333333334</v>
+        <v>13.54166666666667</v>
       </c>
       <c r="H540" t="n">
-        <v>20.02411805889419</v>
+        <v>5.875316023364785</v>
       </c>
       <c r="I540" t="n">
-        <v>9.583333333333334</v>
+        <v>2.291666666666667</v>
       </c>
       <c r="J540" t="n">
-        <v>12.5</v>
+        <v>11.25</v>
       </c>
       <c r="K540" t="n">
-        <v>13.90089160210619</v>
+        <v>6.891842455884057</v>
       </c>
       <c r="L540" t="n">
-        <v>8.172466905040521</v>
+        <v>6.506643078535139</v>
       </c>
       <c r="M540" t="inlineStr">
         <is>
@@ -46869,16 +46869,16 @@
         </is>
       </c>
       <c r="P540" t="n">
-        <v>0.6079830902972041</v>
+        <v>0.828083923874945</v>
       </c>
       <c r="Q540" t="n">
-        <v>0.7666666666666667</v>
+        <v>0.2037037037037037</v>
       </c>
       <c r="R540" t="n">
-        <v>0.134608582167421</v>
+        <v>0.09810176828307079</v>
       </c>
       <c r="S540" t="n">
-        <v>0.6392770146903566</v>
+        <v>0.8951015686699547</v>
       </c>
       <c r="T540" t="inlineStr">
         <is>
@@ -46906,40 +46906,40 @@
     </row>
     <row r="541">
       <c r="A541" t="n">
-        <v>2340</v>
+        <v>2405</v>
       </c>
       <c r="B541" t="n">
-        <v>2351</v>
+        <v>2425</v>
       </c>
       <c r="C541" t="n">
-        <v>2405</v>
+        <v>2482</v>
       </c>
       <c r="D541" t="n">
-        <v>0.6266114054726263</v>
+        <v>0.4924676409654749</v>
       </c>
       <c r="E541" t="n">
-        <v>0.02719098053072591</v>
+        <v>-0.1069527839764255</v>
       </c>
       <c r="F541" t="n">
         <v>-0.5994204249419004</v>
       </c>
       <c r="G541" t="n">
-        <v>13.54166666666667</v>
+        <v>16.04166666666667</v>
       </c>
       <c r="H541" t="n">
-        <v>5.875316023364785</v>
+        <v>3.487459673684346</v>
       </c>
       <c r="I541" t="n">
-        <v>2.291666666666667</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="J541" t="n">
-        <v>11.25</v>
+        <v>11.875</v>
       </c>
       <c r="K541" t="n">
-        <v>6.891842455884057</v>
+        <v>5.432135759019745</v>
       </c>
       <c r="L541" t="n">
-        <v>6.506643078535139</v>
+        <v>5.11371344266174</v>
       </c>
       <c r="M541" t="inlineStr">
         <is>
@@ -46955,16 +46955,16 @@
         </is>
       </c>
       <c r="P541" t="n">
-        <v>0.828083923874945</v>
+        <v>0.8711166223951869</v>
       </c>
       <c r="Q541" t="n">
-        <v>0.2037037037037037</v>
+        <v>0.3508771929824562</v>
       </c>
       <c r="R541" t="n">
-        <v>0.09810176828307079</v>
+        <v>0.1482614095666329</v>
       </c>
       <c r="S541" t="n">
-        <v>0.8951015686699547</v>
+        <v>0.7620105095475886</v>
       </c>
       <c r="T541" t="inlineStr">
         <is>
@@ -46992,65 +46992,65 @@
     </row>
     <row r="542">
       <c r="A542" t="n">
-        <v>2405</v>
+        <v>2534</v>
       </c>
       <c r="B542" t="n">
-        <v>2425</v>
+        <v>2563</v>
       </c>
       <c r="C542" t="n">
-        <v>2482</v>
+        <v>2624</v>
       </c>
       <c r="D542" t="n">
-        <v>0.4924676409654749</v>
+        <v>0.3815954081131991</v>
       </c>
       <c r="E542" t="n">
-        <v>-0.1069527839764255</v>
+        <v>-0.2178250168287012</v>
       </c>
       <c r="F542" t="n">
         <v>-0.5994204249419004</v>
       </c>
       <c r="G542" t="n">
-        <v>16.04166666666667</v>
+        <v>18.75</v>
       </c>
       <c r="H542" t="n">
-        <v>3.487459673684346</v>
+        <v>4.585267690877023</v>
       </c>
       <c r="I542" t="n">
-        <v>4.166666666666667</v>
+        <v>6.041666666666667</v>
       </c>
       <c r="J542" t="n">
-        <v>11.875</v>
+        <v>12.70833333333333</v>
       </c>
       <c r="K542" t="n">
-        <v>5.432135759019745</v>
+        <v>5.441658758563909</v>
       </c>
       <c r="L542" t="n">
-        <v>5.11371344266174</v>
+        <v>3.962432058075593</v>
       </c>
       <c r="M542" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N542" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O542" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 2601, 'value': -0.24148943094768036, 'amplitude': 0.35793099399422, 'start_idx': 2597, 'end_idx': 2623, 'duration': 5.416666666666667, 'fwhm': 3.4671267831708974, 'rise_time': 0.8333333333333334, 'decay_time': 4.583333333333334, 'auc': 1.4111372392400907}]</t>
         </is>
       </c>
       <c r="P542" t="n">
-        <v>0.8711166223951869</v>
+        <v>0.7829452882097613</v>
       </c>
       <c r="Q542" t="n">
-        <v>0.3508771929824562</v>
+        <v>0.4754098360655738</v>
       </c>
       <c r="R542" t="n">
-        <v>0.1482614095666329</v>
+        <v>0.1498451514809415</v>
       </c>
       <c r="S542" t="n">
-        <v>0.7620105095475886</v>
+        <v>0.5495451698178304</v>
       </c>
       <c r="T542" t="inlineStr">
         <is>
@@ -47078,40 +47078,40 @@
     </row>
     <row r="543">
       <c r="A543" t="n">
-        <v>2534</v>
+        <v>2624</v>
       </c>
       <c r="B543" t="n">
-        <v>2563</v>
+        <v>2645</v>
       </c>
       <c r="C543" t="n">
-        <v>2624</v>
+        <v>2680</v>
       </c>
       <c r="D543" t="n">
-        <v>0.3815954081131991</v>
+        <v>0.4132900067913488</v>
       </c>
       <c r="E543" t="n">
-        <v>-0.2178250168287012</v>
+        <v>-0.1861304181505516</v>
       </c>
       <c r="F543" t="n">
         <v>-0.5994204249419004</v>
       </c>
       <c r="G543" t="n">
-        <v>18.75</v>
+        <v>11.66666666666667</v>
       </c>
       <c r="H543" t="n">
-        <v>4.585267690877023</v>
+        <v>7.031113105268598</v>
       </c>
       <c r="I543" t="n">
-        <v>6.041666666666667</v>
+        <v>4.375</v>
       </c>
       <c r="J543" t="n">
-        <v>12.70833333333333</v>
+        <v>7.291666666666667</v>
       </c>
       <c r="K543" t="n">
-        <v>5.441658758563909</v>
+        <v>3.645108954972718</v>
       </c>
       <c r="L543" t="n">
-        <v>3.962432058075593</v>
+        <v>4.291544230811396</v>
       </c>
       <c r="M543" t="inlineStr">
         <is>
@@ -47127,16 +47127,16 @@
         </is>
       </c>
       <c r="P543" t="n">
-        <v>0.7829452882097613</v>
+        <v>0.830205576912744</v>
       </c>
       <c r="Q543" t="n">
-        <v>0.4754098360655738</v>
+        <v>0.6</v>
       </c>
       <c r="R543" t="n">
-        <v>0.1498451514809415</v>
+        <v>0.1833136033613698</v>
       </c>
       <c r="S543" t="n">
-        <v>0.5495451698178304</v>
+        <v>0.8218889236299444</v>
       </c>
       <c r="T543" t="inlineStr">
         <is>
@@ -47164,65 +47164,65 @@
     </row>
     <row r="544">
       <c r="A544" t="n">
-        <v>2624</v>
+        <v>2680</v>
       </c>
       <c r="B544" t="n">
-        <v>2645</v>
+        <v>2699</v>
       </c>
       <c r="C544" t="n">
-        <v>2680</v>
+        <v>2753</v>
       </c>
       <c r="D544" t="n">
-        <v>0.4132900067913488</v>
+        <v>0.4543834205374392</v>
       </c>
       <c r="E544" t="n">
-        <v>-0.1861304181505516</v>
+        <v>-0.1450370044044612</v>
       </c>
       <c r="F544" t="n">
         <v>-0.5994204249419004</v>
       </c>
       <c r="G544" t="n">
-        <v>11.66666666666667</v>
+        <v>15.20833333333333</v>
       </c>
       <c r="H544" t="n">
-        <v>7.031113105268598</v>
+        <v>4.201754344883852</v>
       </c>
       <c r="I544" t="n">
-        <v>4.375</v>
+        <v>3.958333333333333</v>
       </c>
       <c r="J544" t="n">
-        <v>7.291666666666667</v>
+        <v>11.25</v>
       </c>
       <c r="K544" t="n">
-        <v>3.645108954972718</v>
+        <v>5.755116894125415</v>
       </c>
       <c r="L544" t="n">
-        <v>4.291544230811396</v>
+        <v>4.718252352925303</v>
       </c>
       <c r="M544" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N544" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O544" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 2730, 'value': -0.17195762349954172, 'amplitude': 0.4274628014423587, 'start_idx': 2725, 'end_idx': 2743, 'duration': 3.75, 'fwhm': 3.4744081145205996, 'rise_time': 1.0416666666666667, 'decay_time': 2.7083333333333335, 'auc': 1.5084410736558458}]</t>
         </is>
       </c>
       <c r="P544" t="n">
-        <v>0.830205576912744</v>
+        <v>0.8320304840049967</v>
       </c>
       <c r="Q544" t="n">
-        <v>0.6</v>
+        <v>0.3518518518518519</v>
       </c>
       <c r="R544" t="n">
-        <v>0.1833136033613698</v>
+        <v>0.2342923071903956</v>
       </c>
       <c r="S544" t="n">
-        <v>0.8218889236299444</v>
+        <v>0.3402548503825455</v>
       </c>
       <c r="T544" t="inlineStr">
         <is>
@@ -47250,65 +47250,65 @@
     </row>
     <row r="545">
       <c r="A545" t="n">
-        <v>2680</v>
+        <v>2913</v>
       </c>
       <c r="B545" t="n">
-        <v>2699</v>
+        <v>2933</v>
       </c>
       <c r="C545" t="n">
-        <v>2753</v>
+        <v>2998</v>
       </c>
       <c r="D545" t="n">
-        <v>0.4543834205374392</v>
+        <v>0.4234844961523819</v>
       </c>
       <c r="E545" t="n">
-        <v>-0.1450370044044612</v>
+        <v>-0.1759359287895185</v>
       </c>
       <c r="F545" t="n">
         <v>-0.5994204249419004</v>
       </c>
       <c r="G545" t="n">
-        <v>15.20833333333333</v>
+        <v>17.70833333333334</v>
       </c>
       <c r="H545" t="n">
-        <v>4.201754344883852</v>
+        <v>7.580939919518528</v>
       </c>
       <c r="I545" t="n">
-        <v>3.958333333333333</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="J545" t="n">
-        <v>11.25</v>
+        <v>13.54166666666667</v>
       </c>
       <c r="K545" t="n">
-        <v>5.755116894125415</v>
+        <v>6.313249992442276</v>
       </c>
       <c r="L545" t="n">
-        <v>4.718252352925303</v>
+        <v>4.39740234807649</v>
       </c>
       <c r="M545" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N545" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O545" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 2976, 'value': -0.19841934333622807, 'amplitude': 0.4010010816056723, 'start_idx': 2966, 'end_idx': 2990, 'duration': 5.0, 'fwhm': 2.4457043481234564, 'rise_time': 2.0833333333333335, 'decay_time': 2.916666666666667, 'auc': 1.720490265478518}]</t>
         </is>
       </c>
       <c r="P545" t="n">
-        <v>0.8320304840049967</v>
+        <v>0.7304083176128736</v>
       </c>
       <c r="Q545" t="n">
-        <v>0.3518518518518519</v>
+        <v>0.3076923076923077</v>
       </c>
       <c r="R545" t="n">
-        <v>0.2342923071903956</v>
+        <v>0.1058682332148057</v>
       </c>
       <c r="S545" t="n">
-        <v>0.3402548503825455</v>
+        <v>0.3374385293817083</v>
       </c>
       <c r="T545" t="inlineStr">
         <is>
@@ -47336,40 +47336,40 @@
     </row>
     <row r="546">
       <c r="A546" t="n">
-        <v>2913</v>
+        <v>50</v>
       </c>
       <c r="B546" t="n">
-        <v>2933</v>
+        <v>150</v>
       </c>
       <c r="C546" t="n">
-        <v>2998</v>
+        <v>259</v>
       </c>
       <c r="D546" t="n">
-        <v>0.4234844961523819</v>
+        <v>0.7220568027163531</v>
       </c>
       <c r="E546" t="n">
-        <v>-0.1759359287895185</v>
+        <v>0.07957873051930442</v>
       </c>
       <c r="F546" t="n">
-        <v>-0.5994204249419004</v>
+        <v>-0.6424780721970487</v>
       </c>
       <c r="G546" t="n">
-        <v>17.70833333333334</v>
+        <v>43.54166666666667</v>
       </c>
       <c r="H546" t="n">
-        <v>7.580939919518528</v>
+        <v>18.1019099384693</v>
       </c>
       <c r="I546" t="n">
-        <v>4.166666666666667</v>
+        <v>20.83333333333334</v>
       </c>
       <c r="J546" t="n">
-        <v>13.54166666666667</v>
+        <v>22.70833333333334</v>
       </c>
       <c r="K546" t="n">
-        <v>6.313249992442276</v>
+        <v>12.51260224119461</v>
       </c>
       <c r="L546" t="n">
-        <v>4.39740234807649</v>
+        <v>10.93064207625626</v>
       </c>
       <c r="M546" t="inlineStr">
         <is>
@@ -47385,20 +47385,20 @@
         </is>
       </c>
       <c r="P546" t="n">
-        <v>0.7304083176128736</v>
+        <v>0.6964143551833305</v>
       </c>
       <c r="Q546" t="n">
-        <v>0.3076923076923077</v>
+        <v>0.9174311926605505</v>
       </c>
       <c r="R546" t="n">
-        <v>0.1058682332148057</v>
+        <v>0.2293047412664045</v>
       </c>
       <c r="S546" t="n">
-        <v>0.3374385293817083</v>
+        <v>0.8213036030336329</v>
       </c>
       <c r="T546" t="inlineStr">
         <is>
-          <t>n53</t>
+          <t>n54</t>
         </is>
       </c>
       <c r="U546" t="n">
@@ -47422,65 +47422,65 @@
     </row>
     <row r="547">
       <c r="A547" t="n">
-        <v>50</v>
+        <v>259</v>
       </c>
       <c r="B547" t="n">
-        <v>150</v>
+        <v>280</v>
       </c>
       <c r="C547" t="n">
-        <v>259</v>
+        <v>376</v>
       </c>
       <c r="D547" t="n">
-        <v>0.7220568027163531</v>
+        <v>0.2395378978042236</v>
       </c>
       <c r="E547" t="n">
-        <v>0.07957873051930442</v>
+        <v>-0.402940174392825</v>
       </c>
       <c r="F547" t="n">
         <v>-0.6424780721970487</v>
       </c>
       <c r="G547" t="n">
-        <v>43.54166666666667</v>
+        <v>24.375</v>
       </c>
       <c r="H547" t="n">
-        <v>18.1019099384693</v>
+        <v>4.469499769386853</v>
       </c>
       <c r="I547" t="n">
-        <v>20.83333333333334</v>
+        <v>4.375</v>
       </c>
       <c r="J547" t="n">
-        <v>22.70833333333334</v>
+        <v>20</v>
       </c>
       <c r="K547" t="n">
-        <v>12.51260224119461</v>
+        <v>2.410976994733891</v>
       </c>
       <c r="L547" t="n">
-        <v>10.93064207625626</v>
+        <v>3.626173196827245</v>
       </c>
       <c r="M547" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N547" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O547" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 316, 'value': -0.49835995862123184, 'amplitude': 0.14411811357581683, 'start_idx': 301, 'end_idx': 343, 'duration': 8.75, 'fwhm': 4.068836477762948, 'rise_time': 3.125, 'decay_time': 5.625, 'auc': 0.8831086782949401}]</t>
         </is>
       </c>
       <c r="P547" t="n">
-        <v>0.6964143551833305</v>
+        <v>0.8362690462618448</v>
       </c>
       <c r="Q547" t="n">
-        <v>0.9174311926605505</v>
+        <v>0.21875</v>
       </c>
       <c r="R547" t="n">
-        <v>0.2293047412664045</v>
+        <v>0.2189715172207768</v>
       </c>
       <c r="S547" t="n">
-        <v>0.8213036030336329</v>
+        <v>0.7910866849202001</v>
       </c>
       <c r="T547" t="inlineStr">
         <is>
@@ -47508,40 +47508,40 @@
     </row>
     <row r="548">
       <c r="A548" t="n">
-        <v>259</v>
+        <v>985</v>
       </c>
       <c r="B548" t="n">
-        <v>280</v>
+        <v>1029</v>
       </c>
       <c r="C548" t="n">
-        <v>376</v>
+        <v>1072</v>
       </c>
       <c r="D548" t="n">
-        <v>0.2395378978042236</v>
+        <v>0.2357420857706622</v>
       </c>
       <c r="E548" t="n">
-        <v>-0.402940174392825</v>
+        <v>-0.4067359864263864</v>
       </c>
       <c r="F548" t="n">
         <v>-0.6424780721970487</v>
       </c>
       <c r="G548" t="n">
-        <v>24.375</v>
+        <v>18.125</v>
       </c>
       <c r="H548" t="n">
-        <v>4.469499769386853</v>
+        <v>9.684587683023954</v>
       </c>
       <c r="I548" t="n">
-        <v>4.375</v>
+        <v>9.166666666666668</v>
       </c>
       <c r="J548" t="n">
-        <v>20</v>
+        <v>8.958333333333334</v>
       </c>
       <c r="K548" t="n">
-        <v>2.410976994733891</v>
+        <v>1.725863540086055</v>
       </c>
       <c r="L548" t="n">
-        <v>3.626173196827245</v>
+        <v>3.568711425715168</v>
       </c>
       <c r="M548" t="inlineStr">
         <is>
@@ -47557,16 +47557,16 @@
         </is>
       </c>
       <c r="P548" t="n">
-        <v>0.8362690462618448</v>
+        <v>0.6761607636482119</v>
       </c>
       <c r="Q548" t="n">
-        <v>0.21875</v>
+        <v>1.023255813953488</v>
       </c>
       <c r="R548" t="n">
-        <v>0.2189715172207768</v>
+        <v>0.3708344244590994</v>
       </c>
       <c r="S548" t="n">
-        <v>0.7910866849202001</v>
+        <v>0.7577142874573817</v>
       </c>
       <c r="T548" t="inlineStr">
         <is>
@@ -47594,40 +47594,40 @@
     </row>
     <row r="549">
       <c r="A549" t="n">
-        <v>985</v>
+        <v>1674</v>
       </c>
       <c r="B549" t="n">
-        <v>1029</v>
+        <v>1707</v>
       </c>
       <c r="C549" t="n">
-        <v>1072</v>
+        <v>1744</v>
       </c>
       <c r="D549" t="n">
-        <v>0.2357420857706622</v>
+        <v>0.4775820794675392</v>
       </c>
       <c r="E549" t="n">
-        <v>-0.4067359864263864</v>
+        <v>-0.1648959927295095</v>
       </c>
       <c r="F549" t="n">
         <v>-0.6424780721970487</v>
       </c>
       <c r="G549" t="n">
-        <v>18.125</v>
+        <v>14.58333333333333</v>
       </c>
       <c r="H549" t="n">
-        <v>9.684587683023954</v>
+        <v>3.716722586988889</v>
       </c>
       <c r="I549" t="n">
-        <v>9.166666666666668</v>
+        <v>6.875</v>
       </c>
       <c r="J549" t="n">
-        <v>8.958333333333334</v>
+        <v>7.708333333333334</v>
       </c>
       <c r="K549" t="n">
-        <v>1.725863540086055</v>
+        <v>5.824849894660415</v>
       </c>
       <c r="L549" t="n">
-        <v>3.568711425715168</v>
+        <v>7.229734216276796</v>
       </c>
       <c r="M549" t="inlineStr">
         <is>
@@ -47643,16 +47643,16 @@
         </is>
       </c>
       <c r="P549" t="n">
-        <v>0.6761607636482119</v>
+        <v>0.6087819542036188</v>
       </c>
       <c r="Q549" t="n">
-        <v>1.023255813953488</v>
+        <v>0.8918918918918918</v>
       </c>
       <c r="R549" t="n">
-        <v>0.3708344244590994</v>
+        <v>0.1293438122922204</v>
       </c>
       <c r="S549" t="n">
-        <v>0.7577142874573817</v>
+        <v>0.9708192952804314</v>
       </c>
       <c r="T549" t="inlineStr">
         <is>
@@ -47680,40 +47680,40 @@
     </row>
     <row r="550">
       <c r="A550" t="n">
-        <v>1674</v>
+        <v>1744</v>
       </c>
       <c r="B550" t="n">
-        <v>1707</v>
+        <v>1755</v>
       </c>
       <c r="C550" t="n">
-        <v>1744</v>
+        <v>1779</v>
       </c>
       <c r="D550" t="n">
-        <v>0.4775820794675392</v>
+        <v>0.4036284333038022</v>
       </c>
       <c r="E550" t="n">
-        <v>-0.1648959927295095</v>
+        <v>-0.2388496388932465</v>
       </c>
       <c r="F550" t="n">
         <v>-0.6424780721970487</v>
       </c>
       <c r="G550" t="n">
-        <v>14.58333333333333</v>
+        <v>7.291666666666667</v>
       </c>
       <c r="H550" t="n">
-        <v>3.716722586988889</v>
+        <v>2.49908184300305</v>
       </c>
       <c r="I550" t="n">
-        <v>6.875</v>
+        <v>2.291666666666667</v>
       </c>
       <c r="J550" t="n">
-        <v>7.708333333333334</v>
+        <v>5</v>
       </c>
       <c r="K550" t="n">
-        <v>5.824849894660415</v>
+        <v>1.990157721469755</v>
       </c>
       <c r="L550" t="n">
-        <v>7.229734216276796</v>
+        <v>6.110208947061293</v>
       </c>
       <c r="M550" t="inlineStr">
         <is>
@@ -47729,16 +47729,16 @@
         </is>
       </c>
       <c r="P550" t="n">
-        <v>0.6087819542036188</v>
+        <v>0.9434184575699507</v>
       </c>
       <c r="Q550" t="n">
-        <v>0.8918918918918918</v>
+        <v>0.4583333333333334</v>
       </c>
       <c r="R550" t="n">
-        <v>0.1293438122922204</v>
+        <v>0.3344000366495765</v>
       </c>
       <c r="S550" t="n">
-        <v>0.9708192952804314</v>
+        <v>0.9481040797030773</v>
       </c>
       <c r="T550" t="inlineStr">
         <is>
@@ -47766,40 +47766,40 @@
     </row>
     <row r="551">
       <c r="A551" t="n">
-        <v>1744</v>
+        <v>1881</v>
       </c>
       <c r="B551" t="n">
-        <v>1755</v>
+        <v>1893</v>
       </c>
       <c r="C551" t="n">
-        <v>1779</v>
+        <v>1925</v>
       </c>
       <c r="D551" t="n">
-        <v>0.4036284333038022</v>
+        <v>0.2453051764235458</v>
       </c>
       <c r="E551" t="n">
-        <v>-0.2388496388932465</v>
+        <v>-0.3971728957735029</v>
       </c>
       <c r="F551" t="n">
         <v>-0.6424780721970487</v>
       </c>
       <c r="G551" t="n">
-        <v>7.291666666666667</v>
+        <v>9.166666666666668</v>
       </c>
       <c r="H551" t="n">
-        <v>2.49908184300305</v>
+        <v>3.549258281650083</v>
       </c>
       <c r="I551" t="n">
-        <v>2.291666666666667</v>
+        <v>2.5</v>
       </c>
       <c r="J551" t="n">
-        <v>5</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="K551" t="n">
-        <v>1.990157721469755</v>
+        <v>1.71702658410761</v>
       </c>
       <c r="L551" t="n">
-        <v>6.110208947061293</v>
+        <v>3.713479428282584</v>
       </c>
       <c r="M551" t="inlineStr">
         <is>
@@ -47815,16 +47815,16 @@
         </is>
       </c>
       <c r="P551" t="n">
-        <v>0.9434184575699507</v>
+        <v>0.8138011648396268</v>
       </c>
       <c r="Q551" t="n">
-        <v>0.4583333333333334</v>
+        <v>0.375</v>
       </c>
       <c r="R551" t="n">
-        <v>0.3344000366495765</v>
+        <v>0.03636662609128708</v>
       </c>
       <c r="S551" t="n">
-        <v>0.9481040797030773</v>
+        <v>0.958705079580325</v>
       </c>
       <c r="T551" t="inlineStr">
         <is>
@@ -47852,65 +47852,65 @@
     </row>
     <row r="552">
       <c r="A552" t="n">
-        <v>1881</v>
+        <v>1925</v>
       </c>
       <c r="B552" t="n">
-        <v>1893</v>
+        <v>1974</v>
       </c>
       <c r="C552" t="n">
-        <v>1925</v>
+        <v>2044</v>
       </c>
       <c r="D552" t="n">
-        <v>0.2453051764235458</v>
+        <v>0.2623837095648273</v>
       </c>
       <c r="E552" t="n">
-        <v>-0.3971728957735029</v>
+        <v>-0.3800943626322214</v>
       </c>
       <c r="F552" t="n">
         <v>-0.6424780721970487</v>
       </c>
       <c r="G552" t="n">
-        <v>9.166666666666668</v>
+        <v>24.79166666666667</v>
       </c>
       <c r="H552" t="n">
-        <v>3.549258281650083</v>
+        <v>3.844290617877657</v>
       </c>
       <c r="I552" t="n">
-        <v>2.5</v>
+        <v>10.20833333333333</v>
       </c>
       <c r="J552" t="n">
-        <v>6.666666666666667</v>
+        <v>14.58333333333333</v>
       </c>
       <c r="K552" t="n">
-        <v>1.71702658410761</v>
+        <v>4.136982185597908</v>
       </c>
       <c r="L552" t="n">
-        <v>3.713479428282584</v>
+        <v>3.972017720910736</v>
       </c>
       <c r="M552" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N552" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O552" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 1950, 'value': -0.3935069289987447, 'amplitude': 0.248971143198304, 'start_idx': 1945, 'end_idx': 1966, 'duration': 4.375, 'fwhm': 3.980712805394215, 'rise_time': 1.0416666666666667, 'decay_time': 3.3333333333333335, 'auc': 1.0039385567779602}]</t>
         </is>
       </c>
       <c r="P552" t="n">
-        <v>0.8138011648396268</v>
+        <v>0.6228041127600839</v>
       </c>
       <c r="Q552" t="n">
-        <v>0.375</v>
+        <v>0.7000000000000001</v>
       </c>
       <c r="R552" t="n">
-        <v>0.03636662609128708</v>
+        <v>0.3731013562606045</v>
       </c>
       <c r="S552" t="n">
-        <v>0.958705079580325</v>
+        <v>0.9522175243192639</v>
       </c>
       <c r="T552" t="inlineStr">
         <is>
@@ -47938,65 +47938,65 @@
     </row>
     <row r="553">
       <c r="A553" t="n">
-        <v>1925</v>
+        <v>2234</v>
       </c>
       <c r="B553" t="n">
-        <v>1974</v>
+        <v>2325</v>
       </c>
       <c r="C553" t="n">
-        <v>2044</v>
+        <v>2404</v>
       </c>
       <c r="D553" t="n">
-        <v>0.2623837095648273</v>
+        <v>0.3576769578168746</v>
       </c>
       <c r="E553" t="n">
-        <v>-0.3800943626322214</v>
+        <v>-0.2848011143801741</v>
       </c>
       <c r="F553" t="n">
         <v>-0.6424780721970487</v>
       </c>
       <c r="G553" t="n">
-        <v>24.79166666666667</v>
+        <v>35.41666666666667</v>
       </c>
       <c r="H553" t="n">
-        <v>3.844290617877657</v>
+        <v>5.454111031304573</v>
       </c>
       <c r="I553" t="n">
-        <v>10.20833333333333</v>
+        <v>18.95833333333334</v>
       </c>
       <c r="J553" t="n">
-        <v>14.58333333333333</v>
+        <v>16.45833333333334</v>
       </c>
       <c r="K553" t="n">
-        <v>4.136982185597908</v>
+        <v>8.7385563793556</v>
       </c>
       <c r="L553" t="n">
-        <v>3.972017720910736</v>
+        <v>5.414586207224328</v>
       </c>
       <c r="M553" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N553" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O553" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 2277, 'value': -0.3748140601750613, 'amplitude': 0.26766401202198736, 'start_idx': 2273, 'end_idx': 2284, 'duration': 2.291666666666667, 'fwhm': 3.6044162768743604, 'rise_time': 0.8333333333333334, 'decay_time': 1.4583333333333335, 'auc': 0.5721162979105935}]</t>
         </is>
       </c>
       <c r="P553" t="n">
-        <v>0.6228041127600839</v>
+        <v>0.5146588997322531</v>
       </c>
       <c r="Q553" t="n">
-        <v>0.7000000000000001</v>
+        <v>1.151898734177215</v>
       </c>
       <c r="R553" t="n">
-        <v>0.3731013562606045</v>
+        <v>0.1776486587305441</v>
       </c>
       <c r="S553" t="n">
-        <v>0.9522175243192639</v>
+        <v>0.840839376857064</v>
       </c>
       <c r="T553" t="inlineStr">
         <is>
@@ -48024,40 +48024,40 @@
     </row>
     <row r="554">
       <c r="A554" t="n">
-        <v>2234</v>
+        <v>2404</v>
       </c>
       <c r="B554" t="n">
-        <v>2325</v>
+        <v>2426</v>
       </c>
       <c r="C554" t="n">
-        <v>2404</v>
+        <v>2453</v>
       </c>
       <c r="D554" t="n">
-        <v>0.3576769578168746</v>
+        <v>0.3554726938247301</v>
       </c>
       <c r="E554" t="n">
-        <v>-0.2848011143801741</v>
+        <v>-0.2870053783723185</v>
       </c>
       <c r="F554" t="n">
         <v>-0.6424780721970487</v>
       </c>
       <c r="G554" t="n">
-        <v>35.41666666666667</v>
+        <v>10.20833333333333</v>
       </c>
       <c r="H554" t="n">
-        <v>5.454111031304573</v>
+        <v>4.95474542295104</v>
       </c>
       <c r="I554" t="n">
-        <v>18.95833333333334</v>
+        <v>4.583333333333334</v>
       </c>
       <c r="J554" t="n">
-        <v>16.45833333333334</v>
+        <v>5.625</v>
       </c>
       <c r="K554" t="n">
-        <v>8.7385563793556</v>
+        <v>2.801627628560473</v>
       </c>
       <c r="L554" t="n">
-        <v>5.414586207224328</v>
+        <v>5.381217612608129</v>
       </c>
       <c r="M554" t="inlineStr">
         <is>
@@ -48073,16 +48073,16 @@
         </is>
       </c>
       <c r="P554" t="n">
-        <v>0.5146588997322531</v>
+        <v>0.7678192886470626</v>
       </c>
       <c r="Q554" t="n">
-        <v>1.151898734177215</v>
+        <v>0.8148148148148149</v>
       </c>
       <c r="R554" t="n">
-        <v>0.1776486587305441</v>
+        <v>0.1848067150024787</v>
       </c>
       <c r="S554" t="n">
-        <v>0.840839376857064</v>
+        <v>0.9294529537572707</v>
       </c>
       <c r="T554" t="inlineStr">
         <is>
@@ -48110,40 +48110,40 @@
     </row>
     <row r="555">
       <c r="A555" t="n">
-        <v>2404</v>
+        <v>2453</v>
       </c>
       <c r="B555" t="n">
-        <v>2426</v>
+        <v>2494</v>
       </c>
       <c r="C555" t="n">
-        <v>2453</v>
+        <v>2533</v>
       </c>
       <c r="D555" t="n">
-        <v>0.3554726938247301</v>
+        <v>0.4821916378646363</v>
       </c>
       <c r="E555" t="n">
-        <v>-0.2870053783723185</v>
+        <v>-0.1602864343324124</v>
       </c>
       <c r="F555" t="n">
         <v>-0.6424780721970487</v>
       </c>
       <c r="G555" t="n">
-        <v>10.20833333333333</v>
+        <v>16.66666666666667</v>
       </c>
       <c r="H555" t="n">
-        <v>4.95474542295104</v>
+        <v>11.60260657575748</v>
       </c>
       <c r="I555" t="n">
-        <v>4.583333333333334</v>
+        <v>8.541666666666668</v>
       </c>
       <c r="J555" t="n">
-        <v>5.625</v>
+        <v>8.125</v>
       </c>
       <c r="K555" t="n">
-        <v>2.801627628560473</v>
+        <v>5.767740711386011</v>
       </c>
       <c r="L555" t="n">
-        <v>5.381217612608129</v>
+        <v>7.29951464460144</v>
       </c>
       <c r="M555" t="inlineStr">
         <is>
@@ -48159,16 +48159,16 @@
         </is>
       </c>
       <c r="P555" t="n">
-        <v>0.7678192886470626</v>
+        <v>0.7065662362514243</v>
       </c>
       <c r="Q555" t="n">
-        <v>0.8148148148148149</v>
+        <v>1.051282051282051</v>
       </c>
       <c r="R555" t="n">
-        <v>0.1848067150024787</v>
+        <v>0.2384232187685869</v>
       </c>
       <c r="S555" t="n">
-        <v>0.9294529537572707</v>
+        <v>0.9849038548600051</v>
       </c>
       <c r="T555" t="inlineStr">
         <is>
@@ -48196,40 +48196,40 @@
     </row>
     <row r="556">
       <c r="A556" t="n">
-        <v>2453</v>
+        <v>2618</v>
       </c>
       <c r="B556" t="n">
-        <v>2494</v>
+        <v>2640</v>
       </c>
       <c r="C556" t="n">
-        <v>2533</v>
+        <v>2682</v>
       </c>
       <c r="D556" t="n">
-        <v>0.4821916378646363</v>
+        <v>0.393680541135116</v>
       </c>
       <c r="E556" t="n">
-        <v>-0.1602864343324124</v>
+        <v>-0.2487975310619327</v>
       </c>
       <c r="F556" t="n">
         <v>-0.6424780721970487</v>
       </c>
       <c r="G556" t="n">
-        <v>16.66666666666667</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="H556" t="n">
-        <v>11.60260657575748</v>
+        <v>5.007608566830774</v>
       </c>
       <c r="I556" t="n">
-        <v>8.541666666666668</v>
+        <v>4.583333333333334</v>
       </c>
       <c r="J556" t="n">
-        <v>8.125</v>
+        <v>8.75</v>
       </c>
       <c r="K556" t="n">
-        <v>5.767740711386011</v>
+        <v>3.23890508195643</v>
       </c>
       <c r="L556" t="n">
-        <v>7.29951464460144</v>
+        <v>5.959615741235883</v>
       </c>
       <c r="M556" t="inlineStr">
         <is>
@@ -48245,16 +48245,16 @@
         </is>
       </c>
       <c r="P556" t="n">
-        <v>0.7065662362514243</v>
+        <v>0.8556793679152189</v>
       </c>
       <c r="Q556" t="n">
-        <v>1.051282051282051</v>
+        <v>0.5238095238095238</v>
       </c>
       <c r="R556" t="n">
-        <v>0.2384232187685869</v>
+        <v>0.1061861112870746</v>
       </c>
       <c r="S556" t="n">
-        <v>0.9849038548600051</v>
+        <v>0.9585073935407384</v>
       </c>
       <c r="T556" t="inlineStr">
         <is>
@@ -48282,40 +48282,40 @@
     </row>
     <row r="557">
       <c r="A557" t="n">
-        <v>2618</v>
+        <v>0</v>
       </c>
       <c r="B557" t="n">
-        <v>2640</v>
+        <v>11</v>
       </c>
       <c r="C557" t="n">
-        <v>2682</v>
+        <v>38</v>
       </c>
       <c r="D557" t="n">
-        <v>0.393680541135116</v>
+        <v>3.298686904139366</v>
       </c>
       <c r="E557" t="n">
-        <v>-0.2487975310619327</v>
+        <v>2.722202788424738</v>
       </c>
       <c r="F557" t="n">
-        <v>-0.6424780721970487</v>
+        <v>-0.5764841157146284</v>
       </c>
       <c r="G557" t="n">
-        <v>13.33333333333333</v>
+        <v>7.916666666666667</v>
       </c>
       <c r="H557" t="n">
-        <v>5.007608566830774</v>
+        <v>3.20660805043034</v>
       </c>
       <c r="I557" t="n">
-        <v>4.583333333333334</v>
+        <v>2.291666666666667</v>
       </c>
       <c r="J557" t="n">
-        <v>8.75</v>
+        <v>5.625</v>
       </c>
       <c r="K557" t="n">
-        <v>3.23890508195643</v>
+        <v>20.34015772203106</v>
       </c>
       <c r="L557" t="n">
-        <v>5.959615741235883</v>
+        <v>23.93945816199825</v>
       </c>
       <c r="M557" t="inlineStr">
         <is>
@@ -48331,20 +48331,20 @@
         </is>
       </c>
       <c r="P557" t="n">
-        <v>0.8556793679152189</v>
+        <v>0.9500558570876286</v>
       </c>
       <c r="Q557" t="n">
-        <v>0.5238095238095238</v>
+        <v>0.4074074074074074</v>
       </c>
       <c r="R557" t="n">
-        <v>0.1061861112870746</v>
+        <v>0.2405065167450832</v>
       </c>
       <c r="S557" t="n">
-        <v>0.9585073935407384</v>
+        <v>0.9650291178828899</v>
       </c>
       <c r="T557" t="inlineStr">
         <is>
-          <t>n54</t>
+          <t>n55</t>
         </is>
       </c>
       <c r="U557" t="n">
@@ -48368,40 +48368,40 @@
     </row>
     <row r="558">
       <c r="A558" t="n">
-        <v>0</v>
+        <v>38</v>
       </c>
       <c r="B558" t="n">
-        <v>11</v>
+        <v>52</v>
       </c>
       <c r="C558" t="n">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="D558" t="n">
-        <v>3.298686904139366</v>
+        <v>1.752207423098249</v>
       </c>
       <c r="E558" t="n">
-        <v>2.722202788424738</v>
+        <v>1.17572330738362</v>
       </c>
       <c r="F558" t="n">
         <v>-0.5764841157146284</v>
       </c>
       <c r="G558" t="n">
-        <v>7.916666666666667</v>
+        <v>6.666666666666667</v>
       </c>
       <c r="H558" t="n">
-        <v>3.20660805043034</v>
+        <v>3.178060324123357</v>
       </c>
       <c r="I558" t="n">
-        <v>2.291666666666667</v>
+        <v>2.916666666666667</v>
       </c>
       <c r="J558" t="n">
-        <v>5.625</v>
+        <v>3.75</v>
       </c>
       <c r="K558" t="n">
-        <v>20.34015772203106</v>
+        <v>10.33944042550597</v>
       </c>
       <c r="L558" t="n">
-        <v>23.93945816199825</v>
+        <v>12.71624058766114</v>
       </c>
       <c r="M558" t="inlineStr">
         <is>
@@ -48417,16 +48417,16 @@
         </is>
       </c>
       <c r="P558" t="n">
-        <v>0.9500558570876286</v>
+        <v>0.6532804798112163</v>
       </c>
       <c r="Q558" t="n">
-        <v>0.4074074074074074</v>
+        <v>0.7777777777777779</v>
       </c>
       <c r="R558" t="n">
-        <v>0.2405065167450832</v>
+        <v>0.01454016939370568</v>
       </c>
       <c r="S558" t="n">
-        <v>0.9650291178828899</v>
+        <v>0.987846486551849</v>
       </c>
       <c r="T558" t="inlineStr">
         <is>
@@ -48454,40 +48454,40 @@
     </row>
     <row r="559">
       <c r="A559" t="n">
-        <v>38</v>
+        <v>70</v>
       </c>
       <c r="B559" t="n">
-        <v>52</v>
+        <v>80</v>
       </c>
       <c r="C559" t="n">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="D559" t="n">
-        <v>1.752207423098249</v>
+        <v>1.661045501748406</v>
       </c>
       <c r="E559" t="n">
-        <v>1.17572330738362</v>
+        <v>1.084561386033777</v>
       </c>
       <c r="F559" t="n">
         <v>-0.5764841157146284</v>
       </c>
       <c r="G559" t="n">
-        <v>6.666666666666667</v>
+        <v>6.041666666666667</v>
       </c>
       <c r="H559" t="n">
-        <v>3.178060324123357</v>
+        <v>2.024983887853731</v>
       </c>
       <c r="I559" t="n">
-        <v>2.916666666666667</v>
+        <v>2.083333333333333</v>
       </c>
       <c r="J559" t="n">
-        <v>3.75</v>
+        <v>3.958333333333333</v>
       </c>
       <c r="K559" t="n">
-        <v>10.33944042550597</v>
+        <v>8.250143859745656</v>
       </c>
       <c r="L559" t="n">
-        <v>12.71624058766114</v>
+        <v>12.05465400319828</v>
       </c>
       <c r="M559" t="inlineStr">
         <is>
@@ -48503,16 +48503,16 @@
         </is>
       </c>
       <c r="P559" t="n">
-        <v>0.6532804798112163</v>
+        <v>0.9161857347141756</v>
       </c>
       <c r="Q559" t="n">
-        <v>0.7777777777777779</v>
+        <v>0.5263157894736842</v>
       </c>
       <c r="R559" t="n">
-        <v>0.01454016939370568</v>
+        <v>0.1385885161312313</v>
       </c>
       <c r="S559" t="n">
-        <v>0.987846486551849</v>
+        <v>0.9868625471935826</v>
       </c>
       <c r="T559" t="inlineStr">
         <is>
@@ -48540,40 +48540,40 @@
     </row>
     <row r="560">
       <c r="A560" t="n">
-        <v>70</v>
+        <v>99</v>
       </c>
       <c r="B560" t="n">
-        <v>80</v>
+        <v>109</v>
       </c>
       <c r="C560" t="n">
-        <v>99</v>
+        <v>237</v>
       </c>
       <c r="D560" t="n">
-        <v>1.661045501748406</v>
+        <v>1.197465981209974</v>
       </c>
       <c r="E560" t="n">
-        <v>1.084561386033777</v>
+        <v>0.6209818654953455</v>
       </c>
       <c r="F560" t="n">
         <v>-0.5764841157146284</v>
       </c>
       <c r="G560" t="n">
-        <v>6.041666666666667</v>
+        <v>28.75</v>
       </c>
       <c r="H560" t="n">
-        <v>2.024983887853731</v>
+        <v>4.2220928714426</v>
       </c>
       <c r="I560" t="n">
         <v>2.083333333333333</v>
       </c>
       <c r="J560" t="n">
-        <v>3.958333333333333</v>
+        <v>26.66666666666667</v>
       </c>
       <c r="K560" t="n">
-        <v>8.250143859745656</v>
+        <v>19.29682407564328</v>
       </c>
       <c r="L560" t="n">
-        <v>12.05465400319828</v>
+        <v>8.690332726522147</v>
       </c>
       <c r="M560" t="inlineStr">
         <is>
@@ -48589,16 +48589,16 @@
         </is>
       </c>
       <c r="P560" t="n">
-        <v>0.9161857347141756</v>
+        <v>0.7460478595623175</v>
       </c>
       <c r="Q560" t="n">
-        <v>0.5263157894736842</v>
+        <v>0.078125</v>
       </c>
       <c r="R560" t="n">
-        <v>0.1385885161312313</v>
+        <v>0.4037730543074791</v>
       </c>
       <c r="S560" t="n">
-        <v>0.9868625471935826</v>
+        <v>0.6743622932483995</v>
       </c>
       <c r="T560" t="inlineStr">
         <is>
@@ -48626,40 +48626,40 @@
     </row>
     <row r="561">
       <c r="A561" t="n">
-        <v>99</v>
+        <v>1610</v>
       </c>
       <c r="B561" t="n">
-        <v>109</v>
+        <v>1647</v>
       </c>
       <c r="C561" t="n">
-        <v>237</v>
+        <v>1683</v>
       </c>
       <c r="D561" t="n">
-        <v>1.197465981209974</v>
+        <v>0.6618275079365217</v>
       </c>
       <c r="E561" t="n">
-        <v>0.6209818654953455</v>
+        <v>0.08534339222189322</v>
       </c>
       <c r="F561" t="n">
         <v>-0.5764841157146284</v>
       </c>
       <c r="G561" t="n">
-        <v>28.75</v>
+        <v>15.20833333333333</v>
       </c>
       <c r="H561" t="n">
-        <v>4.2220928714426</v>
+        <v>7.218513519699978</v>
       </c>
       <c r="I561" t="n">
-        <v>2.083333333333333</v>
+        <v>7.708333333333334</v>
       </c>
       <c r="J561" t="n">
-        <v>26.66666666666667</v>
+        <v>7.5</v>
       </c>
       <c r="K561" t="n">
-        <v>19.29682407564328</v>
+        <v>7.812846963587878</v>
       </c>
       <c r="L561" t="n">
-        <v>8.690332726522147</v>
+        <v>4.803060247040816</v>
       </c>
       <c r="M561" t="inlineStr">
         <is>
@@ -48675,16 +48675,16 @@
         </is>
       </c>
       <c r="P561" t="n">
-        <v>0.7460478595623175</v>
+        <v>0.5774547956989096</v>
       </c>
       <c r="Q561" t="n">
-        <v>0.078125</v>
+        <v>1.027777777777778</v>
       </c>
       <c r="R561" t="n">
-        <v>0.4037730543074791</v>
+        <v>0.07900080799680309</v>
       </c>
       <c r="S561" t="n">
-        <v>0.6743622932483995</v>
+        <v>0.9381476164520872</v>
       </c>
       <c r="T561" t="inlineStr">
         <is>
@@ -48712,65 +48712,65 @@
     </row>
     <row r="562">
       <c r="A562" t="n">
-        <v>1610</v>
+        <v>1683</v>
       </c>
       <c r="B562" t="n">
-        <v>1647</v>
+        <v>1714</v>
       </c>
       <c r="C562" t="n">
-        <v>1683</v>
+        <v>1771</v>
       </c>
       <c r="D562" t="n">
-        <v>0.6618275079365217</v>
+        <v>0.5634383621621342</v>
       </c>
       <c r="E562" t="n">
-        <v>0.08534339222189322</v>
+        <v>-0.01304575355249425</v>
       </c>
       <c r="F562" t="n">
         <v>-0.5764841157146284</v>
       </c>
       <c r="G562" t="n">
-        <v>15.20833333333333</v>
+        <v>18.33333333333334</v>
       </c>
       <c r="H562" t="n">
-        <v>7.218513519699978</v>
+        <v>8.232317205697845</v>
       </c>
       <c r="I562" t="n">
-        <v>7.708333333333334</v>
+        <v>6.458333333333334</v>
       </c>
       <c r="J562" t="n">
-        <v>7.5</v>
+        <v>11.875</v>
       </c>
       <c r="K562" t="n">
-        <v>7.812846963587878</v>
+        <v>8.387063649005491</v>
       </c>
       <c r="L562" t="n">
-        <v>4.803060247040816</v>
+        <v>4.089023750911086</v>
       </c>
       <c r="M562" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N562" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O562" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 1757, 'value': -0.10219677061183875, 'amplitude': 0.4742873451027897, 'start_idx': 1740, 'end_idx': 1770, 'duration': 6.25, 'fwhm': 3.040745392866124, 'rise_time': 3.541666666666667, 'decay_time': 2.7083333333333335, 'auc': 2.6234556652150727}]</t>
         </is>
       </c>
       <c r="P562" t="n">
-        <v>0.5774547956989096</v>
+        <v>0.6512313297072113</v>
       </c>
       <c r="Q562" t="n">
-        <v>1.027777777777778</v>
+        <v>0.543859649122807</v>
       </c>
       <c r="R562" t="n">
-        <v>0.07900080799680309</v>
+        <v>0.0815708213236853</v>
       </c>
       <c r="S562" t="n">
-        <v>0.9381476164520872</v>
+        <v>0.4865146309684825</v>
       </c>
       <c r="T562" t="inlineStr">
         <is>
@@ -48798,40 +48798,40 @@
     </row>
     <row r="563">
       <c r="A563" t="n">
-        <v>1683</v>
+        <v>2135</v>
       </c>
       <c r="B563" t="n">
-        <v>1714</v>
+        <v>2154</v>
       </c>
       <c r="C563" t="n">
-        <v>1771</v>
+        <v>2185</v>
       </c>
       <c r="D563" t="n">
-        <v>0.5634383621621342</v>
+        <v>1.936550563609353</v>
       </c>
       <c r="E563" t="n">
-        <v>-0.01304575355249425</v>
+        <v>1.360066447894724</v>
       </c>
       <c r="F563" t="n">
         <v>-0.5764841157146284</v>
       </c>
       <c r="G563" t="n">
-        <v>18.33333333333334</v>
+        <v>10.41666666666667</v>
       </c>
       <c r="H563" t="n">
-        <v>8.232317205697845</v>
+        <v>2.786341065776507</v>
       </c>
       <c r="I563" t="n">
+        <v>3.958333333333333</v>
+      </c>
+      <c r="J563" t="n">
         <v>6.458333333333334</v>
       </c>
-      <c r="J563" t="n">
-        <v>11.875</v>
-      </c>
       <c r="K563" t="n">
-        <v>8.387063649005491</v>
+        <v>16.32324909838804</v>
       </c>
       <c r="L563" t="n">
-        <v>4.089023750911086</v>
+        <v>14.05406834396599</v>
       </c>
       <c r="M563" t="inlineStr">
         <is>
@@ -48847,16 +48847,16 @@
         </is>
       </c>
       <c r="P563" t="n">
-        <v>0.6512313297072113</v>
+        <v>0.7489734395898202</v>
       </c>
       <c r="Q563" t="n">
-        <v>0.543859649122807</v>
+        <v>0.6129032258064516</v>
       </c>
       <c r="R563" t="n">
-        <v>0.0815708213236853</v>
+        <v>0.1001560085606872</v>
       </c>
       <c r="S563" t="n">
-        <v>0.4865146309684825</v>
+        <v>0.6932423075341129</v>
       </c>
       <c r="T563" t="inlineStr">
         <is>
@@ -48884,40 +48884,40 @@
     </row>
     <row r="564">
       <c r="A564" t="n">
-        <v>2135</v>
+        <v>2185</v>
       </c>
       <c r="B564" t="n">
-        <v>2154</v>
+        <v>2208</v>
       </c>
       <c r="C564" t="n">
-        <v>2185</v>
+        <v>2248</v>
       </c>
       <c r="D564" t="n">
-        <v>1.936550563609353</v>
+        <v>2.090567757084476</v>
       </c>
       <c r="E564" t="n">
-        <v>1.360066447894724</v>
+        <v>1.514083641369847</v>
       </c>
       <c r="F564" t="n">
         <v>-0.5764841157146284</v>
       </c>
       <c r="G564" t="n">
-        <v>10.41666666666667</v>
+        <v>13.125</v>
       </c>
       <c r="H564" t="n">
-        <v>2.786341065776507</v>
+        <v>19.67314907752306</v>
       </c>
       <c r="I564" t="n">
-        <v>3.958333333333333</v>
+        <v>4.791666666666667</v>
       </c>
       <c r="J564" t="n">
-        <v>6.458333333333334</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="K564" t="n">
-        <v>16.32324909838804</v>
+        <v>21.08027665901386</v>
       </c>
       <c r="L564" t="n">
-        <v>14.05406834396599</v>
+        <v>15.17181254539333</v>
       </c>
       <c r="M564" t="inlineStr">
         <is>
@@ -48933,16 +48933,16 @@
         </is>
       </c>
       <c r="P564" t="n">
-        <v>0.7489734395898202</v>
+        <v>0.8436343934894329</v>
       </c>
       <c r="Q564" t="n">
-        <v>0.6129032258064516</v>
+        <v>0.575</v>
       </c>
       <c r="R564" t="n">
-        <v>0.1001560085606872</v>
+        <v>0.1472981450655109</v>
       </c>
       <c r="S564" t="n">
-        <v>0.6932423075341129</v>
+        <v>0.9676218423821106</v>
       </c>
       <c r="T564" t="inlineStr">
         <is>
@@ -48970,40 +48970,40 @@
     </row>
     <row r="565">
       <c r="A565" t="n">
-        <v>2185</v>
+        <v>2321</v>
       </c>
       <c r="B565" t="n">
-        <v>2208</v>
+        <v>2337</v>
       </c>
       <c r="C565" t="n">
-        <v>2248</v>
+        <v>2455</v>
       </c>
       <c r="D565" t="n">
-        <v>2.090567757084476</v>
+        <v>1.653294690974247</v>
       </c>
       <c r="E565" t="n">
-        <v>1.514083641369847</v>
+        <v>1.076810575259619</v>
       </c>
       <c r="F565" t="n">
         <v>-0.5764841157146284</v>
       </c>
       <c r="G565" t="n">
-        <v>13.125</v>
+        <v>27.91666666666667</v>
       </c>
       <c r="H565" t="n">
-        <v>19.67314907752306</v>
+        <v>3.725203103661083</v>
       </c>
       <c r="I565" t="n">
-        <v>4.791666666666667</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="J565" t="n">
-        <v>8.333333333333334</v>
+        <v>24.58333333333334</v>
       </c>
       <c r="K565" t="n">
-        <v>21.08027665901386</v>
+        <v>27.93009846012884</v>
       </c>
       <c r="L565" t="n">
-        <v>15.17181254539333</v>
+        <v>11.99840428455517</v>
       </c>
       <c r="M565" t="inlineStr">
         <is>
@@ -49019,16 +49019,16 @@
         </is>
       </c>
       <c r="P565" t="n">
-        <v>0.8436343934894329</v>
+        <v>0.7988922086018987</v>
       </c>
       <c r="Q565" t="n">
-        <v>0.575</v>
+        <v>0.1355932203389831</v>
       </c>
       <c r="R565" t="n">
-        <v>0.1472981450655109</v>
+        <v>0.4026629482562857</v>
       </c>
       <c r="S565" t="n">
-        <v>0.9676218423821106</v>
+        <v>0.8733437811117792</v>
       </c>
       <c r="T565" t="inlineStr">
         <is>
@@ -49056,40 +49056,40 @@
     </row>
     <row r="566">
       <c r="A566" t="n">
-        <v>2321</v>
+        <v>2455</v>
       </c>
       <c r="B566" t="n">
-        <v>2337</v>
+        <v>2479</v>
       </c>
       <c r="C566" t="n">
-        <v>2455</v>
+        <v>2519</v>
       </c>
       <c r="D566" t="n">
-        <v>1.653294690974247</v>
+        <v>0.9674041286584292</v>
       </c>
       <c r="E566" t="n">
-        <v>1.076810575259619</v>
+        <v>0.3909200129438007</v>
       </c>
       <c r="F566" t="n">
         <v>-0.5764841157146284</v>
       </c>
       <c r="G566" t="n">
-        <v>27.91666666666667</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="H566" t="n">
-        <v>3.725203103661083</v>
+        <v>8.066812852137939</v>
       </c>
       <c r="I566" t="n">
-        <v>3.333333333333333</v>
+        <v>5</v>
       </c>
       <c r="J566" t="n">
-        <v>24.58333333333334</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="K566" t="n">
-        <v>27.93009846012884</v>
+        <v>10.47168293330745</v>
       </c>
       <c r="L566" t="n">
-        <v>11.99840428455517</v>
+        <v>7.020711979273189</v>
       </c>
       <c r="M566" t="inlineStr">
         <is>
@@ -49105,16 +49105,16 @@
         </is>
       </c>
       <c r="P566" t="n">
-        <v>0.7988922086018987</v>
+        <v>0.8013809526075173</v>
       </c>
       <c r="Q566" t="n">
-        <v>0.1355932203389831</v>
+        <v>0.6</v>
       </c>
       <c r="R566" t="n">
-        <v>0.4026629482562857</v>
+        <v>0.2221155528597475</v>
       </c>
       <c r="S566" t="n">
-        <v>0.8733437811117792</v>
+        <v>0.6916294304766668</v>
       </c>
       <c r="T566" t="inlineStr">
         <is>
@@ -49142,40 +49142,40 @@
     </row>
     <row r="567">
       <c r="A567" t="n">
-        <v>2455</v>
+        <v>2608</v>
       </c>
       <c r="B567" t="n">
-        <v>2479</v>
+        <v>2645</v>
       </c>
       <c r="C567" t="n">
-        <v>2519</v>
+        <v>2683</v>
       </c>
       <c r="D567" t="n">
-        <v>0.9674041286584292</v>
+        <v>1.688852101818673</v>
       </c>
       <c r="E567" t="n">
-        <v>0.3909200129438007</v>
+        <v>1.112367986104045</v>
       </c>
       <c r="F567" t="n">
         <v>-0.5764841157146284</v>
       </c>
       <c r="G567" t="n">
-        <v>13.33333333333333</v>
+        <v>15.625</v>
       </c>
       <c r="H567" t="n">
-        <v>8.066812852137939</v>
+        <v>9.972820769513268</v>
       </c>
       <c r="I567" t="n">
-        <v>5</v>
+        <v>7.708333333333334</v>
       </c>
       <c r="J567" t="n">
-        <v>8.333333333333334</v>
+        <v>7.916666666666667</v>
       </c>
       <c r="K567" t="n">
-        <v>10.47168293330745</v>
+        <v>19.71591251354147</v>
       </c>
       <c r="L567" t="n">
-        <v>7.020711979273189</v>
+        <v>12.25645397947801</v>
       </c>
       <c r="M567" t="inlineStr">
         <is>
@@ -49191,16 +49191,16 @@
         </is>
       </c>
       <c r="P567" t="n">
-        <v>0.8013809526075173</v>
+        <v>0.7019926699786141</v>
       </c>
       <c r="Q567" t="n">
-        <v>0.6</v>
+        <v>0.9736842105263158</v>
       </c>
       <c r="R567" t="n">
-        <v>0.2221155528597475</v>
+        <v>0.09093870644227998</v>
       </c>
       <c r="S567" t="n">
-        <v>0.6916294304766668</v>
+        <v>0.9832106853713622</v>
       </c>
       <c r="T567" t="inlineStr">
         <is>
@@ -49228,40 +49228,40 @@
     </row>
     <row r="568">
       <c r="A568" t="n">
-        <v>2608</v>
+        <v>2873</v>
       </c>
       <c r="B568" t="n">
-        <v>2645</v>
+        <v>2894</v>
       </c>
       <c r="C568" t="n">
-        <v>2683</v>
+        <v>2937</v>
       </c>
       <c r="D568" t="n">
-        <v>1.688852101818673</v>
+        <v>1.110548449381077</v>
       </c>
       <c r="E568" t="n">
-        <v>1.112367986104045</v>
+        <v>0.5340643336664483</v>
       </c>
       <c r="F568" t="n">
         <v>-0.5764841157146284</v>
       </c>
       <c r="G568" t="n">
-        <v>15.625</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="H568" t="n">
-        <v>9.972820769513268</v>
+        <v>3.828272813883208</v>
       </c>
       <c r="I568" t="n">
-        <v>7.708333333333334</v>
+        <v>4.375</v>
       </c>
       <c r="J568" t="n">
-        <v>7.916666666666667</v>
+        <v>8.958333333333334</v>
       </c>
       <c r="K568" t="n">
-        <v>19.71591251354147</v>
+        <v>11.86123662139591</v>
       </c>
       <c r="L568" t="n">
-        <v>12.25645397947801</v>
+        <v>8.059548818491654</v>
       </c>
       <c r="M568" t="inlineStr">
         <is>
@@ -49277,16 +49277,16 @@
         </is>
       </c>
       <c r="P568" t="n">
-        <v>0.7019926699786141</v>
+        <v>0.7028948835804227</v>
       </c>
       <c r="Q568" t="n">
-        <v>0.9736842105263158</v>
+        <v>0.4883720930232558</v>
       </c>
       <c r="R568" t="n">
-        <v>0.09093870644227998</v>
+        <v>0.060153744796582</v>
       </c>
       <c r="S568" t="n">
-        <v>0.9832106853713622</v>
+        <v>0.9328159405549826</v>
       </c>
       <c r="T568" t="inlineStr">
         <is>
@@ -49314,40 +49314,40 @@
     </row>
     <row r="569">
       <c r="A569" t="n">
-        <v>2873</v>
+        <v>2937</v>
       </c>
       <c r="B569" t="n">
-        <v>2894</v>
+        <v>2948</v>
       </c>
       <c r="C569" t="n">
-        <v>2937</v>
+        <v>2998</v>
       </c>
       <c r="D569" t="n">
-        <v>1.110548449381077</v>
+        <v>0.8623512883155193</v>
       </c>
       <c r="E569" t="n">
-        <v>0.5340643336664483</v>
+        <v>0.2858671726008909</v>
       </c>
       <c r="F569" t="n">
         <v>-0.5764841157146284</v>
       </c>
       <c r="G569" t="n">
-        <v>13.33333333333333</v>
+        <v>12.70833333333333</v>
       </c>
       <c r="H569" t="n">
-        <v>3.828272813883208</v>
+        <v>3.220587420435758</v>
       </c>
       <c r="I569" t="n">
-        <v>4.375</v>
+        <v>2.291666666666667</v>
       </c>
       <c r="J569" t="n">
-        <v>8.958333333333334</v>
+        <v>10.41666666666667</v>
       </c>
       <c r="K569" t="n">
-        <v>11.86123662139591</v>
+        <v>10.53085869272119</v>
       </c>
       <c r="L569" t="n">
-        <v>8.059548818491654</v>
+        <v>6.258315259223059</v>
       </c>
       <c r="M569" t="inlineStr">
         <is>
@@ -49363,16 +49363,16 @@
         </is>
       </c>
       <c r="P569" t="n">
-        <v>0.7028948835804227</v>
+        <v>0.7984730079498453</v>
       </c>
       <c r="Q569" t="n">
-        <v>0.4883720930232558</v>
+        <v>0.22</v>
       </c>
       <c r="R569" t="n">
-        <v>0.060153744796582</v>
+        <v>0.2031365524960099</v>
       </c>
       <c r="S569" t="n">
-        <v>0.9328159405549826</v>
+        <v>0.4554505092835494</v>
       </c>
       <c r="T569" t="inlineStr">
         <is>
@@ -49400,69 +49400,69 @@
     </row>
     <row r="570">
       <c r="A570" t="n">
-        <v>2937</v>
+        <v>506</v>
       </c>
       <c r="B570" t="n">
-        <v>2948</v>
+        <v>540</v>
       </c>
       <c r="C570" t="n">
-        <v>2998</v>
+        <v>657</v>
       </c>
       <c r="D570" t="n">
-        <v>0.8623512883155193</v>
+        <v>0.2536794182894964</v>
       </c>
       <c r="E570" t="n">
-        <v>0.2858671726008909</v>
+        <v>-0.4903592408443059</v>
       </c>
       <c r="F570" t="n">
-        <v>-0.5764841157146284</v>
+        <v>-0.7440386591338023</v>
       </c>
       <c r="G570" t="n">
-        <v>12.70833333333333</v>
+        <v>31.45833333333334</v>
       </c>
       <c r="H570" t="n">
-        <v>3.220587420435758</v>
+        <v>10.36070479944475</v>
       </c>
       <c r="I570" t="n">
-        <v>2.291666666666667</v>
+        <v>7.083333333333334</v>
       </c>
       <c r="J570" t="n">
-        <v>10.41666666666667</v>
+        <v>24.375</v>
       </c>
       <c r="K570" t="n">
-        <v>10.53085869272119</v>
+        <v>3.29925920988696</v>
       </c>
       <c r="L570" t="n">
-        <v>6.258315259223059</v>
+        <v>3.947023595902931</v>
       </c>
       <c r="M570" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N570" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O570" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 603, 'value': -0.6578624000846675, 'amplitude': 0.08617625904913484, 'start_idx': 590, 'end_idx': 613, 'duration': 4.791666666666667, 'fwhm': 4.631613194354122, 'rise_time': 2.7083333333333335, 'decay_time': 2.0833333333333335, 'auc': 0.28840562782311474}]</t>
         </is>
       </c>
       <c r="P570" t="n">
-        <v>0.7984730079498453</v>
+        <v>0.8817370162805458</v>
       </c>
       <c r="Q570" t="n">
-        <v>0.22</v>
+        <v>0.2905982905982906</v>
       </c>
       <c r="R570" t="n">
-        <v>0.2031365524960099</v>
+        <v>0.4821851439315137</v>
       </c>
       <c r="S570" t="n">
-        <v>0.4554505092835494</v>
+        <v>0.5773409680765692</v>
       </c>
       <c r="T570" t="inlineStr">
         <is>
-          <t>n55</t>
+          <t>n56</t>
         </is>
       </c>
       <c r="U570" t="n">
@@ -49486,65 +49486,65 @@
     </row>
     <row r="571">
       <c r="A571" t="n">
-        <v>506</v>
+        <v>1245</v>
       </c>
       <c r="B571" t="n">
-        <v>540</v>
+        <v>1312</v>
       </c>
       <c r="C571" t="n">
-        <v>657</v>
+        <v>1502</v>
       </c>
       <c r="D571" t="n">
-        <v>0.2536794182894964</v>
+        <v>0.5016248251772675</v>
       </c>
       <c r="E571" t="n">
-        <v>-0.4903592408443059</v>
+        <v>-0.2424138339565349</v>
       </c>
       <c r="F571" t="n">
         <v>-0.7440386591338023</v>
       </c>
       <c r="G571" t="n">
-        <v>31.45833333333334</v>
+        <v>53.54166666666667</v>
       </c>
       <c r="H571" t="n">
-        <v>10.36070479944475</v>
+        <v>7.867850032105537</v>
       </c>
       <c r="I571" t="n">
-        <v>7.083333333333334</v>
+        <v>13.95833333333333</v>
       </c>
       <c r="J571" t="n">
-        <v>24.375</v>
+        <v>39.58333333333334</v>
       </c>
       <c r="K571" t="n">
-        <v>3.29925920988696</v>
+        <v>9.764456806147855</v>
       </c>
       <c r="L571" t="n">
-        <v>3.947023595902931</v>
+        <v>7.80483113141598</v>
       </c>
       <c r="M571" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N571" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O571" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 1430, 'value': -0.5931198565449496, 'amplitude': 0.1509188025888527, 'start_idx': 1423, 'end_idx': 1445, 'duration': 4.583333333333334, 'fwhm': 11.862355385494965, 'rise_time': 1.4583333333333335, 'decay_time': 3.125, 'auc': 0.6151570125653489}]</t>
         </is>
       </c>
       <c r="P571" t="n">
-        <v>0.8817370162805458</v>
+        <v>0.7212322578796561</v>
       </c>
       <c r="Q571" t="n">
-        <v>0.2905982905982906</v>
+        <v>0.3526315789473684</v>
       </c>
       <c r="R571" t="n">
-        <v>0.4821851439315137</v>
+        <v>0.4981332269840944</v>
       </c>
       <c r="S571" t="n">
-        <v>0.5773409680765692</v>
+        <v>0.6673370823779509</v>
       </c>
       <c r="T571" t="inlineStr">
         <is>
@@ -49572,40 +49572,40 @@
     </row>
     <row r="572">
       <c r="A572" t="n">
-        <v>1245</v>
+        <v>1680</v>
       </c>
       <c r="B572" t="n">
-        <v>1312</v>
+        <v>1705</v>
       </c>
       <c r="C572" t="n">
-        <v>1502</v>
+        <v>1769</v>
       </c>
       <c r="D572" t="n">
-        <v>0.5016248251772675</v>
+        <v>0.7363468569020046</v>
       </c>
       <c r="E572" t="n">
-        <v>-0.2424138339565349</v>
+        <v>-0.007691802231797707</v>
       </c>
       <c r="F572" t="n">
         <v>-0.7440386591338023</v>
       </c>
       <c r="G572" t="n">
-        <v>53.54166666666667</v>
+        <v>18.54166666666667</v>
       </c>
       <c r="H572" t="n">
-        <v>7.867850032105537</v>
+        <v>5.895705168881118</v>
       </c>
       <c r="I572" t="n">
-        <v>13.95833333333333</v>
+        <v>5.208333333333334</v>
       </c>
       <c r="J572" t="n">
-        <v>39.58333333333334</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="K572" t="n">
-        <v>9.764456806147855</v>
+        <v>6.367703066988182</v>
       </c>
       <c r="L572" t="n">
-        <v>7.80483113141598</v>
+        <v>11.45689484215248</v>
       </c>
       <c r="M572" t="inlineStr">
         <is>
@@ -49621,16 +49621,16 @@
         </is>
       </c>
       <c r="P572" t="n">
-        <v>0.7212322578796561</v>
+        <v>0.9712475934955064</v>
       </c>
       <c r="Q572" t="n">
-        <v>0.3526315789473684</v>
+        <v>0.390625</v>
       </c>
       <c r="R572" t="n">
-        <v>0.4981332269840944</v>
+        <v>0.2991137223079339</v>
       </c>
       <c r="S572" t="n">
-        <v>0.6673370823779509</v>
+        <v>0.9696923824202249</v>
       </c>
       <c r="T572" t="inlineStr">
         <is>
@@ -49658,65 +49658,65 @@
     </row>
     <row r="573">
       <c r="A573" t="n">
-        <v>1680</v>
+        <v>1919</v>
       </c>
       <c r="B573" t="n">
-        <v>1705</v>
+        <v>1961</v>
       </c>
       <c r="C573" t="n">
-        <v>1769</v>
+        <v>2055</v>
       </c>
       <c r="D573" t="n">
-        <v>0.7363468569020046</v>
+        <v>0.3390480460120024</v>
       </c>
       <c r="E573" t="n">
-        <v>-0.007691802231797707</v>
+        <v>-0.4049906131217999</v>
       </c>
       <c r="F573" t="n">
         <v>-0.7440386591338023</v>
       </c>
       <c r="G573" t="n">
-        <v>18.54166666666667</v>
+        <v>28.33333333333334</v>
       </c>
       <c r="H573" t="n">
-        <v>5.895705168881118</v>
+        <v>7.078200324707733</v>
       </c>
       <c r="I573" t="n">
-        <v>5.208333333333334</v>
+        <v>8.75</v>
       </c>
       <c r="J573" t="n">
-        <v>13.33333333333333</v>
+        <v>19.58333333333334</v>
       </c>
       <c r="K573" t="n">
-        <v>6.367703066988182</v>
+        <v>6.582985615578804</v>
       </c>
       <c r="L573" t="n">
-        <v>11.45689484215248</v>
+        <v>5.27528266493808</v>
       </c>
       <c r="M573" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N573" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O573" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 2035, 'value': -0.528821180869044, 'amplitude': 0.21521747826475834, 'start_idx': 2025, 'end_idx': 2054, 'duration': 6.041666666666667, 'fwhm': 2.385770583175647, 'rise_time': 2.0833333333333335, 'decay_time': 3.9583333333333335, 'auc': 0.9603196670880134}]</t>
         </is>
       </c>
       <c r="P573" t="n">
-        <v>0.9712475934955064</v>
+        <v>0.7550178490270745</v>
       </c>
       <c r="Q573" t="n">
-        <v>0.390625</v>
+        <v>0.4468085106382978</v>
       </c>
       <c r="R573" t="n">
-        <v>0.2991137223079339</v>
+        <v>0.2371839426397572</v>
       </c>
       <c r="S573" t="n">
-        <v>0.9696923824202249</v>
+        <v>0.7902337359632097</v>
       </c>
       <c r="T573" t="inlineStr">
         <is>
@@ -49744,40 +49744,40 @@
     </row>
     <row r="574">
       <c r="A574" t="n">
-        <v>1919</v>
+        <v>2293</v>
       </c>
       <c r="B574" t="n">
-        <v>1961</v>
+        <v>2309</v>
       </c>
       <c r="C574" t="n">
-        <v>2055</v>
+        <v>2346</v>
       </c>
       <c r="D574" t="n">
-        <v>0.3390480460120024</v>
+        <v>0.5086034297776008</v>
       </c>
       <c r="E574" t="n">
-        <v>-0.4049906131217999</v>
+        <v>-0.2354352293562015</v>
       </c>
       <c r="F574" t="n">
         <v>-0.7440386591338023</v>
       </c>
       <c r="G574" t="n">
-        <v>28.33333333333334</v>
+        <v>11.04166666666667</v>
       </c>
       <c r="H574" t="n">
-        <v>7.078200324707733</v>
+        <v>4.565850960259089</v>
       </c>
       <c r="I574" t="n">
-        <v>8.75</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="J574" t="n">
-        <v>19.58333333333334</v>
+        <v>7.708333333333334</v>
       </c>
       <c r="K574" t="n">
-        <v>6.582985615578804</v>
+        <v>4.792319332739643</v>
       </c>
       <c r="L574" t="n">
-        <v>5.27528266493808</v>
+        <v>7.913411942621398</v>
       </c>
       <c r="M574" t="inlineStr">
         <is>
@@ -49793,16 +49793,16 @@
         </is>
       </c>
       <c r="P574" t="n">
-        <v>0.7550178490270745</v>
+        <v>0.8356923857436556</v>
       </c>
       <c r="Q574" t="n">
-        <v>0.4468085106382978</v>
+        <v>0.4324324324324324</v>
       </c>
       <c r="R574" t="n">
-        <v>0.2371839426397572</v>
+        <v>0.1034710771320428</v>
       </c>
       <c r="S574" t="n">
-        <v>0.7902337359632097</v>
+        <v>0.9157791815522139</v>
       </c>
       <c r="T574" t="inlineStr">
         <is>
@@ -49830,40 +49830,40 @@
     </row>
     <row r="575">
       <c r="A575" t="n">
-        <v>2293</v>
+        <v>2346</v>
       </c>
       <c r="B575" t="n">
-        <v>2309</v>
+        <v>2369</v>
       </c>
       <c r="C575" t="n">
-        <v>2346</v>
+        <v>2404</v>
       </c>
       <c r="D575" t="n">
-        <v>0.5086034297776008</v>
+        <v>0.416453545844842</v>
       </c>
       <c r="E575" t="n">
-        <v>-0.2354352293562015</v>
+        <v>-0.3275851132889603</v>
       </c>
       <c r="F575" t="n">
         <v>-0.7440386591338023</v>
       </c>
       <c r="G575" t="n">
-        <v>11.04166666666667</v>
+        <v>12.08333333333333</v>
       </c>
       <c r="H575" t="n">
-        <v>4.565850960259089</v>
+        <v>3.559016538137788</v>
       </c>
       <c r="I575" t="n">
-        <v>3.333333333333333</v>
+        <v>4.791666666666667</v>
       </c>
       <c r="J575" t="n">
-        <v>7.708333333333334</v>
+        <v>7.291666666666667</v>
       </c>
       <c r="K575" t="n">
-        <v>4.792319332739643</v>
+        <v>3.452362261063548</v>
       </c>
       <c r="L575" t="n">
-        <v>7.913411942621398</v>
+        <v>6.479642625840467</v>
       </c>
       <c r="M575" t="inlineStr">
         <is>
@@ -49879,16 +49879,16 @@
         </is>
       </c>
       <c r="P575" t="n">
-        <v>0.8356923857436556</v>
+        <v>0.87207398077958</v>
       </c>
       <c r="Q575" t="n">
-        <v>0.4324324324324324</v>
+        <v>0.6571428571428571</v>
       </c>
       <c r="R575" t="n">
-        <v>0.1034710771320428</v>
+        <v>0.2684395047469966</v>
       </c>
       <c r="S575" t="n">
-        <v>0.9157791815522139</v>
+        <v>0.9544210527387266</v>
       </c>
       <c r="T575" t="inlineStr">
         <is>
@@ -49916,40 +49916,40 @@
     </row>
     <row r="576">
       <c r="A576" t="n">
-        <v>2346</v>
+        <v>2615</v>
       </c>
       <c r="B576" t="n">
-        <v>2369</v>
+        <v>2649</v>
       </c>
       <c r="C576" t="n">
-        <v>2404</v>
+        <v>2684</v>
       </c>
       <c r="D576" t="n">
-        <v>0.416453545844842</v>
+        <v>0.4133403975706683</v>
       </c>
       <c r="E576" t="n">
-        <v>-0.3275851132889603</v>
+        <v>-0.330698261563134</v>
       </c>
       <c r="F576" t="n">
         <v>-0.7440386591338023</v>
       </c>
       <c r="G576" t="n">
-        <v>12.08333333333333</v>
+        <v>14.375</v>
       </c>
       <c r="H576" t="n">
-        <v>3.559016538137788</v>
+        <v>7.93582891902266</v>
       </c>
       <c r="I576" t="n">
-        <v>4.791666666666667</v>
+        <v>7.083333333333334</v>
       </c>
       <c r="J576" t="n">
         <v>7.291666666666667</v>
       </c>
       <c r="K576" t="n">
-        <v>3.452362261063548</v>
+        <v>4.902589055521458</v>
       </c>
       <c r="L576" t="n">
-        <v>6.479642625840467</v>
+        <v>6.431204838579045</v>
       </c>
       <c r="M576" t="inlineStr">
         <is>
@@ -49965,16 +49965,16 @@
         </is>
       </c>
       <c r="P576" t="n">
-        <v>0.87207398077958</v>
+        <v>0.6644775028352512</v>
       </c>
       <c r="Q576" t="n">
-        <v>0.6571428571428571</v>
+        <v>0.9714285714285714</v>
       </c>
       <c r="R576" t="n">
-        <v>0.2684395047469966</v>
+        <v>0.1764885531003928</v>
       </c>
       <c r="S576" t="n">
-        <v>0.9544210527387266</v>
+        <v>0.8783189386590415</v>
       </c>
       <c r="T576" t="inlineStr">
         <is>
@@ -50002,40 +50002,40 @@
     </row>
     <row r="577">
       <c r="A577" t="n">
-        <v>2615</v>
+        <v>2684</v>
       </c>
       <c r="B577" t="n">
-        <v>2649</v>
+        <v>2732</v>
       </c>
       <c r="C577" t="n">
-        <v>2684</v>
+        <v>2776</v>
       </c>
       <c r="D577" t="n">
-        <v>0.4133403975706683</v>
+        <v>0.5610662384727296</v>
       </c>
       <c r="E577" t="n">
-        <v>-0.330698261563134</v>
+        <v>-0.1829724206610726</v>
       </c>
       <c r="F577" t="n">
         <v>-0.7440386591338023</v>
       </c>
       <c r="G577" t="n">
-        <v>14.375</v>
+        <v>19.16666666666667</v>
       </c>
       <c r="H577" t="n">
-        <v>7.93582891902266</v>
+        <v>5.324959283421246</v>
       </c>
       <c r="I577" t="n">
-        <v>7.083333333333334</v>
+        <v>10</v>
       </c>
       <c r="J577" t="n">
-        <v>7.291666666666667</v>
+        <v>9.166666666666668</v>
       </c>
       <c r="K577" t="n">
-        <v>4.902589055521458</v>
+        <v>5.702901095148733</v>
       </c>
       <c r="L577" t="n">
-        <v>6.431204838579045</v>
+        <v>8.729686062229741</v>
       </c>
       <c r="M577" t="inlineStr">
         <is>
@@ -50051,16 +50051,16 @@
         </is>
       </c>
       <c r="P577" t="n">
-        <v>0.6644775028352512</v>
+        <v>0.6201667848000612</v>
       </c>
       <c r="Q577" t="n">
-        <v>0.9714285714285714</v>
+        <v>1.090909090909091</v>
       </c>
       <c r="R577" t="n">
-        <v>0.1764885531003928</v>
+        <v>0.1191806147639294</v>
       </c>
       <c r="S577" t="n">
-        <v>0.8783189386590415</v>
+        <v>0.6413597683253009</v>
       </c>
       <c r="T577" t="inlineStr">
         <is>
@@ -50088,40 +50088,40 @@
     </row>
     <row r="578">
       <c r="A578" t="n">
-        <v>2684</v>
+        <v>2776</v>
       </c>
       <c r="B578" t="n">
-        <v>2732</v>
+        <v>2794</v>
       </c>
       <c r="C578" t="n">
-        <v>2776</v>
+        <v>2855</v>
       </c>
       <c r="D578" t="n">
-        <v>0.5610662384727296</v>
+        <v>0.3181093485105539</v>
       </c>
       <c r="E578" t="n">
-        <v>-0.1829724206610726</v>
+        <v>-0.4259293106232483</v>
       </c>
       <c r="F578" t="n">
         <v>-0.7440386591338023</v>
       </c>
       <c r="G578" t="n">
-        <v>19.16666666666667</v>
+        <v>16.45833333333334</v>
       </c>
       <c r="H578" t="n">
-        <v>5.324959283421246</v>
+        <v>4.009458118274931</v>
       </c>
       <c r="I578" t="n">
-        <v>10</v>
+        <v>3.75</v>
       </c>
       <c r="J578" t="n">
-        <v>9.166666666666668</v>
+        <v>12.70833333333333</v>
       </c>
       <c r="K578" t="n">
-        <v>5.702901095148733</v>
+        <v>3.878113096083214</v>
       </c>
       <c r="L578" t="n">
-        <v>8.729686062229741</v>
+        <v>4.949495363536369</v>
       </c>
       <c r="M578" t="inlineStr">
         <is>
@@ -50137,16 +50137,16 @@
         </is>
       </c>
       <c r="P578" t="n">
-        <v>0.6201667848000612</v>
+        <v>0.9262080855775082</v>
       </c>
       <c r="Q578" t="n">
-        <v>1.090909090909091</v>
+        <v>0.2950819672131147</v>
       </c>
       <c r="R578" t="n">
-        <v>0.1191806147639294</v>
+        <v>0.1651500566959223</v>
       </c>
       <c r="S578" t="n">
-        <v>0.6413597683253009</v>
+        <v>0.9319351977972037</v>
       </c>
       <c r="T578" t="inlineStr">
         <is>
@@ -50174,69 +50174,69 @@
     </row>
     <row r="579">
       <c r="A579" t="n">
-        <v>2776</v>
+        <v>1350</v>
       </c>
       <c r="B579" t="n">
-        <v>2794</v>
+        <v>1438</v>
       </c>
       <c r="C579" t="n">
-        <v>2855</v>
+        <v>1547</v>
       </c>
       <c r="D579" t="n">
-        <v>0.3181093485105539</v>
+        <v>0.2668638351902223</v>
       </c>
       <c r="E579" t="n">
-        <v>-0.4259293106232483</v>
+        <v>-0.5734463563477037</v>
       </c>
       <c r="F579" t="n">
-        <v>-0.7440386591338023</v>
+        <v>-0.840310191537926</v>
       </c>
       <c r="G579" t="n">
-        <v>16.45833333333334</v>
+        <v>41.04166666666667</v>
       </c>
       <c r="H579" t="n">
-        <v>4.009458118274931</v>
+        <v>6.888304934578855</v>
       </c>
       <c r="I579" t="n">
-        <v>3.75</v>
+        <v>18.33333333333334</v>
       </c>
       <c r="J579" t="n">
-        <v>12.70833333333333</v>
+        <v>22.70833333333334</v>
       </c>
       <c r="K579" t="n">
-        <v>3.878113096083214</v>
+        <v>6.182248094875266</v>
       </c>
       <c r="L579" t="n">
-        <v>4.949495363536369</v>
+        <v>4.0076104357901</v>
       </c>
       <c r="M579" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N579" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O579" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 1373, 'value': -0.6492477119549819, 'amplitude': 0.1910624795829441, 'start_idx': 1351, 'end_idx': 1379, 'duration': 5.833333333333334, 'fwhm': 4.397556323627802, 'rise_time': 4.583333333333334, 'decay_time': 1.25, 'auc': 0.729416438881443}, {'index': 1525, 'value': -0.6761250232989396, 'amplitude': 0.16418516823898632, 'start_idx': 1503, 'end_idx': 1546, 'duration': 8.958333333333334, 'fwhm': 4.303879617628894, 'rise_time': 4.583333333333334, 'decay_time': 4.375, 'auc': 1.1561239068771008}]</t>
         </is>
       </c>
       <c r="P579" t="n">
-        <v>0.9262080855775082</v>
+        <v>0.5203565353359801</v>
       </c>
       <c r="Q579" t="n">
-        <v>0.2950819672131147</v>
+        <v>0.8073394495412844</v>
       </c>
       <c r="R579" t="n">
-        <v>0.1651500566959223</v>
+        <v>0.2214711151327791</v>
       </c>
       <c r="S579" t="n">
-        <v>0.9319351977972037</v>
+        <v>0.5518931632595974</v>
       </c>
       <c r="T579" t="inlineStr">
         <is>
-          <t>n56</t>
+          <t>n57</t>
         </is>
       </c>
       <c r="U579" t="n">
@@ -50260,65 +50260,65 @@
     </row>
     <row r="580">
       <c r="A580" t="n">
-        <v>1350</v>
+        <v>1611</v>
       </c>
       <c r="B580" t="n">
-        <v>1438</v>
+        <v>1653</v>
       </c>
       <c r="C580" t="n">
-        <v>1547</v>
+        <v>1781</v>
       </c>
       <c r="D580" t="n">
-        <v>0.2668638351902223</v>
+        <v>0.2832346750260767</v>
       </c>
       <c r="E580" t="n">
-        <v>-0.5734463563477037</v>
+        <v>-0.5570755165118493</v>
       </c>
       <c r="F580" t="n">
         <v>-0.840310191537926</v>
       </c>
       <c r="G580" t="n">
-        <v>41.04166666666667</v>
+        <v>35.41666666666667</v>
       </c>
       <c r="H580" t="n">
-        <v>6.888304934578855</v>
+        <v>12.63776088927112</v>
       </c>
       <c r="I580" t="n">
-        <v>18.33333333333334</v>
+        <v>8.75</v>
       </c>
       <c r="J580" t="n">
-        <v>22.70833333333334</v>
+        <v>26.66666666666667</v>
       </c>
       <c r="K580" t="n">
-        <v>6.182248094875266</v>
+        <v>6.773084906362675</v>
       </c>
       <c r="L580" t="n">
-        <v>4.0076104357901</v>
+        <v>4.253458467322933</v>
       </c>
       <c r="M580" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N580" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O580" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 1753, 'value': -0.6400456060531909, 'amplitude': 0.20026458548473502, 'start_idx': 1746, 'end_idx': 1776, 'duration': 6.25, 'fwhm': 4.759454113950502, 'rise_time': 1.4583333333333335, 'decay_time': 4.791666666666667, 'auc': 0.9557886448112007}]</t>
         </is>
       </c>
       <c r="P580" t="n">
-        <v>0.5203565353359801</v>
+        <v>0.7746020436986513</v>
       </c>
       <c r="Q580" t="n">
-        <v>0.8073394495412844</v>
+        <v>0.328125</v>
       </c>
       <c r="R580" t="n">
-        <v>0.2214711151327791</v>
+        <v>0.2525705376361567</v>
       </c>
       <c r="S580" t="n">
-        <v>0.5518931632595974</v>
+        <v>0.523648853114832</v>
       </c>
       <c r="T580" t="inlineStr">
         <is>
@@ -50346,40 +50346,40 @@
     </row>
     <row r="581">
       <c r="A581" t="n">
-        <v>1611</v>
+        <v>2151</v>
       </c>
       <c r="B581" t="n">
-        <v>1653</v>
+        <v>2177</v>
       </c>
       <c r="C581" t="n">
-        <v>1781</v>
+        <v>2203</v>
       </c>
       <c r="D581" t="n">
-        <v>0.2832346750260767</v>
+        <v>0.2741493266007593</v>
       </c>
       <c r="E581" t="n">
-        <v>-0.5570755165118493</v>
+        <v>-0.5661608649371667</v>
       </c>
       <c r="F581" t="n">
         <v>-0.840310191537926</v>
       </c>
       <c r="G581" t="n">
-        <v>35.41666666666667</v>
+        <v>10.83333333333333</v>
       </c>
       <c r="H581" t="n">
-        <v>12.63776088927112</v>
+        <v>4.66232734126597</v>
       </c>
       <c r="I581" t="n">
-        <v>8.75</v>
+        <v>5.416666666666667</v>
       </c>
       <c r="J581" t="n">
-        <v>26.66666666666667</v>
+        <v>5.416666666666667</v>
       </c>
       <c r="K581" t="n">
-        <v>6.773084906362675</v>
+        <v>2.298640072121085</v>
       </c>
       <c r="L581" t="n">
-        <v>4.253458467322933</v>
+        <v>4.11701983323024</v>
       </c>
       <c r="M581" t="inlineStr">
         <is>
@@ -50395,16 +50395,16 @@
         </is>
       </c>
       <c r="P581" t="n">
-        <v>0.7746020436986513</v>
+        <v>0.6725673433570081</v>
       </c>
       <c r="Q581" t="n">
-        <v>0.328125</v>
+        <v>1</v>
       </c>
       <c r="R581" t="n">
-        <v>0.2525705376361567</v>
+        <v>0.09696772478686708</v>
       </c>
       <c r="S581" t="n">
-        <v>0.523648853114832</v>
+        <v>0.9040977530706502</v>
       </c>
       <c r="T581" t="inlineStr">
         <is>
@@ -50432,40 +50432,40 @@
     </row>
     <row r="582">
       <c r="A582" t="n">
-        <v>2151</v>
+        <v>2341</v>
       </c>
       <c r="B582" t="n">
-        <v>2177</v>
+        <v>2356</v>
       </c>
       <c r="C582" t="n">
-        <v>2203</v>
+        <v>2414</v>
       </c>
       <c r="D582" t="n">
-        <v>0.2741493266007593</v>
+        <v>0.3263169856702152</v>
       </c>
       <c r="E582" t="n">
-        <v>-0.5661608649371667</v>
+        <v>-0.5139932058677108</v>
       </c>
       <c r="F582" t="n">
         <v>-0.840310191537926</v>
       </c>
       <c r="G582" t="n">
-        <v>10.83333333333333</v>
+        <v>15.20833333333333</v>
       </c>
       <c r="H582" t="n">
-        <v>4.66232734126597</v>
+        <v>4.600008772610428</v>
       </c>
       <c r="I582" t="n">
-        <v>5.416666666666667</v>
+        <v>3.125</v>
       </c>
       <c r="J582" t="n">
-        <v>5.416666666666667</v>
+        <v>12.08333333333333</v>
       </c>
       <c r="K582" t="n">
-        <v>2.298640072121085</v>
+        <v>3.835384638528987</v>
       </c>
       <c r="L582" t="n">
-        <v>4.11701983323024</v>
+        <v>4.900444289183467</v>
       </c>
       <c r="M582" t="inlineStr">
         <is>
@@ -50481,16 +50481,16 @@
         </is>
       </c>
       <c r="P582" t="n">
-        <v>0.6725673433570081</v>
+        <v>0.8842656932305857</v>
       </c>
       <c r="Q582" t="n">
-        <v>1</v>
+        <v>0.2586206896551724</v>
       </c>
       <c r="R582" t="n">
-        <v>0.09696772478686708</v>
+        <v>0.1188251485255735</v>
       </c>
       <c r="S582" t="n">
-        <v>0.9040977530706502</v>
+        <v>0.8777518048053561</v>
       </c>
       <c r="T582" t="inlineStr">
         <is>
@@ -50518,40 +50518,40 @@
     </row>
     <row r="583">
       <c r="A583" t="n">
-        <v>2341</v>
+        <v>2753</v>
       </c>
       <c r="B583" t="n">
-        <v>2356</v>
+        <v>2797</v>
       </c>
       <c r="C583" t="n">
-        <v>2414</v>
+        <v>2851</v>
       </c>
       <c r="D583" t="n">
-        <v>0.3263169856702152</v>
+        <v>0.4037205204370691</v>
       </c>
       <c r="E583" t="n">
-        <v>-0.5139932058677108</v>
+        <v>-0.4365896711008569</v>
       </c>
       <c r="F583" t="n">
         <v>-0.840310191537926</v>
       </c>
       <c r="G583" t="n">
-        <v>15.20833333333333</v>
+        <v>20.41666666666667</v>
       </c>
       <c r="H583" t="n">
-        <v>4.600008772610428</v>
+        <v>5.322326797963703</v>
       </c>
       <c r="I583" t="n">
-        <v>3.125</v>
+        <v>9.166666666666668</v>
       </c>
       <c r="J583" t="n">
-        <v>12.08333333333333</v>
+        <v>11.25</v>
       </c>
       <c r="K583" t="n">
-        <v>3.835384638528987</v>
+        <v>6.247208321455605</v>
       </c>
       <c r="L583" t="n">
-        <v>4.900444289183467</v>
+        <v>6.062846881042985</v>
       </c>
       <c r="M583" t="inlineStr">
         <is>
@@ -50567,16 +50567,16 @@
         </is>
       </c>
       <c r="P583" t="n">
-        <v>0.8842656932305857</v>
+        <v>0.6742497396248555</v>
       </c>
       <c r="Q583" t="n">
-        <v>0.2586206896551724</v>
+        <v>0.8148148148148149</v>
       </c>
       <c r="R583" t="n">
-        <v>0.1188251485255735</v>
+        <v>0.2149375722401525</v>
       </c>
       <c r="S583" t="n">
-        <v>0.8777518048053561</v>
+        <v>0.9918302764998222</v>
       </c>
       <c r="T583" t="inlineStr">
         <is>
@@ -50604,40 +50604,40 @@
     </row>
     <row r="584">
       <c r="A584" t="n">
-        <v>2753</v>
+        <v>2851</v>
       </c>
       <c r="B584" t="n">
-        <v>2797</v>
+        <v>2891</v>
       </c>
       <c r="C584" t="n">
-        <v>2851</v>
+        <v>2998</v>
       </c>
       <c r="D584" t="n">
-        <v>0.4037205204370691</v>
+        <v>0.2766500523733403</v>
       </c>
       <c r="E584" t="n">
-        <v>-0.4365896711008569</v>
+        <v>-0.5636601391645857</v>
       </c>
       <c r="F584" t="n">
         <v>-0.840310191537926</v>
       </c>
       <c r="G584" t="n">
-        <v>20.41666666666667</v>
+        <v>30.625</v>
       </c>
       <c r="H584" t="n">
-        <v>5.322326797963703</v>
+        <v>8.769044739557614</v>
       </c>
       <c r="I584" t="n">
-        <v>9.166666666666668</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="J584" t="n">
-        <v>11.25</v>
+        <v>22.29166666666667</v>
       </c>
       <c r="K584" t="n">
-        <v>6.247208321455605</v>
+        <v>8.176434069855384</v>
       </c>
       <c r="L584" t="n">
-        <v>6.062846881042985</v>
+        <v>4.15457432125632</v>
       </c>
       <c r="M584" t="inlineStr">
         <is>
@@ -50653,16 +50653,16 @@
         </is>
       </c>
       <c r="P584" t="n">
-        <v>0.6742497396248555</v>
+        <v>0.7362821834706195</v>
       </c>
       <c r="Q584" t="n">
-        <v>0.8148148148148149</v>
+        <v>0.3738317757009346</v>
       </c>
       <c r="R584" t="n">
-        <v>0.2149375722401525</v>
+        <v>0.3990351251286113</v>
       </c>
       <c r="S584" t="n">
-        <v>0.9918302764998222</v>
+        <v>0.6998511341478861</v>
       </c>
       <c r="T584" t="inlineStr">
         <is>
@@ -50690,40 +50690,40 @@
     </row>
     <row r="585">
       <c r="A585" t="n">
-        <v>2851</v>
+        <v>1048</v>
       </c>
       <c r="B585" t="n">
-        <v>2891</v>
+        <v>1061</v>
       </c>
       <c r="C585" t="n">
-        <v>2998</v>
+        <v>1132</v>
       </c>
       <c r="D585" t="n">
-        <v>0.2766500523733403</v>
+        <v>0.40869226103031</v>
       </c>
       <c r="E585" t="n">
-        <v>-0.5636601391645857</v>
+        <v>-0.4483457761066572</v>
       </c>
       <c r="F585" t="n">
-        <v>-0.840310191537926</v>
+        <v>-0.8570380371369672</v>
       </c>
       <c r="G585" t="n">
-        <v>30.625</v>
+        <v>17.5</v>
       </c>
       <c r="H585" t="n">
-        <v>8.769044739557614</v>
+        <v>1.934788194893808</v>
       </c>
       <c r="I585" t="n">
-        <v>8.333333333333334</v>
+        <v>2.708333333333333</v>
       </c>
       <c r="J585" t="n">
-        <v>22.29166666666667</v>
+        <v>14.79166666666667</v>
       </c>
       <c r="K585" t="n">
-        <v>8.176434069855384</v>
+        <v>3.669859151469889</v>
       </c>
       <c r="L585" t="n">
-        <v>4.15457432125632</v>
+        <v>8.293769682013847</v>
       </c>
       <c r="M585" t="inlineStr">
         <is>
@@ -50739,20 +50739,20 @@
         </is>
       </c>
       <c r="P585" t="n">
-        <v>0.7362821834706195</v>
+        <v>0.7337665256293577</v>
       </c>
       <c r="Q585" t="n">
-        <v>0.3738317757009346</v>
+        <v>0.1830985915492958</v>
       </c>
       <c r="R585" t="n">
-        <v>0.3990351251286113</v>
+        <v>0.5108232812598075</v>
       </c>
       <c r="S585" t="n">
-        <v>0.6998511341478861</v>
+        <v>0.5662629422754384</v>
       </c>
       <c r="T585" t="inlineStr">
         <is>
-          <t>n57</t>
+          <t>n58</t>
         </is>
       </c>
       <c r="U585" t="n">
@@ -50776,40 +50776,40 @@
     </row>
     <row r="586">
       <c r="A586" t="n">
-        <v>1048</v>
+        <v>1132</v>
       </c>
       <c r="B586" t="n">
-        <v>1061</v>
+        <v>1194</v>
       </c>
       <c r="C586" t="n">
-        <v>1132</v>
+        <v>1251</v>
       </c>
       <c r="D586" t="n">
-        <v>0.40869226103031</v>
+        <v>0.3760546833141346</v>
       </c>
       <c r="E586" t="n">
-        <v>-0.4483457761066572</v>
+        <v>-0.4809833538228326</v>
       </c>
       <c r="F586" t="n">
         <v>-0.8570380371369672</v>
       </c>
       <c r="G586" t="n">
-        <v>17.5</v>
+        <v>24.79166666666667</v>
       </c>
       <c r="H586" t="n">
-        <v>1.934788194893808</v>
+        <v>7.517079882770807</v>
       </c>
       <c r="I586" t="n">
-        <v>2.708333333333333</v>
+        <v>12.91666666666667</v>
       </c>
       <c r="J586" t="n">
-        <v>14.79166666666667</v>
+        <v>11.875</v>
       </c>
       <c r="K586" t="n">
-        <v>3.669859151469889</v>
+        <v>5.255146222184858</v>
       </c>
       <c r="L586" t="n">
-        <v>8.293769682013847</v>
+        <v>7.631441132228288</v>
       </c>
       <c r="M586" t="inlineStr">
         <is>
@@ -50825,16 +50825,16 @@
         </is>
       </c>
       <c r="P586" t="n">
-        <v>0.7337665256293577</v>
+        <v>0.7349957319133514</v>
       </c>
       <c r="Q586" t="n">
-        <v>0.1830985915492958</v>
+        <v>1.087719298245614</v>
       </c>
       <c r="R586" t="n">
-        <v>0.5108232812598075</v>
+        <v>0.2082654388107564</v>
       </c>
       <c r="S586" t="n">
-        <v>0.5662629422754384</v>
+        <v>0.9827047648370151</v>
       </c>
       <c r="T586" t="inlineStr">
         <is>
@@ -50862,65 +50862,65 @@
     </row>
     <row r="587">
       <c r="A587" t="n">
-        <v>1132</v>
+        <v>1251</v>
       </c>
       <c r="B587" t="n">
-        <v>1194</v>
+        <v>1305</v>
       </c>
       <c r="C587" t="n">
-        <v>1251</v>
+        <v>1472</v>
       </c>
       <c r="D587" t="n">
-        <v>0.3760546833141346</v>
+        <v>0.280032212844918</v>
       </c>
       <c r="E587" t="n">
-        <v>-0.4809833538228326</v>
+        <v>-0.5770058242920493</v>
       </c>
       <c r="F587" t="n">
         <v>-0.8570380371369672</v>
       </c>
       <c r="G587" t="n">
-        <v>24.79166666666667</v>
+        <v>46.04166666666667</v>
       </c>
       <c r="H587" t="n">
-        <v>7.517079882770807</v>
+        <v>7.815206340962912</v>
       </c>
       <c r="I587" t="n">
-        <v>12.91666666666667</v>
+        <v>11.25</v>
       </c>
       <c r="J587" t="n">
-        <v>11.875</v>
+        <v>34.79166666666667</v>
       </c>
       <c r="K587" t="n">
-        <v>5.255146222184858</v>
+        <v>6.992350888734775</v>
       </c>
       <c r="L587" t="n">
-        <v>7.631441132228288</v>
+        <v>5.682815404983122</v>
       </c>
       <c r="M587" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N587" t="n">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c r="O587" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 1366, 'value': -0.7057196651860622, 'amplitude': 0.15131837195090503, 'start_idx': 1356, 'end_idx': 1386, 'duration': 6.25, 'fwhm': 4.936368248875359, 'rise_time': 2.0833333333333335, 'decay_time': 4.166666666666667, 'auc': 0.7962620564183384}, {'index': 1455, 'value': -0.6986872358350829, 'amplitude': 0.1583508013018844, 'start_idx': 1444, 'end_idx': 1471, 'duration': 5.625, 'fwhm': 5.093454739934202, 'rise_time': 2.291666666666667, 'decay_time': 3.3333333333333335, 'auc': 0.7020242622802619}]</t>
         </is>
       </c>
       <c r="P587" t="n">
-        <v>0.7349957319133514</v>
+        <v>0.6617274930946968</v>
       </c>
       <c r="Q587" t="n">
-        <v>1.087719298245614</v>
+        <v>0.3233532934131736</v>
       </c>
       <c r="R587" t="n">
-        <v>0.2082654388107564</v>
+        <v>0.3799184034579211</v>
       </c>
       <c r="S587" t="n">
-        <v>0.9827047648370151</v>
+        <v>0.2229300754165039</v>
       </c>
       <c r="T587" t="inlineStr">
         <is>
@@ -50948,40 +50948,40 @@
     </row>
     <row r="588">
       <c r="A588" t="n">
-        <v>1251</v>
+        <v>1682</v>
       </c>
       <c r="B588" t="n">
-        <v>1305</v>
+        <v>1701</v>
       </c>
       <c r="C588" t="n">
-        <v>1472</v>
+        <v>1773</v>
       </c>
       <c r="D588" t="n">
-        <v>0.280032212844918</v>
+        <v>0.226091271036282</v>
       </c>
       <c r="E588" t="n">
-        <v>-0.5770058242920493</v>
+        <v>-0.6309467661006852</v>
       </c>
       <c r="F588" t="n">
         <v>-0.8570380371369672</v>
       </c>
       <c r="G588" t="n">
-        <v>46.04166666666667</v>
+        <v>18.95833333333334</v>
       </c>
       <c r="H588" t="n">
-        <v>7.815206340962912</v>
+        <v>5.72892962486525</v>
       </c>
       <c r="I588" t="n">
-        <v>11.25</v>
+        <v>3.958333333333333</v>
       </c>
       <c r="J588" t="n">
-        <v>34.79166666666667</v>
+        <v>15</v>
       </c>
       <c r="K588" t="n">
-        <v>6.992350888734775</v>
+        <v>2.387803535884214</v>
       </c>
       <c r="L588" t="n">
-        <v>5.682815404983122</v>
+        <v>4.588168428639817</v>
       </c>
       <c r="M588" t="inlineStr">
         <is>
@@ -50997,16 +50997,16 @@
         </is>
       </c>
       <c r="P588" t="n">
-        <v>0.6617274930946968</v>
+        <v>0.8967791138345889</v>
       </c>
       <c r="Q588" t="n">
-        <v>0.3233532934131736</v>
+        <v>0.2638888888888889</v>
       </c>
       <c r="R588" t="n">
-        <v>0.3799184034579211</v>
+        <v>0.3700144217814291</v>
       </c>
       <c r="S588" t="n">
-        <v>0.2229300754165039</v>
+        <v>0.7373855466765927</v>
       </c>
       <c r="T588" t="inlineStr">
         <is>
@@ -51034,40 +51034,40 @@
     </row>
     <row r="589">
       <c r="A589" t="n">
-        <v>1682</v>
+        <v>1978</v>
       </c>
       <c r="B589" t="n">
-        <v>1701</v>
+        <v>2002</v>
       </c>
       <c r="C589" t="n">
-        <v>1773</v>
+        <v>2047</v>
       </c>
       <c r="D589" t="n">
-        <v>0.226091271036282</v>
+        <v>0.2271991232330727</v>
       </c>
       <c r="E589" t="n">
-        <v>-0.6309467661006852</v>
+        <v>-0.6298389139038946</v>
       </c>
       <c r="F589" t="n">
         <v>-0.8570380371369672</v>
       </c>
       <c r="G589" t="n">
-        <v>18.95833333333334</v>
+        <v>14.375</v>
       </c>
       <c r="H589" t="n">
-        <v>5.72892962486525</v>
+        <v>31.56299128919254</v>
       </c>
       <c r="I589" t="n">
-        <v>3.958333333333333</v>
+        <v>5</v>
       </c>
       <c r="J589" t="n">
-        <v>15</v>
+        <v>9.375</v>
       </c>
       <c r="K589" t="n">
-        <v>2.387803535884214</v>
+        <v>2.40536176099111</v>
       </c>
       <c r="L589" t="n">
-        <v>4.588168428639817</v>
+        <v>4.610650554772402</v>
       </c>
       <c r="M589" t="inlineStr">
         <is>
@@ -51083,16 +51083,16 @@
         </is>
       </c>
       <c r="P589" t="n">
-        <v>0.8967791138345889</v>
+        <v>0.7356687464254208</v>
       </c>
       <c r="Q589" t="n">
-        <v>0.2638888888888889</v>
+        <v>0.5333333333333333</v>
       </c>
       <c r="R589" t="n">
-        <v>0.3700144217814291</v>
+        <v>0.1860947034393419</v>
       </c>
       <c r="S589" t="n">
-        <v>0.7373855466765927</v>
+        <v>0.6959574947143137</v>
       </c>
       <c r="T589" t="inlineStr">
         <is>
@@ -51120,40 +51120,40 @@
     </row>
     <row r="590">
       <c r="A590" t="n">
-        <v>1978</v>
+        <v>2227</v>
       </c>
       <c r="B590" t="n">
-        <v>2002</v>
+        <v>2246</v>
       </c>
       <c r="C590" t="n">
-        <v>2047</v>
+        <v>2270</v>
       </c>
       <c r="D590" t="n">
-        <v>0.2271991232330727</v>
+        <v>0.3614276483097587</v>
       </c>
       <c r="E590" t="n">
-        <v>-0.6298389139038946</v>
+        <v>-0.4956103888272086</v>
       </c>
       <c r="F590" t="n">
         <v>-0.8570380371369672</v>
       </c>
       <c r="G590" t="n">
-        <v>14.375</v>
+        <v>8.958333333333334</v>
       </c>
       <c r="H590" t="n">
-        <v>31.56299128919254</v>
+        <v>7.323197088225868</v>
       </c>
       <c r="I590" t="n">
+        <v>3.958333333333333</v>
+      </c>
+      <c r="J590" t="n">
         <v>5</v>
       </c>
-      <c r="J590" t="n">
-        <v>9.375</v>
-      </c>
       <c r="K590" t="n">
-        <v>2.40536176099111</v>
+        <v>2.379461294531456</v>
       </c>
       <c r="L590" t="n">
-        <v>4.610650554772402</v>
+        <v>7.334608353571753</v>
       </c>
       <c r="M590" t="inlineStr">
         <is>
@@ -51169,16 +51169,16 @@
         </is>
       </c>
       <c r="P590" t="n">
-        <v>0.7356687464254208</v>
+        <v>0.7712430204211776</v>
       </c>
       <c r="Q590" t="n">
-        <v>0.5333333333333333</v>
+        <v>0.7916666666666667</v>
       </c>
       <c r="R590" t="n">
-        <v>0.1860947034393419</v>
+        <v>0.1361218789100436</v>
       </c>
       <c r="S590" t="n">
-        <v>0.6959574947143137</v>
+        <v>0.9050086308806369</v>
       </c>
       <c r="T590" t="inlineStr">
         <is>
@@ -51206,40 +51206,40 @@
     </row>
     <row r="591">
       <c r="A591" t="n">
-        <v>2227</v>
+        <v>2351</v>
       </c>
       <c r="B591" t="n">
-        <v>2246</v>
+        <v>2364</v>
       </c>
       <c r="C591" t="n">
-        <v>2270</v>
+        <v>2415</v>
       </c>
       <c r="D591" t="n">
-        <v>0.3614276483097587</v>
+        <v>0.2911431503050254</v>
       </c>
       <c r="E591" t="n">
-        <v>-0.4956103888272086</v>
+        <v>-0.5658948868319419</v>
       </c>
       <c r="F591" t="n">
         <v>-0.8570380371369672</v>
       </c>
       <c r="G591" t="n">
-        <v>8.958333333333334</v>
+        <v>13.33333333333333</v>
       </c>
       <c r="H591" t="n">
-        <v>7.323197088225868</v>
+        <v>2.706974714974232</v>
       </c>
       <c r="I591" t="n">
-        <v>3.958333333333333</v>
+        <v>2.708333333333333</v>
       </c>
       <c r="J591" t="n">
-        <v>5</v>
+        <v>10.625</v>
       </c>
       <c r="K591" t="n">
-        <v>2.379461294531456</v>
+        <v>2.740695989187971</v>
       </c>
       <c r="L591" t="n">
-        <v>7.334608353571753</v>
+        <v>5.908294487980871</v>
       </c>
       <c r="M591" t="inlineStr">
         <is>
@@ -51255,16 +51255,16 @@
         </is>
       </c>
       <c r="P591" t="n">
-        <v>0.7712430204211776</v>
+        <v>0.8936377034158568</v>
       </c>
       <c r="Q591" t="n">
-        <v>0.7916666666666667</v>
+        <v>0.2549019607843138</v>
       </c>
       <c r="R591" t="n">
-        <v>0.1361218789100436</v>
+        <v>0.1585782707760072</v>
       </c>
       <c r="S591" t="n">
-        <v>0.9050086308806369</v>
+        <v>0.945017734666963</v>
       </c>
       <c r="T591" t="inlineStr">
         <is>
@@ -51292,40 +51292,40 @@
     </row>
     <row r="592">
       <c r="A592" t="n">
-        <v>2351</v>
+        <v>2627</v>
       </c>
       <c r="B592" t="n">
-        <v>2364</v>
+        <v>2643</v>
       </c>
       <c r="C592" t="n">
-        <v>2415</v>
+        <v>2682</v>
       </c>
       <c r="D592" t="n">
-        <v>0.2911431503050254</v>
+        <v>0.1843859907370222</v>
       </c>
       <c r="E592" t="n">
-        <v>-0.5658948868319419</v>
+        <v>-0.672652046399945</v>
       </c>
       <c r="F592" t="n">
         <v>-0.8570380371369672</v>
       </c>
       <c r="G592" t="n">
-        <v>13.33333333333333</v>
+        <v>11.45833333333333</v>
       </c>
       <c r="H592" t="n">
-        <v>2.706974714974232</v>
+        <v>7.006270640082164</v>
       </c>
       <c r="I592" t="n">
-        <v>2.708333333333333</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="J592" t="n">
-        <v>10.625</v>
+        <v>8.125</v>
       </c>
       <c r="K592" t="n">
-        <v>2.740695989187971</v>
+        <v>1.455873098347241</v>
       </c>
       <c r="L592" t="n">
-        <v>5.908294487980871</v>
+        <v>3.741825049262154</v>
       </c>
       <c r="M592" t="inlineStr">
         <is>
@@ -51341,16 +51341,16 @@
         </is>
       </c>
       <c r="P592" t="n">
-        <v>0.8936377034158568</v>
+        <v>0.8331331828502974</v>
       </c>
       <c r="Q592" t="n">
-        <v>0.2549019607843138</v>
+        <v>0.4102564102564103</v>
       </c>
       <c r="R592" t="n">
-        <v>0.1585782707760072</v>
+        <v>0.1022426041386415</v>
       </c>
       <c r="S592" t="n">
-        <v>0.945017734666963</v>
+        <v>0.8394468866933462</v>
       </c>
       <c r="T592" t="inlineStr">
         <is>
@@ -51378,40 +51378,40 @@
     </row>
     <row r="593">
       <c r="A593" t="n">
-        <v>2627</v>
+        <v>917</v>
       </c>
       <c r="B593" t="n">
-        <v>2643</v>
+        <v>934</v>
       </c>
       <c r="C593" t="n">
-        <v>2682</v>
+        <v>957</v>
       </c>
       <c r="D593" t="n">
-        <v>0.1843859907370222</v>
+        <v>0.2534070400624904</v>
       </c>
       <c r="E593" t="n">
-        <v>-0.672652046399945</v>
+        <v>-0.6092356901517669</v>
       </c>
       <c r="F593" t="n">
-        <v>-0.8570380371369672</v>
+        <v>-0.8626427302142573</v>
       </c>
       <c r="G593" t="n">
-        <v>11.45833333333333</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="H593" t="n">
-        <v>7.006270640082164</v>
+        <v>3.456520548053751</v>
       </c>
       <c r="I593" t="n">
-        <v>3.333333333333333</v>
+        <v>3.541666666666667</v>
       </c>
       <c r="J593" t="n">
-        <v>8.125</v>
+        <v>4.791666666666667</v>
       </c>
       <c r="K593" t="n">
-        <v>1.455873098347241</v>
+        <v>1.747995573939692</v>
       </c>
       <c r="L593" t="n">
-        <v>3.741825049262154</v>
+        <v>4.853708743136406</v>
       </c>
       <c r="M593" t="inlineStr">
         <is>
@@ -51427,20 +51427,20 @@
         </is>
       </c>
       <c r="P593" t="n">
-        <v>0.8331331828502974</v>
+        <v>0.7781141817186308</v>
       </c>
       <c r="Q593" t="n">
-        <v>0.4102564102564103</v>
+        <v>0.7391304347826088</v>
       </c>
       <c r="R593" t="n">
-        <v>0.1022426041386415</v>
+        <v>0.09976577252319226</v>
       </c>
       <c r="S593" t="n">
-        <v>0.8394468866933462</v>
+        <v>0.954359344260464</v>
       </c>
       <c r="T593" t="inlineStr">
         <is>
-          <t>n58</t>
+          <t>n59</t>
         </is>
       </c>
       <c r="U593" t="n">
@@ -51464,65 +51464,65 @@
     </row>
     <row r="594">
       <c r="A594" t="n">
-        <v>917</v>
+        <v>957</v>
       </c>
       <c r="B594" t="n">
-        <v>934</v>
+        <v>1035</v>
       </c>
       <c r="C594" t="n">
-        <v>957</v>
+        <v>1237</v>
       </c>
       <c r="D594" t="n">
-        <v>0.2534070400624904</v>
+        <v>0.4860959729757399</v>
       </c>
       <c r="E594" t="n">
-        <v>-0.6092356901517669</v>
+        <v>-0.3765467572385174</v>
       </c>
       <c r="F594" t="n">
         <v>-0.8626427302142573</v>
       </c>
       <c r="G594" t="n">
-        <v>8.333333333333334</v>
+        <v>58.33333333333334</v>
       </c>
       <c r="H594" t="n">
-        <v>3.456520548053751</v>
+        <v>17.36979626268763</v>
       </c>
       <c r="I594" t="n">
-        <v>3.541666666666667</v>
+        <v>16.25</v>
       </c>
       <c r="J594" t="n">
-        <v>4.791666666666667</v>
+        <v>42.08333333333334</v>
       </c>
       <c r="K594" t="n">
-        <v>1.747995573939692</v>
+        <v>11.26751719620572</v>
       </c>
       <c r="L594" t="n">
-        <v>4.853708743136406</v>
+        <v>9.310586925501063</v>
       </c>
       <c r="M594" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N594" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O594" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 1185, 'value': -0.7187711162650636, 'amplitude': 0.14387161394919368, 'start_idx': 1176, 'end_idx': 1210, 'duration': 7.083333333333334, 'fwhm': 7.511999562666271, 'rise_time': 1.875, 'decay_time': 5.208333333333334, 'auc': 0.7111766124619554}]</t>
         </is>
       </c>
       <c r="P594" t="n">
-        <v>0.7781141817186308</v>
+        <v>0.7769083905217075</v>
       </c>
       <c r="Q594" t="n">
-        <v>0.7391304347826088</v>
+        <v>0.3861386138613861</v>
       </c>
       <c r="R594" t="n">
-        <v>0.09976577252319226</v>
+        <v>0.5882875226275293</v>
       </c>
       <c r="S594" t="n">
-        <v>0.954359344260464</v>
+        <v>0.6511234276339903</v>
       </c>
       <c r="T594" t="inlineStr">
         <is>
@@ -51550,40 +51550,40 @@
     </row>
     <row r="595">
       <c r="A595" t="n">
-        <v>957</v>
+        <v>1627</v>
       </c>
       <c r="B595" t="n">
-        <v>1035</v>
+        <v>1645</v>
       </c>
       <c r="C595" t="n">
-        <v>1237</v>
+        <v>1685</v>
       </c>
       <c r="D595" t="n">
-        <v>0.4860959729757399</v>
+        <v>0.2144828826316727</v>
       </c>
       <c r="E595" t="n">
-        <v>-0.3765467572385174</v>
+        <v>-0.6481598475825846</v>
       </c>
       <c r="F595" t="n">
         <v>-0.8626427302142573</v>
       </c>
       <c r="G595" t="n">
-        <v>58.33333333333334</v>
+        <v>12.08333333333333</v>
       </c>
       <c r="H595" t="n">
-        <v>17.36979626268763</v>
+        <v>7.957774138087691</v>
       </c>
       <c r="I595" t="n">
-        <v>16.25</v>
+        <v>3.75</v>
       </c>
       <c r="J595" t="n">
-        <v>42.08333333333334</v>
+        <v>8.333333333333334</v>
       </c>
       <c r="K595" t="n">
-        <v>11.26751719620572</v>
+        <v>2.091281901648837</v>
       </c>
       <c r="L595" t="n">
-        <v>9.310586925501063</v>
+        <v>4.108163066131583</v>
       </c>
       <c r="M595" t="inlineStr">
         <is>
@@ -51599,16 +51599,16 @@
         </is>
       </c>
       <c r="P595" t="n">
-        <v>0.7769083905217075</v>
+        <v>0.8599816268480103</v>
       </c>
       <c r="Q595" t="n">
-        <v>0.3861386138613861</v>
+        <v>0.45</v>
       </c>
       <c r="R595" t="n">
-        <v>0.5882875226275293</v>
+        <v>0.2101302919879678</v>
       </c>
       <c r="S595" t="n">
-        <v>0.6511234276339903</v>
+        <v>0.7528732904644746</v>
       </c>
       <c r="T595" t="inlineStr">
         <is>
@@ -51636,40 +51636,40 @@
     </row>
     <row r="596">
       <c r="A596" t="n">
-        <v>1627</v>
+        <v>1685</v>
       </c>
       <c r="B596" t="n">
-        <v>1645</v>
+        <v>1730</v>
       </c>
       <c r="C596" t="n">
-        <v>1685</v>
+        <v>1779</v>
       </c>
       <c r="D596" t="n">
-        <v>0.2144828826316727</v>
+        <v>0.1977215811994103</v>
       </c>
       <c r="E596" t="n">
-        <v>-0.6481598475825846</v>
+        <v>-0.664921149014847</v>
       </c>
       <c r="F596" t="n">
         <v>-0.8626427302142573</v>
       </c>
       <c r="G596" t="n">
-        <v>12.08333333333333</v>
+        <v>19.58333333333334</v>
       </c>
       <c r="H596" t="n">
-        <v>7.957774138087691</v>
+        <v>9.534276874240438</v>
       </c>
       <c r="I596" t="n">
-        <v>3.75</v>
+        <v>9.375</v>
       </c>
       <c r="J596" t="n">
-        <v>8.333333333333334</v>
+        <v>10.20833333333333</v>
       </c>
       <c r="K596" t="n">
-        <v>2.091281901648837</v>
+        <v>3.088936418112243</v>
       </c>
       <c r="L596" t="n">
-        <v>4.108163066131583</v>
+        <v>3.787120385991147</v>
       </c>
       <c r="M596" t="inlineStr">
         <is>
@@ -51685,16 +51685,16 @@
         </is>
       </c>
       <c r="P596" t="n">
-        <v>0.8599816268480103</v>
+        <v>0.5450866640724161</v>
       </c>
       <c r="Q596" t="n">
-        <v>0.45</v>
+        <v>0.9183673469387754</v>
       </c>
       <c r="R596" t="n">
-        <v>0.2101302919879678</v>
+        <v>0.1255669487269128</v>
       </c>
       <c r="S596" t="n">
-        <v>0.7528732904644746</v>
+        <v>0.6923569823816983</v>
       </c>
       <c r="T596" t="inlineStr">
         <is>
@@ -51722,40 +51722,40 @@
     </row>
     <row r="597">
       <c r="A597" t="n">
-        <v>1685</v>
+        <v>1885</v>
       </c>
       <c r="B597" t="n">
-        <v>1730</v>
+        <v>1898</v>
       </c>
       <c r="C597" t="n">
-        <v>1779</v>
+        <v>1918</v>
       </c>
       <c r="D597" t="n">
-        <v>0.1977215811994103</v>
+        <v>0.2973374187198595</v>
       </c>
       <c r="E597" t="n">
-        <v>-0.664921149014847</v>
+        <v>-0.5653053114943978</v>
       </c>
       <c r="F597" t="n">
         <v>-0.8626427302142573</v>
       </c>
       <c r="G597" t="n">
-        <v>19.58333333333334</v>
+        <v>6.875</v>
       </c>
       <c r="H597" t="n">
-        <v>9.534276874240438</v>
+        <v>3.98284795891712</v>
       </c>
       <c r="I597" t="n">
-        <v>9.375</v>
+        <v>2.708333333333333</v>
       </c>
       <c r="J597" t="n">
-        <v>10.20833333333333</v>
+        <v>4.166666666666667</v>
       </c>
       <c r="K597" t="n">
-        <v>3.088936418112243</v>
+        <v>1.788283507760976</v>
       </c>
       <c r="L597" t="n">
-        <v>3.787120385991147</v>
+        <v>5.695142599614837</v>
       </c>
       <c r="M597" t="inlineStr">
         <is>
@@ -51771,16 +51771,16 @@
         </is>
       </c>
       <c r="P597" t="n">
-        <v>0.5450866640724161</v>
+        <v>0.7065759096364931</v>
       </c>
       <c r="Q597" t="n">
-        <v>0.9183673469387754</v>
+        <v>0.65</v>
       </c>
       <c r="R597" t="n">
-        <v>0.1255669487269128</v>
+        <v>0.05100453701200697</v>
       </c>
       <c r="S597" t="n">
-        <v>0.6923569823816983</v>
+        <v>0.9151060244586984</v>
       </c>
       <c r="T597" t="inlineStr">
         <is>
@@ -51808,65 +51808,65 @@
     </row>
     <row r="598">
       <c r="A598" t="n">
-        <v>1885</v>
+        <v>1980</v>
       </c>
       <c r="B598" t="n">
-        <v>1898</v>
+        <v>2004</v>
       </c>
       <c r="C598" t="n">
-        <v>1918</v>
+        <v>2054</v>
       </c>
       <c r="D598" t="n">
-        <v>0.2973374187198595</v>
+        <v>0.2967865439637819</v>
       </c>
       <c r="E598" t="n">
-        <v>-0.5653053114943978</v>
+        <v>-0.5658561862504754</v>
       </c>
       <c r="F598" t="n">
         <v>-0.8626427302142573</v>
       </c>
       <c r="G598" t="n">
-        <v>6.875</v>
+        <v>15.41666666666667</v>
       </c>
       <c r="H598" t="n">
-        <v>3.98284795891712</v>
+        <v>5.496396140875106</v>
       </c>
       <c r="I598" t="n">
-        <v>2.708333333333333</v>
+        <v>5</v>
       </c>
       <c r="J598" t="n">
-        <v>4.166666666666667</v>
+        <v>10.41666666666667</v>
       </c>
       <c r="K598" t="n">
-        <v>1.788283507760976</v>
+        <v>3.436191950704258</v>
       </c>
       <c r="L598" t="n">
-        <v>5.695142599614837</v>
+        <v>5.684591252583248</v>
       </c>
       <c r="M598" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N598" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O598" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 2036, 'value': -0.6404351935760523, 'amplitude': 0.22220753663820503, 'start_idx': 2024, 'end_idx': 2053, 'duration': 6.041666666666667, 'fwhm': 2.866565527100041, 'rise_time': 2.5, 'decay_time': 3.541666666666667, 'auc': 1.1402175288238443}]</t>
         </is>
       </c>
       <c r="P598" t="n">
-        <v>0.7065759096364931</v>
+        <v>0.7957921060460611</v>
       </c>
       <c r="Q598" t="n">
-        <v>0.65</v>
+        <v>0.4799999999999999</v>
       </c>
       <c r="R598" t="n">
-        <v>0.05100453701200697</v>
+        <v>0.2193464258570107</v>
       </c>
       <c r="S598" t="n">
-        <v>0.9151060244586984</v>
+        <v>0.5148466800099536</v>
       </c>
       <c r="T598" t="inlineStr">
         <is>
@@ -51894,40 +51894,40 @@
     </row>
     <row r="599">
       <c r="A599" t="n">
-        <v>1980</v>
+        <v>2228</v>
       </c>
       <c r="B599" t="n">
-        <v>2004</v>
+        <v>2245</v>
       </c>
       <c r="C599" t="n">
-        <v>2054</v>
+        <v>2261</v>
       </c>
       <c r="D599" t="n">
-        <v>0.2967865439637819</v>
+        <v>0.3369413617825155</v>
       </c>
       <c r="E599" t="n">
-        <v>-0.5658561862504754</v>
+        <v>-0.5257013684317418</v>
       </c>
       <c r="F599" t="n">
         <v>-0.8626427302142573</v>
       </c>
       <c r="G599" t="n">
-        <v>15.41666666666667</v>
+        <v>6.875</v>
       </c>
       <c r="H599" t="n">
-        <v>5.496396140875106</v>
+        <v>4.536665630850413</v>
       </c>
       <c r="I599" t="n">
-        <v>5</v>
+        <v>3.541666666666667</v>
       </c>
       <c r="J599" t="n">
-        <v>10.41666666666667</v>
+        <v>3.333333333333333</v>
       </c>
       <c r="K599" t="n">
-        <v>3.436191950704258</v>
+        <v>1.845093986338501</v>
       </c>
       <c r="L599" t="n">
-        <v>5.684591252583248</v>
+        <v>6.453708757281517</v>
       </c>
       <c r="M599" t="inlineStr">
         <is>
@@ -51943,16 +51943,16 @@
         </is>
       </c>
       <c r="P599" t="n">
-        <v>0.7957921060460611</v>
+        <v>0.6508779668646603</v>
       </c>
       <c r="Q599" t="n">
-        <v>0.4799999999999999</v>
+        <v>1.0625</v>
       </c>
       <c r="R599" t="n">
-        <v>0.2193464258570107</v>
+        <v>0.06400687655193975</v>
       </c>
       <c r="S599" t="n">
-        <v>0.5148466800099536</v>
+        <v>0.982257694493359</v>
       </c>
       <c r="T599" t="inlineStr">
         <is>
@@ -51980,65 +51980,65 @@
     </row>
     <row r="600">
       <c r="A600" t="n">
-        <v>2228</v>
+        <v>2261</v>
       </c>
       <c r="B600" t="n">
-        <v>2245</v>
+        <v>2300</v>
       </c>
       <c r="C600" t="n">
-        <v>2261</v>
+        <v>2343</v>
       </c>
       <c r="D600" t="n">
-        <v>0.3369413617825155</v>
+        <v>0.3190392469298157</v>
       </c>
       <c r="E600" t="n">
-        <v>-0.5257013684317418</v>
+        <v>-0.5436034832844416</v>
       </c>
       <c r="F600" t="n">
         <v>-0.8626427302142573</v>
       </c>
       <c r="G600" t="n">
-        <v>6.875</v>
+        <v>17.08333333333334</v>
       </c>
       <c r="H600" t="n">
-        <v>4.536665630850413</v>
+        <v>13.34638000506449</v>
       </c>
       <c r="I600" t="n">
-        <v>3.541666666666667</v>
+        <v>8.125</v>
       </c>
       <c r="J600" t="n">
-        <v>3.333333333333333</v>
+        <v>8.958333333333334</v>
       </c>
       <c r="K600" t="n">
-        <v>1.845093986338501</v>
+        <v>4.69635306590944</v>
       </c>
       <c r="L600" t="n">
-        <v>6.453708757281517</v>
+        <v>6.110815160640501</v>
       </c>
       <c r="M600" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N600" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O600" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 2327, 'value': -0.5525375630631009, 'amplitude': 0.31010516715115644, 'start_idx': 2310, 'end_idx': 2342, 'duration': 6.666666666666667, 'fwhm': 2.228157095880003, 'rise_time': 3.541666666666667, 'decay_time': 3.125, 'auc': 1.7825762034912476}]</t>
         </is>
       </c>
       <c r="P600" t="n">
-        <v>0.6508779668646603</v>
+        <v>0.419812390266923</v>
       </c>
       <c r="Q600" t="n">
-        <v>1.0625</v>
+        <v>0.9069767441860465</v>
       </c>
       <c r="R600" t="n">
-        <v>0.06400687655193975</v>
+        <v>0.06171507181313773</v>
       </c>
       <c r="S600" t="n">
-        <v>0.982257694493359</v>
+        <v>0.4229182076138047</v>
       </c>
       <c r="T600" t="inlineStr">
         <is>
@@ -52066,40 +52066,40 @@
     </row>
     <row r="601">
       <c r="A601" t="n">
-        <v>2261</v>
+        <v>2343</v>
       </c>
       <c r="B601" t="n">
-        <v>2300</v>
+        <v>2364</v>
       </c>
       <c r="C601" t="n">
-        <v>2343</v>
+        <v>2388</v>
       </c>
       <c r="D601" t="n">
-        <v>0.3190392469298157</v>
+        <v>0.304278463232433</v>
       </c>
       <c r="E601" t="n">
-        <v>-0.5436034832844416</v>
+        <v>-0.5583642669818243</v>
       </c>
       <c r="F601" t="n">
         <v>-0.8626427302142573</v>
       </c>
       <c r="G601" t="n">
-        <v>17.08333333333334</v>
+        <v>9.375</v>
       </c>
       <c r="H601" t="n">
-        <v>13.34638000506449</v>
+        <v>4.650489166162876</v>
       </c>
       <c r="I601" t="n">
-        <v>8.125</v>
+        <v>4.375</v>
       </c>
       <c r="J601" t="n">
-        <v>8.958333333333334</v>
+        <v>5</v>
       </c>
       <c r="K601" t="n">
-        <v>4.69635306590944</v>
+        <v>2.219107567417288</v>
       </c>
       <c r="L601" t="n">
-        <v>6.110815160640501</v>
+        <v>5.828090004820584</v>
       </c>
       <c r="M601" t="inlineStr">
         <is>
@@ -52115,16 +52115,16 @@
         </is>
       </c>
       <c r="P601" t="n">
-        <v>0.419812390266923</v>
+        <v>0.7896289460206104</v>
       </c>
       <c r="Q601" t="n">
-        <v>0.9069767441860465</v>
+        <v>0.875</v>
       </c>
       <c r="R601" t="n">
-        <v>0.06171507181313773</v>
+        <v>0.1359196940905952</v>
       </c>
       <c r="S601" t="n">
-        <v>0.4229182076138047</v>
+        <v>0.9738214357046353</v>
       </c>
       <c r="T601" t="inlineStr">
         <is>
@@ -52152,40 +52152,40 @@
     </row>
     <row r="602">
       <c r="A602" t="n">
-        <v>2343</v>
+        <v>2751</v>
       </c>
       <c r="B602" t="n">
-        <v>2364</v>
+        <v>2799</v>
       </c>
       <c r="C602" t="n">
-        <v>2388</v>
+        <v>2866</v>
       </c>
       <c r="D602" t="n">
-        <v>0.304278463232433</v>
+        <v>0.3655228136180082</v>
       </c>
       <c r="E602" t="n">
-        <v>-0.5583642669818243</v>
+        <v>-0.4971199165962491</v>
       </c>
       <c r="F602" t="n">
         <v>-0.8626427302142573</v>
       </c>
       <c r="G602" t="n">
-        <v>9.375</v>
+        <v>23.95833333333334</v>
       </c>
       <c r="H602" t="n">
-        <v>4.650489166162876</v>
+        <v>11.54913205885085</v>
       </c>
       <c r="I602" t="n">
-        <v>4.375</v>
+        <v>10</v>
       </c>
       <c r="J602" t="n">
-        <v>5</v>
+        <v>13.95833333333333</v>
       </c>
       <c r="K602" t="n">
-        <v>2.219107567417288</v>
+        <v>6.495178505103107</v>
       </c>
       <c r="L602" t="n">
-        <v>5.828090004820584</v>
+        <v>7.001152279889464</v>
       </c>
       <c r="M602" t="inlineStr">
         <is>
@@ -52201,16 +52201,16 @@
         </is>
       </c>
       <c r="P602" t="n">
-        <v>0.7896289460206104</v>
+        <v>0.7563299382572706</v>
       </c>
       <c r="Q602" t="n">
-        <v>0.875</v>
+        <v>0.7164179104477612</v>
       </c>
       <c r="R602" t="n">
-        <v>0.1359196940905952</v>
+        <v>0.2883087284547744</v>
       </c>
       <c r="S602" t="n">
-        <v>0.9738214357046353</v>
+        <v>0.9417904797208708</v>
       </c>
       <c r="T602" t="inlineStr">
         <is>
@@ -52238,65 +52238,65 @@
     </row>
     <row r="603">
       <c r="A603" t="n">
-        <v>2751</v>
+        <v>2866</v>
       </c>
       <c r="B603" t="n">
-        <v>2799</v>
+        <v>2896</v>
       </c>
       <c r="C603" t="n">
-        <v>2866</v>
+        <v>2998</v>
       </c>
       <c r="D603" t="n">
-        <v>0.3655228136180082</v>
+        <v>0.2331217290146543</v>
       </c>
       <c r="E603" t="n">
-        <v>-0.4971199165962491</v>
+        <v>-0.629521001199603</v>
       </c>
       <c r="F603" t="n">
         <v>-0.8626427302142573</v>
       </c>
       <c r="G603" t="n">
-        <v>23.95833333333334</v>
+        <v>27.5</v>
       </c>
       <c r="H603" t="n">
-        <v>11.54913205885085</v>
+        <v>3.54075774582905</v>
       </c>
       <c r="I603" t="n">
-        <v>10</v>
+        <v>6.25</v>
       </c>
       <c r="J603" t="n">
-        <v>13.95833333333333</v>
+        <v>21.25</v>
       </c>
       <c r="K603" t="n">
-        <v>6.495178505103107</v>
+        <v>5.299889778584411</v>
       </c>
       <c r="L603" t="n">
-        <v>7.001152279889464</v>
+        <v>4.465167874004107</v>
       </c>
       <c r="M603" t="inlineStr">
         <is>
-          <t>simple</t>
+          <t>complex</t>
         </is>
       </c>
       <c r="N603" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O603" t="inlineStr">
         <is>
-          <t>[]</t>
+          <t>[{'index': 2980, 'value': -0.6134868258957475, 'amplitude': 0.24915590431850976, 'start_idx': 2969, 'end_idx': 2982, 'duration': 2.7083333333333335, 'fwhm': 4.312425143981784, 'rise_time': 2.291666666666667, 'decay_time': 0.4166666666666667, 'auc': 0.6158437921885159}]</t>
         </is>
       </c>
       <c r="P603" t="n">
-        <v>0.7563299382572706</v>
+        <v>0.6883787042867273</v>
       </c>
       <c r="Q603" t="n">
-        <v>0.7164179104477612</v>
+        <v>0.2941176470588235</v>
       </c>
       <c r="R603" t="n">
-        <v>0.2883087284547744</v>
+        <v>0.2629967717631905</v>
       </c>
       <c r="S603" t="n">
-        <v>0.9417904797208708</v>
+        <v>0.4297480246665677</v>
       </c>
       <c r="T603" t="inlineStr">
         <is>
@@ -52317,92 +52317,6 @@
         </is>
       </c>
       <c r="X603" t="inlineStr">
-        <is>
-          <t>/home/nanchang/LJH02/Brain_Neuroimage_Processing/Visualization/datasets/bla6250EM0626goodtrace.xlsx</t>
-        </is>
-      </c>
-    </row>
-    <row r="604">
-      <c r="A604" t="n">
-        <v>2866</v>
-      </c>
-      <c r="B604" t="n">
-        <v>2896</v>
-      </c>
-      <c r="C604" t="n">
-        <v>2998</v>
-      </c>
-      <c r="D604" t="n">
-        <v>0.2331217290146543</v>
-      </c>
-      <c r="E604" t="n">
-        <v>-0.629521001199603</v>
-      </c>
-      <c r="F604" t="n">
-        <v>-0.8626427302142573</v>
-      </c>
-      <c r="G604" t="n">
-        <v>27.5</v>
-      </c>
-      <c r="H604" t="n">
-        <v>3.54075774582905</v>
-      </c>
-      <c r="I604" t="n">
-        <v>6.25</v>
-      </c>
-      <c r="J604" t="n">
-        <v>21.25</v>
-      </c>
-      <c r="K604" t="n">
-        <v>5.299889778584411</v>
-      </c>
-      <c r="L604" t="n">
-        <v>4.465167874004107</v>
-      </c>
-      <c r="M604" t="inlineStr">
-        <is>
-          <t>simple</t>
-        </is>
-      </c>
-      <c r="N604" t="n">
-        <v>0</v>
-      </c>
-      <c r="O604" t="inlineStr">
-        <is>
-          <t>[]</t>
-        </is>
-      </c>
-      <c r="P604" t="n">
-        <v>0.6883787042867273</v>
-      </c>
-      <c r="Q604" t="n">
-        <v>0.2941176470588235</v>
-      </c>
-      <c r="R604" t="n">
-        <v>0.2629967717631905</v>
-      </c>
-      <c r="S604" t="n">
-        <v>0.4297480246665677</v>
-      </c>
-      <c r="T604" t="inlineStr">
-        <is>
-          <t>n59</t>
-        </is>
-      </c>
-      <c r="U604" t="n">
-        <v>603</v>
-      </c>
-      <c r="V604" t="inlineStr">
-        <is>
-          <t>bla6250EM0626goodtrace.xlsx</t>
-        </is>
-      </c>
-      <c r="W604" t="inlineStr">
-        <is>
-          <t>../datasets/bla6250EM0626goodtrace.xlsx</t>
-        </is>
-      </c>
-      <c r="X604" t="inlineStr">
         <is>
           <t>/home/nanchang/LJH02/Brain_Neuroimage_Processing/Visualization/datasets/bla6250EM0626goodtrace.xlsx</t>
         </is>
